--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0056999999999789</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004090267983074222</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>12.95089999999909</v>
+        <v>7.143400000000838</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8510937222121577</v>
+        <v>0.5248088209142746</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>54.34459999999963</v>
+        <v>45.99380000000237</v>
       </c>
       <c r="F8" t="n">
-        <v>1.475849702052548</v>
+        <v>1.173173692341571</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>2.375</v>
+        <v>1.815000000000873</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7058486967570495</v>
+        <v>0.5094087730455431</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>7.678500000003259</v>
+        <v>4.547100000001956</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4531195589087765</v>
+        <v>0.3012478235642285</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4095000000001164</v>
+        <v>0.3311999999999898</v>
       </c>
       <c r="F14" t="n">
-        <v>2.143298969073569</v>
+        <v>1.450515463918495</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>3.317600000000675</v>
+        <v>2.300299999999697</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5653041825090648</v>
+        <v>0.3504119138143047</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -919,7 +919,7 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2475000000005821</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>44655</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7402000000001863</v>
+        <v>0.4934999999997672</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04665784248839626</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>1057.7</v>
@@ -1027,7 +1027,7 @@
         <v>44729</v>
       </c>
       <c r="E22" t="n">
-        <v>0.008199999999487773</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>6.036000000004424</v>
+        <v>3.90559999999823</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1687044662654693</v>
+        <v>0.1968165980360451</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.5703000000008615</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.005872060110150056</v>
       </c>
       <c r="G26" t="n">
         <v>1943.100000000004</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4134999999994761</v>
+        <v>5.916100000000734</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.5841701956041848</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>5.274299999995856</v>
+        <v>3.397999999998137</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3483615510645308</v>
+        <v>0.2374385581651257</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>70.29780000000028</v>
+        <v>71.47110000000103</v>
       </c>
       <c r="F30" t="n">
-        <v>1.469286922093337</v>
+        <v>1.509052666309086</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>3.269500000000698</v>
+        <v>3.338800000000629</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.5214485794318749</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>4.04989999999525</v>
+        <v>2.820600000000559</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6754151478322116</v>
+        <v>0.5017415957868337</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1621,7 +1621,7 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>1.547099999990314</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>6.071899999999732</v>
+        <v>2.74429999999993</v>
       </c>
       <c r="F46" t="n">
-        <v>2.041492726122596</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>9.954200000001583</v>
+        <v>7.616599999996834</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7924340848304323</v>
+        <v>0.7059992357659679</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>4.922299999999813</v>
+        <v>4.520899999997345</v>
       </c>
       <c r="F55" t="n">
-        <v>0.07697553743506849</v>
+        <v>0.08224610822832447</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>21.49890000000014</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1.49937174174578</v>
       </c>
       <c r="G56" t="n">
         <v>748.1000000000222</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>0.01500000000005457</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>0.151515151515697</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>32.36409999999451</v>
+        <v>22.38810000000522</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2121503674568202</v>
+        <v>0.187404610056912</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2191,7 +2191,7 @@
         <v>0.005599999999685678</v>
       </c>
       <c r="F65" t="n">
-        <v>0.001407742584134154</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2269,7 +2269,7 @@
         <v>44707</v>
       </c>
       <c r="E68" t="n">
-        <v>0.008699999999998908</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>1.083600000001024</v>
+        <v>0.4714999999996508</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1039768618947438</v>
+        <v>0.04109423957619308</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.175</v>
+        <v>0.0275999999998021</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05471633629524112</v>
+        <v>0.003485987696478219</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1523999999997613</v>
+        <v>0.1724000000001979</v>
       </c>
       <c r="F71" t="n">
-        <v>0.03778990450197039</v>
+        <v>0.03983628922238388</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>9.695199999999023</v>
+        <v>6.669099999999162</v>
       </c>
       <c r="F72" t="n">
-        <v>0.6080902586680806</v>
+        <v>0.4601678591085147</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>2.145399999991059</v>
+        <v>2.681599999999162</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1232563483851008</v>
+        <v>0.2156842468108671</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>2.520499999995809</v>
+        <v>1.527899999998044</v>
       </c>
       <c r="F77" t="n">
-        <v>0.02226798703003615</v>
+        <v>0.01217246516515265</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6720000000001164</v>
+        <v>0.2122000000003027</v>
       </c>
       <c r="F78" t="n">
-        <v>0.05015471892727441</v>
+        <v>0.01367973182054551</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0238999999999578</v>
+        <v>0.01190000000005966</v>
       </c>
       <c r="F83" t="n">
-        <v>0.05020920502125447</v>
+        <v>0.02510460251100778</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2755,10 +2755,10 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>0.6090999999985798</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>0.01401110636467189</v>
       </c>
       <c r="G86" t="n">
         <v>1170.500000000015</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.2256999999997788</v>
+        <v>0.0930000000000291</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3539999999993463</v>
+        <v>0.1769999999996731</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.009100000000034924</v>
+        <v>0.00459999999984575</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01188630491010218</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>27.30850000000209</v>
+        <v>17.05420000000158</v>
       </c>
       <c r="F94" t="n">
-        <v>5.973767885535341</v>
+        <v>4.624854266031853</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>12.81650000000372</v>
+        <v>8.18399999999674</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3634962448155065</v>
+        <v>0.1817453200308787</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>0.04809999999997672</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>0.03306808134424622</v>
       </c>
       <c r="G97" t="n">
         <v>113.1000000000029</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>9.227000000001862</v>
+        <v>5.621799999999348</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1330658436214854</v>
+        <v>0.104777091906771</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,7 +3106,7 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>0.01350000000002183</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>1.050899999999092</v>
+        <v>0.8597000000008848</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1630261660977996</v>
+        <v>0.1086841107322343</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>3.187700000000768</v>
+        <v>1.312599999998929</v>
       </c>
       <c r="F104" t="n">
-        <v>0.03920451575805866</v>
+        <v>0.06860398264772602</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1144000000000233</v>
+        <v>0.1069999999999709</v>
       </c>
       <c r="F105" t="n">
-        <v>0.08614457831326851</v>
+        <v>0.06114457831310693</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5885000000009313</v>
+        <v>0.3825000000011641</v>
       </c>
       <c r="F106" t="n">
-        <v>0.04740773286500922</v>
+        <v>0.03015524311670166</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3376,7 +3376,7 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0.02109999999993306</v>
+        <v>0.04220000000004802</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>2.571099999999569</v>
+        <v>0.3896000000007916</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1117292801833478</v>
+        <v>0.1005448809867644</v>
       </c>
       <c r="G112" t="n">
         <v>348.7000000000023</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>1.218400000000838</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>0.2339421613411222</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>4.140399999998044</v>
+        <v>2.870600000000559</v>
       </c>
       <c r="F117" t="n">
-        <v>0.824462365591492</v>
+        <v>0.6348118279593551</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>200.7989000000001</v>
+        <v>89.42600000000093</v>
       </c>
       <c r="F119" t="n">
-        <v>22.94801679888157</v>
+        <v>4.175641623891753</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7938999999983934</v>
+        <v>0.703200000000652</v>
       </c>
       <c r="F122" t="n">
-        <v>0.02368787414723066</v>
+        <v>0.01579423639148152</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3754,10 +3754,10 @@
         <v>44656</v>
       </c>
       <c r="E123" t="n">
-        <v>0.8986999999993713</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.01611323342138812</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
         <v>1020.900000000006</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>4.49100000000035</v>
+        <v>2.125099999998929</v>
       </c>
       <c r="F126" t="n">
-        <v>2.781818181818021</v>
+        <v>1.54772727272489</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>2.404899999999907</v>
+        <v>1.596799999999348</v>
       </c>
       <c r="F129" t="n">
-        <v>0.04106712460849648</v>
+        <v>0.0208273077851852</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>7.075599999999395</v>
+        <v>4.410099999999511</v>
       </c>
       <c r="F133" t="n">
-        <v>0.103530784943066</v>
+        <v>0.07328567259995708</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>36.24960000000137</v>
+        <v>33.27619999999879</v>
       </c>
       <c r="F134" t="n">
-        <v>2.625367647059184</v>
+        <v>2.444602941176597</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>0.07250000000003638</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>0.01497524752472679</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,7 +4132,7 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>0.005799999999999273</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4159,10 +4159,10 @@
         <v>44732</v>
       </c>
       <c r="E138" t="n">
-        <v>79.65200000000186</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>1.41080273963725</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
         <v>3080.7</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0157999999999447</v>
+        <v>0.04740000000019791</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>0.006106280193215398</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>1.577000000001863</v>
+        <v>1.169500000000699</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2339200586731873</v>
+        <v>0.1819215254863275</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>3.207799999997951</v>
+        <v>2.075599999993574</v>
       </c>
       <c r="F145" t="n">
-        <v>0.09004581026855703</v>
+        <v>0.06302729528472834</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>3.564200000002165</v>
+        <v>2.170699999999488</v>
       </c>
       <c r="F146" t="n">
-        <v>0.9854579207931686</v>
+        <v>0.6803836633660546</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4483,10 +4483,10 @@
         <v>44734</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>0.01129999999993743</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>0.03692810457495923</v>
       </c>
       <c r="G150" t="n">
         <v>30.59999999999974</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>1.323699999999371</v>
+        <v>1.320799999999872</v>
       </c>
       <c r="F151" t="n">
-        <v>0.5911926605507298</v>
+        <v>0.6411009174309497</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>2.536500000001979</v>
+        <v>0.7480999999999767</v>
       </c>
       <c r="F157" t="n">
-        <v>0.1469238050166248</v>
+        <v>0.08851159488878098</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>0.4995999999999185</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>0.6547837483616431</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>
@@ -4915,10 +4915,10 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>0.04899999999997817</v>
+        <v>0.006099999999969441</v>
       </c>
       <c r="F166" t="n">
-        <v>0.01796874999993035</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>102.4000000000001</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>7.143400000000838</v>
+        <v>5.181299999999465</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5248088209142746</v>
+        <v>0.291516983816339</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>45.99380000000237</v>
+        <v>40.77179999999935</v>
       </c>
       <c r="F8" t="n">
-        <v>1.173173692341571</v>
+        <v>1.038280732730147</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>1.815000000000873</v>
+        <v>0.9460999999995693</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5094087730455431</v>
+        <v>0.09205340114363797</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>4.547100000001956</v>
+        <v>4.075200000003679</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3012478235642285</v>
+        <v>0.2539466047596812</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.02200000000000273</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.1913043478261103</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3311999999999898</v>
+        <v>0.2703999999999723</v>
       </c>
       <c r="F14" t="n">
-        <v>1.450515463918495</v>
+        <v>1.337113402060359</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>2.300299999999697</v>
+        <v>2.034799999999814</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3504119138143047</v>
+        <v>0.2943282636254439</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.3092000000004191</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.0165043362242597</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -973,7 +973,7 @@
         <v>44655</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4934999999997672</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>3.90559999999823</v>
+        <v>7.101199999998789</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1968165980360451</v>
+        <v>0.3655210643015144</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5703000000008615</v>
+        <v>0.114100000000326</v>
       </c>
       <c r="F26" t="n">
-        <v>0.005872060110150056</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>1943.100000000004</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>5.916100000000734</v>
+        <v>5.198300000000745</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5841701956041848</v>
+        <v>0.4252873563217636</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>3.397999999998137</v>
+        <v>3.340799999999581</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2374385581651257</v>
+        <v>0.2108956854177516</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>71.47110000000103</v>
+        <v>36.59000000000233</v>
       </c>
       <c r="F30" t="n">
-        <v>1.509052666309086</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>3.338800000000629</v>
+        <v>1.815899999999965</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5214485794318749</v>
+        <v>0.2051620648256536</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>27.00870000000577</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.01381782580289909</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>2.820600000000559</v>
+        <v>2.144099999999162</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5017415957868337</v>
+        <v>0.3666666666648862</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1675,7 +1675,7 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>2.74429999999993</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>7.616599999996834</v>
+        <v>5.957500000001164</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7059992357659679</v>
+        <v>0.4322315628586502</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>4.520899999997345</v>
+        <v>4.603899999998975</v>
       </c>
       <c r="F55" t="n">
-        <v>0.08224610822832447</v>
+        <v>0.0790066716085665</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>21.49890000000014</v>
+        <v>17.65310000000172</v>
       </c>
       <c r="F56" t="n">
-        <v>1.49937174174578</v>
+        <v>0.8603528939982649</v>
       </c>
       <c r="G56" t="n">
         <v>748.1000000000222</v>
@@ -1975,7 +1975,7 @@
         <v>0.01500000000005457</v>
       </c>
       <c r="F57" t="n">
-        <v>0.151515151515697</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>22.38810000000522</v>
+        <v>18.78669999999693</v>
       </c>
       <c r="F63" t="n">
-        <v>0.187404610056912</v>
+        <v>0.1041133240359765</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,7 +2188,7 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.005599999999685678</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4714999999996508</v>
+        <v>0.4213000000017928</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04109423957619308</v>
+        <v>0.06044830079541</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0275999999998021</v>
+        <v>0.02289999999993597</v>
       </c>
       <c r="F70" t="n">
-        <v>0.003485987696478219</v>
+        <v>0.004340396445673547</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1724000000001979</v>
+        <v>0.157300000000032</v>
       </c>
       <c r="F71" t="n">
-        <v>0.03983628922238388</v>
+        <v>0.03169622555707733</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>6.669099999999162</v>
+        <v>6.728900000004796</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4601678591085147</v>
+        <v>0.4656576774909307</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>2.681599999999162</v>
+        <v>2.145299999997951</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2156842468108671</v>
+        <v>0.03081695966942215</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>1.527899999998044</v>
+        <v>2.147800000000279</v>
       </c>
       <c r="F77" t="n">
-        <v>0.01217246516515265</v>
+        <v>0.0433441416177044</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2122000000003027</v>
+        <v>0.1061000000001513</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01367973182054551</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01190000000005966</v>
+        <v>0.0239000000001397</v>
       </c>
       <c r="F83" t="n">
-        <v>0.02510460251100778</v>
+        <v>0.07489539748957492</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2755,10 +2755,10 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>0.6090999999985798</v>
+        <v>0.6325000000011641</v>
       </c>
       <c r="F86" t="n">
-        <v>0.01401110636467189</v>
+        <v>0.04002563007284676</v>
       </c>
       <c r="G86" t="n">
         <v>1170.500000000015</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0930000000000291</v>
+        <v>0.09290000000000873</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1769999999996731</v>
+        <v>0.1326666666670109</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2890,10 +2890,10 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2.54089999999851</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.06432821084074339</v>
       </c>
       <c r="G91" t="n">
         <v>3949.89999999998</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.00459999999984575</v>
+        <v>0.01370000000024447</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>0.03540051679649731</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>17.05420000000158</v>
+        <v>16.79969999999739</v>
       </c>
       <c r="F94" t="n">
-        <v>4.624854266031853</v>
+        <v>4.278007419182733</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>8.18399999999674</v>
+        <v>6.639899999997579</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1817453200308787</v>
+        <v>0.1904046631547345</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0.04809999999997672</v>
+        <v>0.06680000000051223</v>
       </c>
       <c r="F97" t="n">
-        <v>0.03306808134424622</v>
+        <v>0.02599469496036079</v>
       </c>
       <c r="G97" t="n">
         <v>113.1000000000029</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>5.621799999999348</v>
+        <v>5.37730000000156</v>
       </c>
       <c r="F98" t="n">
-        <v>0.104777091906771</v>
+        <v>0.07962962962963362</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,7 +3106,7 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.01350000000002183</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8597000000008848</v>
+        <v>0.4777000000001863</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1086841107322343</v>
+        <v>0.07246871444796135</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>1.312599999998929</v>
+        <v>1.687599999998929</v>
       </c>
       <c r="F104" t="n">
-        <v>0.06860398264772602</v>
+        <v>0.01959964459311157</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1069999999999709</v>
+        <v>0.0923000000000684</v>
       </c>
       <c r="F105" t="n">
-        <v>0.06114457831310693</v>
+        <v>0.07786144578337834</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.3825000000011641</v>
+        <v>0.323599999997532</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03015524311670166</v>
+        <v>0.01723784417057619</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3376,7 +3376,7 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0.04220000000004802</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.3896000000007916</v>
+        <v>0.3506000000008498</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1005448809867644</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>348.7000000000023</v>
@@ -3541,7 +3541,7 @@
         <v>0.02880000000000109</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07128712871298719</v>
+        <v>0.07128712871276206</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>1.218400000000838</v>
+        <v>1.11020000000135</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2339421613411222</v>
+        <v>0.254185692542329</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>2.870600000000559</v>
+        <v>2.521000000002096</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6348118279593551</v>
+        <v>0.4616935483867898</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>89.42600000000093</v>
+        <v>33.32509999999893</v>
       </c>
       <c r="F119" t="n">
-        <v>4.175641623891753</v>
+        <v>3.599696686887585</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.703200000000652</v>
+        <v>0.4537000000011176</v>
       </c>
       <c r="F122" t="n">
-        <v>0.01579423639148152</v>
+        <v>0.01578727551170086</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>2.125099999998929</v>
+        <v>1.648399999999674</v>
       </c>
       <c r="F126" t="n">
-        <v>1.54772727272489</v>
+        <v>1.12824675324867</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>1.596799999999348</v>
+        <v>1.236499999999069</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0208273077851852</v>
+        <v>0.01642865750777148</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>4.410099999999511</v>
+        <v>3.687799999999697</v>
       </c>
       <c r="F133" t="n">
-        <v>0.07328567259995708</v>
+        <v>0.06122702071780281</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>33.27619999999879</v>
+        <v>33.83800000000046</v>
       </c>
       <c r="F134" t="n">
-        <v>2.444602941176597</v>
+        <v>2.531573529411741</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.07250000000003638</v>
+        <v>0.03629999999993742</v>
       </c>
       <c r="F135" t="n">
-        <v>0.01497524752472679</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4135,7 +4135,7 @@
         <v>0.005799999999999273</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>0.0185897435897414</v>
       </c>
       <c r="G137" t="n">
         <v>31.19999999999976</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.04740000000019791</v>
+        <v>0.03149999999986904</v>
       </c>
       <c r="F139" t="n">
-        <v>0.006106280193215398</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>3.078300000000309</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>0.2558173356603224</v>
       </c>
       <c r="G142" t="n">
         <v>343.8000000000002</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>1.169500000000699</v>
+        <v>1.063199999998324</v>
       </c>
       <c r="F144" t="n">
-        <v>0.1819215254863275</v>
+        <v>0.2079207920786901</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>2.075599999993574</v>
+        <v>1.320900000003167</v>
       </c>
       <c r="F145" t="n">
-        <v>0.06302729528472834</v>
+        <v>0.0630368390912515</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>2.170699999999488</v>
+        <v>2.009599999999045</v>
       </c>
       <c r="F146" t="n">
-        <v>0.6803836633660546</v>
+        <v>0.5631806930690094</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4486,7 +4486,7 @@
         <v>0.01129999999993743</v>
       </c>
       <c r="F150" t="n">
-        <v>0.03692810457495923</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
         <v>30.59999999999974</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>1.320799999999872</v>
+        <v>1.577499999999418</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6411009174309497</v>
+        <v>0.8061467889904924</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4618,10 +4618,10 @@
         <v>44712</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>0.003500000000349246</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>0.0002069461938680603</v>
       </c>
       <c r="G155" t="n">
         <v>1111.399999999981</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.7480999999999767</v>
+        <v>0.763200000001234</v>
       </c>
       <c r="F157" t="n">
-        <v>0.08851159488878098</v>
+        <v>0.001786559394374975</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.4995999999999185</v>
+        <v>0.9940999999998894</v>
       </c>
       <c r="F165" t="n">
-        <v>0.6547837483616431</v>
+        <v>0.6480996068151847</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>
@@ -4915,7 +4915,7 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>0.006099999999969441</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.08420000000000982</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.007898448519046511</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>5.181299999999465</v>
+        <v>3.660700000001816</v>
       </c>
       <c r="F6" t="n">
-        <v>0.291516983816339</v>
+        <v>0.2000711364040571</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>40.77179999999935</v>
+        <v>37.62410000000382</v>
       </c>
       <c r="F8" t="n">
-        <v>1.038280732730147</v>
+        <v>0.9807382476275008</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9460999999995693</v>
+        <v>0.5116999999998371</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09205340114363797</v>
+        <v>0.233248569612779</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -730,7 +730,7 @@
         <v>44632</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.02329999999992651</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>4.075200000003679</v>
+        <v>3.388800000003539</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2539466047596812</v>
+        <v>0.2365206035989012</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02200000000000273</v>
+        <v>0.03089999999999691</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1913043478261103</v>
+        <v>0.03826086956520229</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2703999999999723</v>
+        <v>0.2126999999998588</v>
       </c>
       <c r="F14" t="n">
-        <v>1.337113402060359</v>
+        <v>0.8556701030926342</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>2.034799999999814</v>
+        <v>1.916800000000512</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2943282636254439</v>
+        <v>0.3130228136877827</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3092000000004191</v>
+        <v>0.4948000000003958</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0165043362242597</v>
+        <v>0.0495130086723908</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>7.101199999998789</v>
+        <v>5.325899999996182</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3655210643015144</v>
+        <v>0.05623218245142476</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.114100000000326</v>
+        <v>0.1900999999998021</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.005872060110150056</v>
       </c>
       <c r="G26" t="n">
         <v>1943.100000000004</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>5.198300000000745</v>
+        <v>2.50170000000071</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4252873563217636</v>
+        <v>0.07918935269228769</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>3.340799999999581</v>
+        <v>2.974700000003213</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2108956854177516</v>
+        <v>0.1952758055710679</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>36.59000000000233</v>
+        <v>35.90640000000131</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.4470573679219878</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.04619999999999891</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.054198473282376</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>1.815899999999965</v>
+        <v>0.9214999999996507</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2051620648256536</v>
+        <v>0.1635454181672467</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>27.00870000000577</v>
+        <v>7.254399999999441</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01381782580289909</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>2.144099999999162</v>
+        <v>1.762899999995716</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3666666666648862</v>
+        <v>0.3473471040907555</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1621,7 +1621,7 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1.071000000007916</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>5.957500000001164</v>
+        <v>5.127900000003865</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4322315628586502</v>
+        <v>0.5474971341233789</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>0.0008000000000265572</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.002173913043550415</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>4.603899999998975</v>
+        <v>4.196500000002561</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0790066716085665</v>
+        <v>0.07571163825064783</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>17.65310000000172</v>
+        <v>6.436300000001211</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8603528939982649</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>748.1000000000222</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01500000000005457</v>
+        <v>0.1074999999999818</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>0.633333333333721</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>18.78669999999693</v>
+        <v>15.48389999999199</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1041133240359765</v>
+        <v>0.1383659526458117</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,7 +2188,7 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>0.005599999999685678</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2.133799999998883</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>0.3122807017552833</v>
       </c>
       <c r="G67" t="n">
         <v>262.2000000000071</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4213000000017928</v>
+        <v>0.4415000000008149</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06044830079541</v>
+        <v>0.04596288262247449</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.02289999999993597</v>
+        <v>0.02100000000027649</v>
       </c>
       <c r="F70" t="n">
-        <v>0.004340396445673547</v>
+        <v>0.002836637047243942</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.157300000000032</v>
+        <v>0.1202999999997701</v>
       </c>
       <c r="F71" t="n">
-        <v>0.03169622555707733</v>
+        <v>0.02301045929957229</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>6.728900000004796</v>
+        <v>6.191399999998976</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4656576774909307</v>
+        <v>0.3889515685191389</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,7 +2458,7 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>2.145299999997951</v>
+        <v>0.5364000000059604</v>
       </c>
       <c r="F75" t="n">
         <v>0.03081695966942215</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>2.147800000000279</v>
+        <v>1.852999999996973</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0433441416177044</v>
+        <v>0.03614494785712234</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.1061000000001513</v>
+        <v>0.1415000000000873</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>0.004564208354813801</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0239000000001397</v>
+        <v>0.01790000000000873</v>
       </c>
       <c r="F83" t="n">
-        <v>0.07489539748957492</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2755,10 +2755,10 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>0.6325000000011641</v>
+        <v>0.4685000000026776</v>
       </c>
       <c r="F86" t="n">
-        <v>0.04002563007284676</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>1170.500000000015</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.09290000000000873</v>
+        <v>0.0930000000000291</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1326666666670109</v>
+        <v>0.1773333333330744</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2893,7 +2893,7 @@
         <v>2.54089999999851</v>
       </c>
       <c r="F91" t="n">
-        <v>0.06432821084074339</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>3949.89999999998</v>
@@ -2920,7 +2920,7 @@
         <v>0.01370000000024447</v>
       </c>
       <c r="F92" t="n">
-        <v>0.03540051679649731</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>16.79969999999739</v>
+        <v>14.98150000000023</v>
       </c>
       <c r="F94" t="n">
-        <v>4.278007419182733</v>
+        <v>3.661314255434378</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>6.639899999997579</v>
+        <v>6.331099999998696</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1904046631547345</v>
+        <v>0.1644378432906652</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0.06680000000051223</v>
+        <v>0.04809999999997672</v>
       </c>
       <c r="F97" t="n">
-        <v>0.02599469496036079</v>
+        <v>0.01653404067180145</v>
       </c>
       <c r="G97" t="n">
         <v>113.1000000000029</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>5.37730000000156</v>
+        <v>4.399700000000303</v>
       </c>
       <c r="F98" t="n">
-        <v>0.07962962962963362</v>
+        <v>0.07125171467764699</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>0.0100999999999658</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>0.06538461538438152</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.4777000000001863</v>
+        <v>0.286600000000908</v>
       </c>
       <c r="F102" t="n">
-        <v>0.07246871444796135</v>
+        <v>0.03621539628427294</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>1.687599999998929</v>
+        <v>0.9376000000018394</v>
       </c>
       <c r="F104" t="n">
-        <v>0.01959964459311157</v>
+        <v>0.02940469346165499</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0923000000000684</v>
+        <v>0.103400000000147</v>
       </c>
       <c r="F105" t="n">
-        <v>0.07786144578337834</v>
+        <v>0.07786144578310439</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.323599999997532</v>
+        <v>0.4119999999995343</v>
       </c>
       <c r="F106" t="n">
-        <v>0.01723784417057619</v>
+        <v>0.04310193321658488</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,7 +3322,7 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>54.46399999999558</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>2.048099999999977</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>0.6886884108257496</v>
       </c>
       <c r="G109" t="n">
         <v>144.1000000000003</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>2.749099999997997</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>0.1614053350680568</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3457,7 +3457,7 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.3506000000008498</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>0.02880000000000109</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07128712871276206</v>
+        <v>0.07128712871298719</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>1.11020000000135</v>
+        <v>1.127299999998649</v>
       </c>
       <c r="F116" t="n">
-        <v>0.254185692542329</v>
+        <v>0.3177574835097499</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>2.521000000002096</v>
+        <v>1.80339999999851</v>
       </c>
       <c r="F117" t="n">
-        <v>0.4616935483867898</v>
+        <v>0.3462813620068183</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>33.32509999999893</v>
+        <v>1430.142099999997</v>
       </c>
       <c r="F119" t="n">
-        <v>3.599696686887585</v>
+        <v>330.0778814745809</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.4537000000011176</v>
+        <v>0.2268000000010943</v>
       </c>
       <c r="F122" t="n">
-        <v>0.01578727551170086</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>1.648399999999674</v>
+        <v>1.329699999999139</v>
       </c>
       <c r="F126" t="n">
-        <v>1.12824675324867</v>
+        <v>1.030357142853879</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>1.236499999999069</v>
+        <v>1.139099999994505</v>
       </c>
       <c r="F129" t="n">
-        <v>0.01642865750777148</v>
+        <v>0.0178928657508226</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>3.687799999999697</v>
+        <v>3.270699999999488</v>
       </c>
       <c r="F133" t="n">
-        <v>0.06122702071780281</v>
+        <v>0.05807192880070809</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>33.83800000000046</v>
+        <v>32.13379999999889</v>
       </c>
       <c r="F134" t="n">
-        <v>2.531573529411741</v>
+        <v>2.193985294117538</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.03629999999993742</v>
+        <v>0.01460000000006403</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>0.006023102310257491</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,10 +4132,10 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.005799999999999273</v>
+        <v>0.005700000000069849</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0185897435897414</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>31.19999999999976</v>
@@ -4186,7 +4186,7 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.03149999999986904</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -4240,7 +4240,7 @@
         <v>44717</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>0.009199999999987085</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>3.078300000000309</v>
+        <v>3.518100000000049</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2558173356603224</v>
+        <v>0.7674810936590629</v>
       </c>
       <c r="G142" t="n">
         <v>343.8000000000002</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>1.063199999998324</v>
+        <v>0.726500000001397</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2079207920786901</v>
+        <v>0.0584891822526909</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>1.320900000003167</v>
+        <v>1.320899999991525</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0630368390912515</v>
+        <v>0.06302729528472834</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>2.009599999999045</v>
+        <v>1.668400000000838</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5631806930690094</v>
+        <v>0.4692450495057759</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4483,7 +4483,7 @@
         <v>44734</v>
       </c>
       <c r="E150" t="n">
-        <v>0.01129999999993743</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>1.577499999999418</v>
+        <v>1.894100000000617</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8061467889904924</v>
+        <v>0.9315596330283715</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4618,10 +4618,10 @@
         <v>44712</v>
       </c>
       <c r="E155" t="n">
-        <v>0.003500000000349246</v>
+        <v>0.002299999998649582</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0002069461938680603</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
         <v>1111.399999999981</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.763200000001234</v>
+        <v>0.03520000000135041</v>
       </c>
       <c r="F157" t="n">
-        <v>0.001786559394374975</v>
+        <v>0.002378135352590291</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>0.01670000000012806</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>0.005934718101235846</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.9940999999998894</v>
+        <v>0.769300000000294</v>
       </c>
       <c r="F165" t="n">
-        <v>0.6480996068151847</v>
+        <v>0.3601572739191762</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08420000000000982</v>
+        <v>0.02809999999999491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007898448519046511</v>
+        <v>0.03173483779970494</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>3.660700000001816</v>
+        <v>1.814900000000489</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2000711364040571</v>
+        <v>0.09455806508998887</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>37.62410000000382</v>
+        <v>32.59679999999935</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9807382476275008</v>
+        <v>0.8178051202823919</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -676,7 +676,7 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.02240000000456348</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5116999999998371</v>
+        <v>0.8110000000000582</v>
       </c>
       <c r="F10" t="n">
-        <v>0.233248569612779</v>
+        <v>0.2823267641444169</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -730,7 +730,7 @@
         <v>44632</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02329999999992651</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>3.388800000003539</v>
+        <v>2.882699999999022</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2365206035989012</v>
+        <v>0.1817469529883152</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03089999999999691</v>
+        <v>0.004399999999998272</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03826086956520229</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2126999999998588</v>
+        <v>0.1566000000000713</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8556701030926342</v>
+        <v>0.7587628865986824</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>1.916800000000512</v>
+        <v>0.9878999999986263</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3130228136877827</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4948000000003958</v>
+        <v>0.4947999999989406</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0495130086723908</v>
+        <v>0.01650433622406555</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>5.325899999996182</v>
+        <v>3.19550000000163</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05623218245142476</v>
+        <v>0.1968165980365061</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1900999999998021</v>
+        <v>0.114100000000326</v>
       </c>
       <c r="F26" t="n">
-        <v>0.005872060110150056</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>1943.100000000004</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>2.50170000000071</v>
+        <v>4.756299999999465</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07918935269228769</v>
+        <v>0.5107683000604476</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>2.974700000003213</v>
+        <v>2.597100000001956</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1952758055710679</v>
+        <v>0.1593255051883438</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>35.90640000000131</v>
+        <v>17.03760000000475</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4470573679219878</v>
+        <v>0.2556110034231147</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04619999999999891</v>
+        <v>0.0319999999999709</v>
       </c>
       <c r="F31" t="n">
-        <v>0.054198473282376</v>
+        <v>0.06793893129766539</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9214999999996507</v>
+        <v>0.7171000000002096</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1635454181672467</v>
+        <v>0.1234093637455995</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>7.254399999999441</v>
+        <v>20.42389999999432</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.01764428012790674</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.762899999995716</v>
+        <v>1.686700000002747</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3473471040907555</v>
+        <v>0.3358039692193751</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1621,7 +1621,7 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>1.071000000007916</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2.322099999999773</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.6500316255531093</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>5.127900000003865</v>
+        <v>4.826299999997718</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5474971341233789</v>
+        <v>0.3746083301482659</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1759,7 +1759,7 @@
         <v>0.0008000000000265572</v>
       </c>
       <c r="F49" t="n">
-        <v>0.002173913043550415</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>4.196500000002561</v>
+        <v>4.344599999999628</v>
       </c>
       <c r="F55" t="n">
-        <v>0.07571163825064783</v>
+        <v>0.08328762045967074</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>6.436300000001211</v>
+        <v>9.160399999999209</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.6140355567435584</v>
       </c>
       <c r="G56" t="n">
         <v>748.1000000000222</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1074999999999818</v>
+        <v>0.1583000000000538</v>
       </c>
       <c r="F57" t="n">
-        <v>0.633333333333721</v>
+        <v>0.9656565656566614</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>15.48389999999199</v>
+        <v>18.42090000000317</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1383659526458117</v>
+        <v>0.1502859739568673</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,7 +2188,7 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.005599999999685678</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>2.133799999998883</v>
+        <v>1.612800000002608</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3122807017552833</v>
+        <v>0.3028222730740699</v>
       </c>
       <c r="G67" t="n">
         <v>262.2000000000071</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4415000000008149</v>
+        <v>0.3812999999994645</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04596288262247449</v>
+        <v>0.04593878042873158</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.02100000000027649</v>
+        <v>0.01380000000026485</v>
       </c>
       <c r="F70" t="n">
-        <v>0.002836637047243942</v>
+        <v>0.001879699248130255</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1202999999997701</v>
+        <v>0.0995999999999185</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02301045929957229</v>
+        <v>0.0222828558436385</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>6.191399999998976</v>
+        <v>5.71359999999986</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3889515685191389</v>
+        <v>0.3971794166211799</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5364000000059604</v>
+        <v>0.2682000000029802</v>
       </c>
       <c r="F75" t="n">
-        <v>0.03081695966942215</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>1.852999999996973</v>
+        <v>1.080699999997159</v>
       </c>
       <c r="F77" t="n">
-        <v>0.03614494785712234</v>
+        <v>0.01120848304276172</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2542,7 +2542,7 @@
         <v>0.1415000000000873</v>
       </c>
       <c r="F78" t="n">
-        <v>0.004564208354813801</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01790000000000873</v>
+        <v>0.01189999999987776</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>0.04979079497856715</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2755,10 +2755,10 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4685000000026776</v>
+        <v>0.1873999999981606</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>0.01601025202889006</v>
       </c>
       <c r="G86" t="n">
         <v>1170.500000000015</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.0930000000000291</v>
+        <v>0.1195999999999913</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1773333333330744</v>
+        <v>0.221333333333548</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2890,7 +2890,7 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>2.54089999999851</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.01370000000024447</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>14.98150000000023</v>
+        <v>11.34519999999902</v>
       </c>
       <c r="F94" t="n">
-        <v>3.661314255434378</v>
+        <v>2.350980392154773</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>6.331099999998696</v>
+        <v>4.632499999995344</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1644378432906652</v>
+        <v>0.09520233157736727</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0.04809999999997672</v>
+        <v>0.02929999999978463</v>
       </c>
       <c r="F97" t="n">
-        <v>0.01653404067180145</v>
+        <v>0.009372236958423031</v>
       </c>
       <c r="G97" t="n">
         <v>113.1000000000029</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>4.399700000000303</v>
+        <v>4.216399999998975</v>
       </c>
       <c r="F98" t="n">
-        <v>0.07125171467764699</v>
+        <v>0.07334362139913544</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0100999999999658</v>
+        <v>0.006799999999975626</v>
       </c>
       <c r="F99" t="n">
-        <v>0.06538461538438152</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.286600000000908</v>
+        <v>0.1433000000019092</v>
       </c>
       <c r="F102" t="n">
-        <v>0.03621539628427294</v>
+        <v>0.01812665908239604</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9376000000018394</v>
+        <v>0.7501000000018394</v>
       </c>
       <c r="F104" t="n">
-        <v>0.02940469346165499</v>
+        <v>0.009799822296555787</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.103400000000147</v>
+        <v>0.1236999999999171</v>
       </c>
       <c r="F105" t="n">
-        <v>0.07786144578310439</v>
+        <v>0.1084337349396579</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.4119999999995343</v>
+        <v>0.5591000000014901</v>
       </c>
       <c r="F106" t="n">
-        <v>0.04310193321658488</v>
+        <v>0.03878148799042919</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,7 +3322,7 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>54.46399999999558</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>2.048099999999977</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.6886884108257496</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>144.1000000000003</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>2.749099999997997</v>
+        <v>1.240399999998044</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1614053350680568</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3541,7 +3541,7 @@
         <v>0.02880000000000109</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07128712871298719</v>
+        <v>0.07128712871276206</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>1.127299999998649</v>
+        <v>1.002000000001863</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3177574835097499</v>
+        <v>0.1762049720952882</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>1.80339999999851</v>
+        <v>2.116200000001117</v>
       </c>
       <c r="F117" t="n">
-        <v>0.3462813620068183</v>
+        <v>0.6018369175635873</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>1430.142099999997</v>
+        <v>1476.137599999999</v>
       </c>
       <c r="F119" t="n">
-        <v>330.0778814745809</v>
+        <v>14.33126458236202</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2268000000010943</v>
+        <v>0.136099999997532</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>0.004740359181277361</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>1.329699999999139</v>
+        <v>1.063799999997718</v>
       </c>
       <c r="F126" t="n">
-        <v>1.030357142853879</v>
+        <v>0.6965909090905098</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>1.139099999994505</v>
+        <v>1.217000000004191</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0178928657508226</v>
+        <v>0.01877259580630534</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>3.270699999999488</v>
+        <v>2.879099999999744</v>
       </c>
       <c r="F133" t="n">
-        <v>0.05807192880070809</v>
+        <v>0.04694339072073013</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>32.13379999999889</v>
+        <v>28.70780000000086</v>
       </c>
       <c r="F134" t="n">
-        <v>2.193985294117538</v>
+        <v>2.027750000000264</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.01460000000006403</v>
+        <v>0.02180000000007567</v>
       </c>
       <c r="F135" t="n">
-        <v>0.006023102310257491</v>
+        <v>0.0029702970297078</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,7 +4132,7 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.005700000000069849</v>
+        <v>0.05199999999995271</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4240,10 +4240,10 @@
         <v>44717</v>
       </c>
       <c r="E141" t="n">
-        <v>0.009199999999987085</v>
+        <v>0.02740000000001146</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>0.04499178981939472</v>
       </c>
       <c r="G141" t="n">
         <v>60.90000000000018</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>3.518100000000049</v>
+        <v>2.63859999999986</v>
       </c>
       <c r="F142" t="n">
-        <v>0.7674810936590629</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
         <v>343.8000000000002</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.726500000001397</v>
+        <v>0.3898999999975786</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0584891822526909</v>
+        <v>0.07799779977922247</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>1.320899999991525</v>
+        <v>1.273600000003353</v>
       </c>
       <c r="F145" t="n">
-        <v>0.06302729528472834</v>
+        <v>0.05852261882133625</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>1.668400000000838</v>
+        <v>1.440799999999581</v>
       </c>
       <c r="F146" t="n">
-        <v>0.4692450495057759</v>
+        <v>0.4223391089098143</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4483,10 +4483,10 @@
         <v>44734</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>0.01130000000002838</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>0.03692810457525645</v>
       </c>
       <c r="G150" t="n">
         <v>30.59999999999974</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>1.894100000000617</v>
+        <v>2.09490000000078</v>
       </c>
       <c r="F151" t="n">
-        <v>0.9315596330283715</v>
+        <v>0.9903669724768751</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4618,7 +4618,7 @@
         <v>44712</v>
       </c>
       <c r="E155" t="n">
-        <v>0.002299999998649582</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.03520000000135041</v>
+        <v>0.6171000000002096</v>
       </c>
       <c r="F157" t="n">
-        <v>0.002378135352590291</v>
+        <v>0.07063416942736826</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4864,7 +4864,7 @@
         <v>0.01670000000012806</v>
       </c>
       <c r="F164" t="n">
-        <v>0.005934718101235846</v>
+        <v>0.00397626112732712</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.769300000000294</v>
+        <v>0.4297000000002299</v>
       </c>
       <c r="F165" t="n">
-        <v>0.3601572739191762</v>
+        <v>0.2030144167757688</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02809999999999491</v>
+        <v>0.02249999999999091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03173483779970494</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>1.814900000000489</v>
+        <v>1.160100000002422</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09455806508998887</v>
+        <v>0.06916236884269475</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>32.59679999999935</v>
+        <v>33.97960000000312</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8178051202823919</v>
+        <v>0.9476440079451937</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02240000000456348</v>
+        <v>0.01109999999171123</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0001641137854354317</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8110000000000582</v>
+        <v>0.5309999999997672</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2823267641444169</v>
+        <v>0.05524475524514082</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>2.882699999999022</v>
+        <v>2.239199999999255</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1817469529883152</v>
+        <v>0.1294689495068196</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004399999999998272</v>
+        <v>0.008799999999996543</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.07652173913040458</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1566000000000713</v>
+        <v>0.1221000000001368</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7587628865986824</v>
+        <v>0.5000000000005567</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9878999999986263</v>
+        <v>0.486600000000908</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.1541825095059936</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4947999999989406</v>
+        <v>0.1855999999999767</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01650433622406555</v>
+        <v>0.00825883922623153</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>3.19550000000163</v>
+        <v>3.905600000004051</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1968165980365061</v>
+        <v>0.1124643649033105</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.114100000000326</v>
+        <v>0.2660999999992782</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.01173897380475875</v>
       </c>
       <c r="G26" t="n">
         <v>1943.100000000004</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>4.756299999999465</v>
+        <v>5.336199999999371</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5107683000604476</v>
+        <v>0.5516636418630515</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>2.597100000001956</v>
+        <v>2.18519999999553</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1593255051883438</v>
+        <v>0.1390360458760348</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>17.03760000000475</v>
+        <v>9.028899999998975</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2556110034231147</v>
+        <v>0.1167608363920769</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0319999999999709</v>
+        <v>0.01779999999998836</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06793893129766539</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7171000000002096</v>
+        <v>0.5763999999995576</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1234093637455995</v>
+        <v>0.107242897158583</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>20.42389999999432</v>
+        <v>9.263299999991432</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01764428012790674</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.686700000002747</v>
+        <v>1.505600000004051</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3358039692193751</v>
+        <v>0.2739975698669028</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>2.322099999999773</v>
+        <v>1.588799999999901</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6500316255531093</v>
+        <v>0.354901960784596</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>4.826299999997718</v>
+        <v>2.563999999995576</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3746083301482659</v>
+        <v>0.1152655712647287</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0008000000000265572</v>
+        <v>0.003999999999996362</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.002173913043550415</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>4.344599999999628</v>
+        <v>4.400900000002002</v>
       </c>
       <c r="F55" t="n">
-        <v>0.08328762045967074</v>
+        <v>0.0786212008895447</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>9.160399999999209</v>
+        <v>6.86359999999986</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6140355567435584</v>
+        <v>0.3034353696031408</v>
       </c>
       <c r="G56" t="n">
         <v>748.1000000000222</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1583000000000538</v>
+        <v>0.170299999999952</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9656565656566614</v>
+        <v>0.7545454545448086</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>18.42090000000317</v>
+        <v>20.94370000000345</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1502859739568673</v>
+        <v>0.1772944513217029</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>0.02240000000019791</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>0.004223227752768273</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>1.612800000002608</v>
+        <v>1.265399999998044</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3028222730740699</v>
+        <v>0.179786422577345</v>
       </c>
       <c r="G67" t="n">
         <v>262.2000000000071</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3812999999994645</v>
+        <v>0.3209999999991851</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04593878042873158</v>
+        <v>0.03142926006275462</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01380000000026485</v>
+        <v>0.007699999999749707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.001879699248130255</v>
+        <v>0.000751879699152636</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0995999999999185</v>
+        <v>0.08559999999997672</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0222828558436385</v>
+        <v>0.01664392905857999</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>5.71359999999986</v>
+        <v>6.609500000003027</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3971794166211799</v>
+        <v>0.5122179416621168</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2682000000029802</v>
+        <v>1.34079999999376</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>0.1540618177632729</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>1.080699999997159</v>
+        <v>1.746299999998882</v>
       </c>
       <c r="F77" t="n">
-        <v>0.01120848304276172</v>
+        <v>0.03562352116380955</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2542,7 +2542,7 @@
         <v>0.1415000000000873</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>0.009128416709627602</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01189999999987776</v>
+        <v>0.01790000000000873</v>
       </c>
       <c r="F83" t="n">
-        <v>0.04979079497856715</v>
+        <v>0.02510460251100778</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2758,7 +2758,7 @@
         <v>0.1873999999981606</v>
       </c>
       <c r="F86" t="n">
-        <v>0.01601025202889006</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>1170.500000000015</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1195999999999913</v>
+        <v>0.8101000000002386</v>
       </c>
       <c r="F87" t="n">
-        <v>0.221333333333548</v>
+        <v>2.479000000000478</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>11.34519999999902</v>
+        <v>9.163499999995111</v>
       </c>
       <c r="F94" t="n">
-        <v>2.350980392154773</v>
+        <v>2.505140434552428</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>4.632499999995344</v>
+        <v>5.404600000008941</v>
       </c>
       <c r="F95" t="n">
-        <v>0.09520233157736727</v>
+        <v>0.1904046631547345</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0.02929999999978463</v>
+        <v>0.03729999999995925</v>
       </c>
       <c r="F97" t="n">
-        <v>0.009372236958423031</v>
+        <v>0.02360742705568688</v>
       </c>
       <c r="G97" t="n">
         <v>113.1000000000029</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>4.216399999998975</v>
+        <v>4.094099999999162</v>
       </c>
       <c r="F98" t="n">
-        <v>0.07334362139913544</v>
+        <v>0.06705761316873705</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.006799999999975626</v>
+        <v>0.0068000000000211</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>0.06538461538481877</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1433000000019092</v>
+        <v>0.0478000000002794</v>
       </c>
       <c r="F102" t="n">
-        <v>0.01812665908239604</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7501000000018394</v>
+        <v>0.75</v>
       </c>
       <c r="F104" t="n">
-        <v>0.009799822296555787</v>
+        <v>0.02939946688966736</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1236999999999171</v>
+        <v>0.1144000000000233</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1084337349396579</v>
+        <v>0.06385542168687916</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5591000000014901</v>
+        <v>0.5002000000036787</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03878148799042919</v>
+        <v>0.03447568834200487</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>3707.588700000005</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>1118.765449607777</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>0.02430000000003929</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>0.05449101796428278</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>1.240399999998044</v>
+        <v>2.177500000002328</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>0.09431359791829873</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>0.1168999999994412</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>0.03352451964423299</v>
       </c>
       <c r="G112" t="n">
         <v>348.7000000000023</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02880000000000109</v>
+        <v>0.0431999999999789</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07128712871276206</v>
+        <v>0.1425742574257493</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>1.002000000001863</v>
+        <v>0.6490999999979976</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1762049720952882</v>
+        <v>0.1531202435302808</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>2.116200000001117</v>
+        <v>2.521000000002096</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6018369175635873</v>
+        <v>0.5276433691757175</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>1476.137599999999</v>
+        <v>172.0250999999989</v>
       </c>
       <c r="F119" t="n">
-        <v>14.33126458236202</v>
+        <v>25.80524965002382</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.136099999997532</v>
+        <v>0.06809999999823049</v>
       </c>
       <c r="F122" t="n">
-        <v>0.004740359181277361</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>1.063799999997718</v>
+        <v>0.7703000000008615</v>
       </c>
       <c r="F126" t="n">
-        <v>0.6965909090905098</v>
+        <v>0.5538961038979312</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>1.217000000004191</v>
+        <v>1.392299999995157</v>
       </c>
       <c r="F129" t="n">
-        <v>0.01877259580630534</v>
+        <v>0.0234664979512827</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>2.879099999999744</v>
+        <v>2.217800000001444</v>
       </c>
       <c r="F133" t="n">
-        <v>0.04694339072073013</v>
+        <v>0.03395097753143825</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>28.70780000000086</v>
+        <v>26.32170000000042</v>
       </c>
       <c r="F134" t="n">
-        <v>2.027750000000264</v>
+        <v>1.843088235293942</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.02180000000007567</v>
+        <v>0.03629999999993742</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0029702970297078</v>
+        <v>0.012004950495019</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,7 +4132,7 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.05199999999995271</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
         <v>0.02740000000001146</v>
       </c>
       <c r="F141" t="n">
-        <v>0.04499178981939472</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>60.90000000000018</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>2.63859999999986</v>
+        <v>7.47609999999986</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>0.5116637579988463</v>
       </c>
       <c r="G142" t="n">
         <v>343.8000000000002</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3898999999975786</v>
+        <v>0.3721000000019558</v>
       </c>
       <c r="F144" t="n">
-        <v>0.07799779977922247</v>
+        <v>0.05848918225055641</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>1.273600000003353</v>
+        <v>1.037800000002608</v>
       </c>
       <c r="F145" t="n">
-        <v>0.05852261882133625</v>
+        <v>0.04052300057303698</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>1.440799999999581</v>
+        <v>1.251299999997718</v>
       </c>
       <c r="F146" t="n">
-        <v>0.4223391089098143</v>
+        <v>0.3519801980194738</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4486,7 +4486,7 @@
         <v>0.01130000000002838</v>
       </c>
       <c r="F150" t="n">
-        <v>0.03692810457525645</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
         <v>30.59999999999974</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>2.09490000000078</v>
+        <v>2.263699999998789</v>
       </c>
       <c r="F151" t="n">
-        <v>0.9903669724768751</v>
+        <v>1.086422018347642</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.6171000000002096</v>
+        <v>1.02269999999844</v>
       </c>
       <c r="F157" t="n">
-        <v>0.07063416942736826</v>
+        <v>0.05036677709398056</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.01670000000012806</v>
+        <v>0.0217000000004191</v>
       </c>
       <c r="F164" t="n">
-        <v>0.00397626112732712</v>
+        <v>0.007893175074280957</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.4297000000002299</v>
+        <v>0.2896999999997206</v>
       </c>
       <c r="F165" t="n">
-        <v>0.2030144167757688</v>
+        <v>0.176671035386393</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02249999999999091</v>
+        <v>0.01690000000003238</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.02383638928072257</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>1.160100000002422</v>
+        <v>0.8372000000003027</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06916236884269475</v>
+        <v>0.05470389471813921</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>33.97960000000312</v>
+        <v>34.18979999999865</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9476440079451937</v>
+        <v>0.9272015007726158</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01109999999171123</v>
+        <v>0.02229999999981374</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001641137854354317</v>
+        <v>0.0001655922882503716</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5309999999997672</v>
+        <v>0.08690000000060535</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05524475524514082</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>2.239199999999255</v>
+        <v>1.930400000000372</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1294689495068196</v>
+        <v>0.150623911781692</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -787,7 +787,7 @@
         <v>0.008799999999996543</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07652173913040458</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1221000000001368</v>
+        <v>0.1197000000000116</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5000000000005567</v>
+        <v>0.7340206185561574</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.486600000000908</v>
+        <v>0.7961999999999534</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1541825095059936</v>
+        <v>0.09809885931528847</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -922,7 +922,7 @@
         <v>0.1855999999999767</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00825883922623153</v>
+        <v>0.01650433622406555</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>3.905600000004051</v>
+        <v>1.775199999997858</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1124643649033105</v>
+        <v>0.02811213177057582</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2660999999992782</v>
+        <v>0.2281000000002678</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01173897380475875</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>1943.100000000004</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>5.336199999999371</v>
+        <v>3.260999999998603</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5516636418630515</v>
+        <v>0.1059286146399861</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>2.18519999999553</v>
+        <v>1.945000000001164</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1390360458760348</v>
+        <v>0.1249726925184226</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>9.028899999998975</v>
+        <v>4.631799999997019</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1167608363920769</v>
+        <v>0.07426485750807599</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01779999999998836</v>
+        <v>0.04610000000002401</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.06755725190844822</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5763999999995576</v>
+        <v>0.5591000000000349</v>
       </c>
       <c r="F33" t="n">
-        <v>0.107242897158583</v>
+        <v>0.1164865946381475</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,7 +1486,7 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>9.263299999991432</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.505600000004051</v>
+        <v>1.238800000003539</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2739975698669028</v>
+        <v>0.2277035236950998</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1621,10 +1621,10 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1.529999999993015</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>0.07525629077309166</v>
       </c>
       <c r="G44" t="n">
         <v>858.4000000000742</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>1.588799999999901</v>
+        <v>1.25</v>
       </c>
       <c r="F46" t="n">
-        <v>0.354901960784596</v>
+        <v>0.4357368753950427</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>2.563999999995576</v>
+        <v>1.131200000003446</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1152655712647287</v>
+        <v>0.1008597630882447</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.003999999999996362</v>
+        <v>0.002400000000034197</v>
       </c>
       <c r="F49" t="n">
-        <v>0.002173913043550415</v>
+        <v>0.004347826086977257</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>4.400900000002002</v>
+        <v>4.209799999999814</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0786212008895447</v>
+        <v>0.07741289844328478</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>6.86359999999986</v>
+        <v>2.270000000001164</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3034353696031408</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>748.1000000000222</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.170299999999952</v>
+        <v>0.176299999999992</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7545454545448086</v>
+        <v>1.026262626263124</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>20.94370000000345</v>
+        <v>24.11180000000168</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1772944513217029</v>
+        <v>0.1999294858737269</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.02240000000019791</v>
+        <v>0.03359999999956927</v>
       </c>
       <c r="F65" t="n">
-        <v>0.004223227752768273</v>
+        <v>0.004223227752402463</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>1.265399999998044</v>
+        <v>1.364699999999721</v>
       </c>
       <c r="F67" t="n">
-        <v>0.179786422577345</v>
+        <v>0.3217391304342767</v>
       </c>
       <c r="G67" t="n">
         <v>262.2000000000071</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3209999999991851</v>
+        <v>0.3913000000000466</v>
       </c>
       <c r="F69" t="n">
-        <v>0.03142926006275462</v>
+        <v>0.0628826223185507</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.007699999999749707</v>
+        <v>0.004299999999784631</v>
       </c>
       <c r="F70" t="n">
-        <v>0.000751879699152636</v>
+        <v>0.0007177033493041822</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.08559999999997672</v>
+        <v>0.08060000000004948</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01664392905857999</v>
+        <v>0.02000909504330774</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>6.609500000003027</v>
+        <v>6.967800000001444</v>
       </c>
       <c r="F72" t="n">
-        <v>0.5122179416621168</v>
+        <v>0.4464777105119911</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>1.34079999999376</v>
+        <v>3.486100000003353</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1540618177632729</v>
+        <v>0.2465012064816269</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>1.746299999998882</v>
+        <v>1.024700000003213</v>
       </c>
       <c r="F77" t="n">
-        <v>0.03562352116380955</v>
+        <v>0.00927613706085121</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2542,7 +2542,7 @@
         <v>0.1415000000000873</v>
       </c>
       <c r="F78" t="n">
-        <v>0.009128416709627602</v>
+        <v>0.004564208354907612</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01790000000000873</v>
+        <v>0.006000000000130967</v>
       </c>
       <c r="F83" t="n">
-        <v>0.02510460251100778</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2755,7 +2755,7 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1873999999981606</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.8101000000002386</v>
+        <v>0.7703000000001339</v>
       </c>
       <c r="F87" t="n">
-        <v>2.479000000000478</v>
+        <v>0.08866666666653719</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>9.163499999995111</v>
+        <v>7.927100000000792</v>
       </c>
       <c r="F94" t="n">
-        <v>2.505140434552428</v>
+        <v>1.695760466349524</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>5.404600000008941</v>
+        <v>5.404599999997299</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1904046631547345</v>
+        <v>0.1125098083169283</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0.03729999999995925</v>
+        <v>0.02669999999998254</v>
       </c>
       <c r="F97" t="n">
-        <v>0.02360742705568688</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>113.1000000000029</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>4.094099999999162</v>
+        <v>3.391400000001886</v>
       </c>
       <c r="F98" t="n">
-        <v>0.06705761316873705</v>
+        <v>0.04924554183818633</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0068000000000211</v>
+        <v>0.01359999999999673</v>
       </c>
       <c r="F99" t="n">
-        <v>0.06538461538481877</v>
+        <v>0.06538461538438152</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0478000000002794</v>
+        <v>0.1432999999989988</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>0.05434205536556531</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>0.75</v>
+        <v>1.500099999998929</v>
       </c>
       <c r="F104" t="n">
-        <v>0.02939946688966736</v>
+        <v>0.04900433805461445</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1144000000000233</v>
+        <v>0.09969999999993888</v>
       </c>
       <c r="F105" t="n">
-        <v>0.06385542168687916</v>
+        <v>0.0862951807226638</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5002000000036787</v>
+        <v>0.4413999999989756</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03447568834200487</v>
+        <v>0.03016988869358054</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3325,7 +3325,7 @@
         <v>3707.588700000005</v>
       </c>
       <c r="F107" t="n">
-        <v>1118.765449607777</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.02430000000003929</v>
+        <v>0.0181999999999789</v>
       </c>
       <c r="F108" t="n">
-        <v>0.05449101796428278</v>
+        <v>0.05449101796373818</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>2.177500000002328</v>
+        <v>0.7248000000021421</v>
       </c>
       <c r="F111" t="n">
-        <v>0.09431359791829873</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3460,7 +3460,7 @@
         <v>0.1168999999994412</v>
       </c>
       <c r="F112" t="n">
-        <v>0.03352451964423299</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>348.7000000000023</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0431999999999789</v>
+        <v>0.04320000000002437</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1425742574257493</v>
+        <v>0.07128712871298719</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6490999999979976</v>
+        <v>0.6261999999987893</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1531202435302808</v>
+        <v>0.1559614408940815</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>2.521000000002096</v>
+        <v>2.171399999997811</v>
       </c>
       <c r="F117" t="n">
-        <v>0.5276433691757175</v>
+        <v>0.445206093188906</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>172.0250999999989</v>
+        <v>110.6012999999977</v>
       </c>
       <c r="F119" t="n">
-        <v>25.80524965002382</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,7 +3727,7 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.06809999999823049</v>
+        <v>0.1134000000020023</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3808,10 +3808,10 @@
         <v>44733</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>232.2495999999985</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>5.142588902174382</v>
       </c>
       <c r="G125" t="n">
         <v>4516.199999999981</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.7703000000008615</v>
+        <v>0.5544000000023516</v>
       </c>
       <c r="F126" t="n">
-        <v>0.5538961038979312</v>
+        <v>0.3461038961059075</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>1.392299999995157</v>
+        <v>1.635700000007637</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0234664979512827</v>
+        <v>0.02581344902412211</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>2.217800000001444</v>
+        <v>1.648000000001048</v>
       </c>
       <c r="F133" t="n">
-        <v>0.03395097753143825</v>
+        <v>0.02615990662383791</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>26.32170000000042</v>
+        <v>23.78289999999979</v>
       </c>
       <c r="F134" t="n">
-        <v>1.843088235293942</v>
+        <v>1.654397058823698</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.03629999999993742</v>
+        <v>0.07989999999990686</v>
       </c>
       <c r="F135" t="n">
-        <v>0.012004950495019</v>
+        <v>0.02095709570956334</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,7 +4132,7 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>0.05200000000004366</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>0.0157999999999447</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>0.003053140096607699</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4240,7 +4240,7 @@
         <v>44717</v>
       </c>
       <c r="E141" t="n">
-        <v>0.02740000000001146</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>7.47609999999986</v>
+        <v>2.19890000000014</v>
       </c>
       <c r="F142" t="n">
-        <v>0.5116637579988463</v>
+        <v>0.1279232111693148</v>
       </c>
       <c r="G142" t="n">
         <v>343.8000000000002</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3721000000019558</v>
+        <v>0.2126000000047497</v>
       </c>
       <c r="F144" t="n">
-        <v>0.05848918225055641</v>
+        <v>0.01950861752866607</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>1.037800000002608</v>
+        <v>0.6604000000050292</v>
       </c>
       <c r="F145" t="n">
-        <v>0.04052300057303698</v>
+        <v>0.0225042947128024</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>1.251299999997718</v>
+        <v>1.317600000000675</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3519801980194738</v>
+        <v>0.4633663366344167</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4486,7 +4486,7 @@
         <v>0.01130000000002838</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>0.03692810457525645</v>
       </c>
       <c r="G150" t="n">
         <v>30.59999999999974</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>2.263699999998789</v>
+        <v>2.584500000000117</v>
       </c>
       <c r="F151" t="n">
-        <v>1.086422018347642</v>
+        <v>1.284678899083589</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>1.02269999999844</v>
+        <v>0.8512999999977182</v>
       </c>
       <c r="F157" t="n">
-        <v>0.05036677709398056</v>
+        <v>0.05035494557494022</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.0217000000004191</v>
+        <v>0.03340000000025611</v>
       </c>
       <c r="F164" t="n">
-        <v>0.007893175074280957</v>
+        <v>0.01192878338284497</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.2896999999997206</v>
+        <v>0.1797999999998865</v>
       </c>
       <c r="F165" t="n">
-        <v>0.176671035386393</v>
+        <v>0.05897771952827539</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01690000000003238</v>
+        <v>0.08150000000000546</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02383638928072257</v>
+        <v>0.0911142454160406</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8372000000003027</v>
+        <v>0.6130000000004656</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05470389471813921</v>
+        <v>0.03828916948284335</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>34.18979999999865</v>
+        <v>36.41310000000522</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9272015007726158</v>
+        <v>0.9794692120946087</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02229999999981374</v>
+        <v>0.01120000000810251</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001655922882503716</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08690000000060535</v>
+        <v>0.2123999999996158</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.135028607755638</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>1.930400000000372</v>
+        <v>1.038099999999395</v>
       </c>
       <c r="F12" t="n">
-        <v>0.150623911781692</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,7 +784,7 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008799999999996543</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1197000000000116</v>
+        <v>0.1412999999998647</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7340206185561574</v>
+        <v>0.7226804123701562</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7961999999999534</v>
+        <v>0.6782999999995809</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09809885931528847</v>
+        <v>0.1168250950572058</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1855999999999767</v>
+        <v>0.1236999999993714</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01650433622406555</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>1.775199999997858</v>
+        <v>1.420199999999022</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02811213177057582</v>
+        <v>0.08435223313273464</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1135,7 +1135,7 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2281000000002678</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
         <v>44696</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.3584000000000288</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>5.338297872340389</v>
       </c>
       <c r="G27" t="n">
         <v>4.70000000000006</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>3.260999999998603</v>
+        <v>2.613499999999476</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1059286146399861</v>
+        <v>0.1006856221012735</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>1.945000000001164</v>
+        <v>1.887800000002608</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1249726925184226</v>
+        <v>0.1327826324409698</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>4.631799999997019</v>
+        <v>3.157600000000093</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07426485750807599</v>
+        <v>0.05596156225519716</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04610000000002401</v>
+        <v>0.031899999999996</v>
       </c>
       <c r="F31" t="n">
-        <v>0.06755725190844822</v>
+        <v>0.054198473282376</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5591000000000349</v>
+        <v>0.5744000000006053</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1164865946381475</v>
+        <v>0.1133653461384031</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.238800000003539</v>
+        <v>1.067300000000978</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2277035236950998</v>
+        <v>0.2045767517204351</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1621,10 +1621,10 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>1.529999999993015</v>
+        <v>1.343000000005122</v>
       </c>
       <c r="F44" t="n">
-        <v>0.07525629077309166</v>
+        <v>0.08119757688825574</v>
       </c>
       <c r="G44" t="n">
         <v>858.4000000000742</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>1.25</v>
+        <v>0.55</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4357368753950427</v>
+        <v>0.07381404174581206</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>1.131200000003446</v>
+        <v>1.357400000002235</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1008597630882447</v>
+        <v>0.1584829957964047</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.002400000000034197</v>
+        <v>0.00160000000000764</v>
       </c>
       <c r="F49" t="n">
-        <v>0.004347826086977257</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>4.209799999999814</v>
+        <v>2.487099999998463</v>
       </c>
       <c r="F55" t="n">
-        <v>0.07741289844328478</v>
+        <v>0.01477020014820593</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,7 +1945,7 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>2.270000000001164</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.176299999999992</v>
+        <v>0.1733000000000175</v>
       </c>
       <c r="F57" t="n">
-        <v>1.026262626263124</v>
+        <v>0.7242424242420367</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>24.11180000000168</v>
+        <v>22.34000000000233</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1999294858737269</v>
+        <v>0.1501339768400065</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.03359999999956927</v>
+        <v>0.02239999999874271</v>
       </c>
       <c r="F65" t="n">
-        <v>0.004223227752402463</v>
+        <v>0.001407742584134154</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2242,7 +2242,7 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>1.364699999999721</v>
+        <v>1.687199999997392</v>
       </c>
       <c r="F67" t="n">
         <v>0.3217391304342767</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3913000000000466</v>
+        <v>0.4614999999990687</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0628826223185507</v>
+        <v>0.04834899975883083</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.004299999999784631</v>
+        <v>0.002100000000064029</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0007177033493041822</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.08060000000004948</v>
+        <v>0.09730000000017754</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02000909504330774</v>
+        <v>0.02423829013185347</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2380,7 +2380,7 @@
         <v>6.967800000001444</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4464777105119911</v>
+        <v>0.5122179416621168</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>3.486100000003353</v>
+        <v>2.145300000009593</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2465012064816269</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>1.024700000003213</v>
+        <v>0.2117000000027474</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00927613706085121</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.1415000000000873</v>
+        <v>0.318300000000454</v>
       </c>
       <c r="F78" t="n">
-        <v>0.004564208354907612</v>
+        <v>0.03191077875191511</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.006000000000130967</v>
+        <v>0.05959999999995489</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>0.2493723849370452</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7703000000001339</v>
+        <v>0.09299999999966531</v>
       </c>
       <c r="F87" t="n">
-        <v>0.08866666666653719</v>
+        <v>0.2213333333323354</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>7.927100000000792</v>
+        <v>5.963500000000932</v>
       </c>
       <c r="F94" t="n">
-        <v>1.695760466349524</v>
+        <v>1.464546899841164</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>5.404599999997299</v>
+        <v>2.007399999990594</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1125098083169283</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,7 +3052,7 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0.02669999999998254</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>3.391400000001886</v>
+        <v>2.780300000001444</v>
       </c>
       <c r="F98" t="n">
-        <v>0.04924554183818633</v>
+        <v>0.0461008230452651</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.01359999999999673</v>
+        <v>0.02029999999999745</v>
       </c>
       <c r="F99" t="n">
-        <v>0.06538461538438152</v>
+        <v>0.1298076923079032</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1432999999989988</v>
+        <v>0.3820999999996275</v>
       </c>
       <c r="F102" t="n">
-        <v>0.05434205536556531</v>
+        <v>0.09055745164983825</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>1.500099999998929</v>
+        <v>0.937599999998929</v>
       </c>
       <c r="F104" t="n">
-        <v>0.04900433805461445</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.09969999999993888</v>
+        <v>0.1457999999998719</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0862951807226638</v>
+        <v>0.1332831325301502</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3298,7 +3298,7 @@
         <v>0.4413999999989756</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03016988869358054</v>
+        <v>0.03447568834200487</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>3707.588700000005</v>
+        <v>26.22339999999967</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>7.912914906457711</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0181999999999789</v>
+        <v>0.0363999999999578</v>
       </c>
       <c r="F108" t="n">
-        <v>0.05449101796373818</v>
+        <v>0.1634730538923037</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3430,7 +3430,7 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>0.7248000000021421</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1168999999994412</v>
+        <v>0.03890000000101281</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.04320000000002437</v>
+        <v>0.02870000000002619</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07128712871298719</v>
+        <v>0.07079207920793584</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6261999999987893</v>
+        <v>0.6547000000020489</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1559614408940815</v>
+        <v>0.1762049720952882</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>2.171399999997811</v>
+        <v>2.613000000000466</v>
       </c>
       <c r="F117" t="n">
-        <v>0.445206093188906</v>
+        <v>0.7254928315425008</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>110.6012999999977</v>
+        <v>43.58490000000457</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>10.16913205786427</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1134000000020023</v>
+        <v>0.4082000000023981</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>0.01262703605744842</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3811,7 +3811,7 @@
         <v>232.2495999999985</v>
       </c>
       <c r="F125" t="n">
-        <v>5.142588902174382</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
         <v>4516.199999999981</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.5544000000023516</v>
+        <v>0.489199999999255</v>
       </c>
       <c r="F126" t="n">
-        <v>0.3461038961059075</v>
+        <v>0.4480519480487459</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>1.635700000007637</v>
+        <v>1.567500000004657</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02581344902412211</v>
+        <v>0.02141178597240284</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>1.648000000001048</v>
+        <v>1.383599999998114</v>
       </c>
       <c r="F133" t="n">
-        <v>0.02615990662383791</v>
+        <v>0.02430697402972633</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>23.78289999999979</v>
+        <v>11.24990000000107</v>
       </c>
       <c r="F134" t="n">
-        <v>1.654397058823698</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.07989999999990686</v>
+        <v>0.07250000000003638</v>
       </c>
       <c r="F135" t="n">
-        <v>0.02095709570956334</v>
+        <v>0.008952145214544346</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,7 +4132,7 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.05200000000004366</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>0.0157999999999447</v>
       </c>
       <c r="F139" t="n">
-        <v>0.003053140096607699</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>2.19890000000014</v>
+        <v>1.759100000000035</v>
       </c>
       <c r="F142" t="n">
-        <v>0.1279232111693148</v>
+        <v>0.3837405468295315</v>
       </c>
       <c r="G142" t="n">
         <v>343.8000000000002</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2126000000047497</v>
+        <v>0.2480999999970663</v>
       </c>
       <c r="F144" t="n">
-        <v>0.01950861752866607</v>
+        <v>0.07147048038008408</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>0.6604000000050292</v>
+        <v>0.5660999999963678</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0225042947128024</v>
+        <v>0.03152319144833181</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>1.317600000000675</v>
+        <v>0.7488000000012107</v>
       </c>
       <c r="F146" t="n">
-        <v>0.4633663366344167</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4486,7 +4486,7 @@
         <v>0.01130000000002838</v>
       </c>
       <c r="F150" t="n">
-        <v>0.03692810457525645</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
         <v>30.59999999999974</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>2.584500000000117</v>
+        <v>3.732300000000396</v>
       </c>
       <c r="F151" t="n">
-        <v>1.284678899083589</v>
+        <v>2.139449541283647</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.8512999999977182</v>
+        <v>0.7127999999996973</v>
       </c>
       <c r="F157" t="n">
-        <v>0.05035494557494022</v>
+        <v>0.03398012304783515</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.03340000000025611</v>
+        <v>0.02679999999963911</v>
       </c>
       <c r="F164" t="n">
-        <v>0.01192878338284497</v>
+        <v>0.00397626112732712</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1797999999998865</v>
+        <v>0.06500000000014552</v>
       </c>
       <c r="F165" t="n">
-        <v>0.05897771952827539</v>
+        <v>0.0262123197903976</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08150000000000546</v>
+        <v>0.1460999999999785</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0911142454160406</v>
+        <v>0.1149506346967632</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6130000000004656</v>
+        <v>0.4438999999983935</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03828916948284335</v>
+        <v>0.02619598079313809</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>36.41310000000522</v>
+        <v>36.27930000000051</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9794692120946087</v>
+        <v>1.022048112999188</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01120000000810251</v>
+        <v>0.04479999999748543</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0003311845763286229</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2123999999996158</v>
+        <v>0.4248000000006869</v>
       </c>
       <c r="F10" t="n">
-        <v>0.135028607755638</v>
+        <v>0.1350286077565632</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>1.038099999999395</v>
+        <v>2.702500000002328</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.1954439930358475</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1412999999998647</v>
+        <v>0.1226999999998952</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7226804123701562</v>
+        <v>0.5422680412369013</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6782999999995809</v>
+        <v>0.6046000000002095</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1168250950572058</v>
+        <v>0.07474651457530984</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1236999999993714</v>
+        <v>0.03090000000083819</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.004122748499111164</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>1.420199999999022</v>
+        <v>8.166300000000046</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08435223313273464</v>
+        <v>0.5623297434272864</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1162,10 +1162,10 @@
         <v>44696</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3584000000000288</v>
+        <v>0.3585000000000036</v>
       </c>
       <c r="F27" t="n">
-        <v>5.338297872340389</v>
+        <v>2.289361702127677</v>
       </c>
       <c r="G27" t="n">
         <v>4.70000000000006</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>2.613499999999476</v>
+        <v>3.677100000000792</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1006856221012735</v>
+        <v>0.155212744504941</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>1.887800000002608</v>
+        <v>2.253899999998976</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1327826324409698</v>
+        <v>0.1640223921359268</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>3.157600000000093</v>
+        <v>2.198499999998603</v>
       </c>
       <c r="F30" t="n">
-        <v>0.05596156225519716</v>
+        <v>0.03470944859144764</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.031899999999996</v>
+        <v>0.01419999999998254</v>
       </c>
       <c r="F31" t="n">
-        <v>0.054198473282376</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1297,10 +1297,10 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.07169999999999846</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.5693548387096053</v>
       </c>
       <c r="G32" t="n">
         <v>6.199999999999939</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5744000000006053</v>
+        <v>0.547400000000198</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1133653461384031</v>
+        <v>0.1056822729092931</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>13.28120000000345</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.01084184280852525</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.067300000000978</v>
+        <v>1.095900000003166</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2045767517204351</v>
+        <v>0.239287160793669</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1621,10 +1621,10 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>1.343000000005122</v>
+        <v>0.6970000000088475</v>
       </c>
       <c r="F44" t="n">
-        <v>0.08119757688825574</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>858.4000000000742</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0.55</v>
+        <v>0.3111000000004424</v>
       </c>
       <c r="F46" t="n">
-        <v>0.07381404174581206</v>
+        <v>0.1229601518028562</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>1.357400000002235</v>
+        <v>2.337699999997858</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1584829957964047</v>
+        <v>0.2881543752387294</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,7 +1756,7 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00160000000000764</v>
+        <v>0.001699999999982538</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>2.487099999998463</v>
+        <v>6.97390000000014</v>
       </c>
       <c r="F55" t="n">
-        <v>0.01477020014820593</v>
+        <v>0.1499406968125511</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1733000000000175</v>
+        <v>0.1104999999999563</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7242424242420367</v>
+        <v>0.3919191919190962</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>22.34000000000233</v>
+        <v>12.7877000000095</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1501339768400065</v>
+        <v>0.0496419449363825</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.02239999999874271</v>
+        <v>0.005599999999685678</v>
       </c>
       <c r="F65" t="n">
-        <v>0.001407742584134154</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>1.687199999997392</v>
+        <v>1.984899999998743</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3217391304342767</v>
+        <v>0.4163615560646658</v>
       </c>
       <c r="G67" t="n">
         <v>262.2000000000071</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4614999999990687</v>
+        <v>0.3010000000009313</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04834899975883083</v>
+        <v>0.02419860207315833</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.002100000000064029</v>
+        <v>0.008699999999953434</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>0.002973342447010756</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.09730000000017754</v>
+        <v>0.1113999999997759</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02423829013185347</v>
+        <v>0.02642110050015115</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>6.967800000001444</v>
+        <v>8.480799999996089</v>
       </c>
       <c r="F72" t="n">
-        <v>0.5122179416621168</v>
+        <v>0.6546505228400675</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>2.145300000009593</v>
+        <v>2.68169999999227</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>0.1848787774326951</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>0.2117000000027474</v>
+        <v>1.954700000002049</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>0.04482955043391823</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.318300000000454</v>
+        <v>0.2830000000001746</v>
       </c>
       <c r="F78" t="n">
-        <v>0.03191077875191511</v>
+        <v>0.004564208354813801</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.05959999999995489</v>
+        <v>0.08349999999991269</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2493723849370452</v>
+        <v>0.09999999999982162</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2755,7 +2755,7 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>0.7495999999984633</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.09299999999966531</v>
+        <v>0.1725999999998749</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2213333333323354</v>
+        <v>0.354000000000559</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2890,10 +2890,10 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2.54100000000326</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.06433074255052718</v>
       </c>
       <c r="G91" t="n">
         <v>3949.89999999998</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>5.963500000000932</v>
+        <v>5.636200000002281</v>
       </c>
       <c r="F94" t="n">
-        <v>1.464546899841164</v>
+        <v>1.52231054584147</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>2.007399999990594</v>
+        <v>9.110500000009779</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>0.2682939132387917</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,7 +3052,7 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>0.02669999999998254</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>2.780300000001444</v>
+        <v>1.863699999998789</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0461008230452651</v>
+        <v>0.01781207133055072</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.02029999999999745</v>
+        <v>0.02699999999999818</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1298076923079032</v>
+        <v>0.1298076923074659</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.3820999999996275</v>
+        <v>0.286600000000908</v>
       </c>
       <c r="F102" t="n">
-        <v>0.09055745164983825</v>
+        <v>0.01812665908239604</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,7 +3241,7 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>0.937599999998929</v>
+        <v>0.7501000000018394</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1457999999998719</v>
+        <v>0.1734000000000378</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1332831325301502</v>
+        <v>0.1278614457831536</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.4413999999989756</v>
+        <v>0.4119999999995343</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03447568834200487</v>
+        <v>0.02586408904515621</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>26.22339999999967</v>
+        <v>54.46399999999558</v>
       </c>
       <c r="F107" t="n">
-        <v>7.912914906457711</v>
+        <v>8.521605310801803</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0363999999999578</v>
+        <v>0.03330000000005384</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1634730538923037</v>
+        <v>0.03592814371281566</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>0.1266999999999825</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>0.0879250520471772</v>
       </c>
       <c r="G109" t="n">
         <v>144.1000000000003</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>4.325499999997556</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>0.2814313597917565</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3457,7 +3457,7 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.03890000000101281</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02870000000002619</v>
+        <v>0.02869999999998072</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07079207920793584</v>
+        <v>0.07128712871276206</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6547000000020489</v>
+        <v>0.6776000000012573</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1762049720952882</v>
+        <v>0.1560121765607121</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>2.613000000000466</v>
+        <v>3.312199999997392</v>
       </c>
       <c r="F117" t="n">
-        <v>0.7254928315425008</v>
+        <v>0.7172491039409509</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>43.58490000000457</v>
+        <v>82.65700000000069</v>
       </c>
       <c r="F119" t="n">
-        <v>10.16913205786427</v>
+        <v>9.116215585627083</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.4082000000023981</v>
+        <v>0.1814000000013039</v>
       </c>
       <c r="F122" t="n">
-        <v>0.01262703605744842</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3808,7 +3808,7 @@
         <v>44733</v>
       </c>
       <c r="E125" t="n">
-        <v>232.2495999999985</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.489199999999255</v>
+        <v>0.5519999999989522</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4480519480487459</v>
+        <v>0.4480519480534705</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>1.567500000004657</v>
+        <v>1.635700000007637</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02141178597240284</v>
+        <v>0.02816040009661079</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>1.383599999998114</v>
+        <v>1.078299999999581</v>
       </c>
       <c r="F133" t="n">
-        <v>0.02430697402972633</v>
+        <v>0.0150277210387925</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>11.24990000000107</v>
+        <v>17.86490000000049</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>1.108985294117548</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.07250000000003638</v>
+        <v>0.0217000000000553</v>
       </c>
       <c r="F135" t="n">
-        <v>0.008952145214544346</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,10 +4132,10 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>0.005799999999999273</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>0.0185897435897414</v>
       </c>
       <c r="G137" t="n">
         <v>31.19999999999976</v>
@@ -4186,7 +4186,7 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0157999999999447</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>1.759100000000035</v>
+        <v>1.759000000000015</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3837405468295315</v>
+        <v>0.1278941244910076</v>
       </c>
       <c r="G142" t="n">
         <v>343.8000000000002</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2480999999970663</v>
+        <v>0.3188999999954831</v>
       </c>
       <c r="F144" t="n">
-        <v>0.07147048038008408</v>
+        <v>0.03898056472189033</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5660999999963678</v>
+        <v>0.7076000000000932</v>
       </c>
       <c r="F145" t="n">
-        <v>0.03152319144833181</v>
+        <v>0.03600878030201069</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>0.7488000000012107</v>
+        <v>1.592499999998836</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>0.5513613861388349</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4483,7 +4483,7 @@
         <v>44734</v>
       </c>
       <c r="E150" t="n">
-        <v>0.01130000000002838</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>3.732300000000396</v>
+        <v>4.831499999998778</v>
       </c>
       <c r="F151" t="n">
-        <v>2.139449541283647</v>
+        <v>2.293119266054552</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.7127999999996973</v>
+        <v>0.5038000000000465</v>
       </c>
       <c r="F157" t="n">
-        <v>0.03398012304783515</v>
+        <v>0.02562707051582394</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.02679999999963911</v>
+        <v>0.01330000000016298</v>
       </c>
       <c r="F164" t="n">
-        <v>0.00397626112732712</v>
+        <v>0.003916913946953837</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.06500000000014552</v>
+        <v>0.05</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0262123197903976</v>
+        <v>0.039318479685358</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>
@@ -4915,7 +4915,7 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>0.0184000000001106</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>54.46399999999558</v>
+        <v>54.4640000000014</v>
       </c>
       <c r="F107" t="n">
-        <v>8.521605310801803</v>
+        <v>8.521605310803558</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1460999999999785</v>
+        <v>0.1376999999999953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1149506346967632</v>
+        <v>0.07926657263750291</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4438999999983935</v>
+        <v>0.338399999999092</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02619598079313809</v>
+        <v>0.02032722745832923</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>36.27930000000051</v>
+        <v>44.44670000000042</v>
       </c>
       <c r="F8" t="n">
-        <v>1.022048112999188</v>
+        <v>1.426738026925575</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04479999999748543</v>
+        <v>0.02240000000456348</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0003311845763286229</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4248000000006869</v>
+        <v>0.4343999999997322</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1350286077565632</v>
+        <v>0.141131595676201</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>2.702500000002328</v>
+        <v>2.582400000002235</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1954439930358475</v>
+        <v>0.1792513058617585</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.004399999999998272</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.03826086956520229</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1226999999998952</v>
+        <v>0.1087000000001353</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5422680412369013</v>
+        <v>0.5783505154654276</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6046000000002095</v>
+        <v>0.575</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07474651457530984</v>
+        <v>0.1074461343473801</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03090000000083819</v>
+        <v>0.1546000000002095</v>
       </c>
       <c r="F18" t="n">
-        <v>0.004122748499111164</v>
+        <v>0.01650433622406555</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>8.166300000000046</v>
+        <v>20.59319999999716</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5623297434272864</v>
+        <v>1.068427304402687</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1162,10 +1162,10 @@
         <v>44696</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3585000000000036</v>
+        <v>0.2688999999999851</v>
       </c>
       <c r="F27" t="n">
-        <v>2.289361702127677</v>
+        <v>3.431914893616614</v>
       </c>
       <c r="G27" t="n">
         <v>4.70000000000006</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>3.677100000000792</v>
+        <v>6.719700000000012</v>
       </c>
       <c r="F28" t="n">
-        <v>0.155212744504941</v>
+        <v>0.6916918733616926</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>2.253899999998976</v>
+        <v>2.688600000005681</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1640223921359268</v>
+        <v>0.1983888585476216</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>2.198499999998603</v>
+        <v>1.729200000001583</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03470944859144764</v>
+        <v>0.03660659050623777</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,7 +1270,7 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01419999999998254</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1297,10 +1297,10 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0.07169999999999846</v>
+        <v>0.08479999999999563</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5693548387096053</v>
+        <v>0.7983870967742087</v>
       </c>
       <c r="G32" t="n">
         <v>6.199999999999939</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.547400000000198</v>
+        <v>0.4588000000003376</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1056822729092931</v>
+        <v>0.07791116446579023</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>13.28120000000345</v>
+        <v>21.76330000000307</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01084184280852525</v>
+        <v>0.03061182507528312</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.095900000003166</v>
+        <v>1.219699999998556</v>
       </c>
       <c r="F40" t="n">
-        <v>0.239287160793669</v>
+        <v>0.2547185095176033</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1621,7 +1621,7 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6970000000088475</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3111000000004424</v>
+        <v>0.5277999999998428</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1229601518028562</v>
+        <v>0.210879190385535</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>2.337699999997858</v>
+        <v>3.393499999999767</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2881543752387294</v>
+        <v>0.360202521971782</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001699999999982538</v>
+        <v>0.0007999999999810826</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.002173913043426842</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>6.97390000000014</v>
+        <v>8.299699999997392</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1499406968125511</v>
+        <v>0.1549925871014832</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1104999999999563</v>
+        <v>0.05970000000006621</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3919191919190962</v>
+        <v>0.2111111111118528</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2053,10 +2053,10 @@
         <v>44600</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>0.03699999999998908</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>0.09487179487176674</v>
       </c>
       <c r="G60" t="n">
         <v>39.00000000000006</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>12.7877000000095</v>
+        <v>8.425600000005215</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0496419449363825</v>
+        <v>0.08223357412609537</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.005599999999685678</v>
+        <v>0.01119999999937136</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>0.002815485168268309</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>1.984899999998743</v>
+        <v>2.505899999995017</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4163615560646658</v>
+        <v>0.539359267734255</v>
       </c>
       <c r="G67" t="n">
         <v>262.2000000000071</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3010000000009313</v>
+        <v>0.250800000000163</v>
       </c>
       <c r="F69" t="n">
-        <v>0.02419860207315833</v>
+        <v>0.03624969872225167</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.008699999999953434</v>
+        <v>0.01490000000012515</v>
       </c>
       <c r="F70" t="n">
-        <v>0.002973342447010756</v>
+        <v>0.00211893369793976</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1113999999997759</v>
+        <v>0.1104999999999563</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02642110050015115</v>
+        <v>0.02382901318787004</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>8.480799999996089</v>
+        <v>10.21280000000261</v>
       </c>
       <c r="F72" t="n">
-        <v>0.6546505228400675</v>
+        <v>0.7505228398460314</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>2.68169999999227</v>
+        <v>3.486100000003353</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1848787774326951</v>
+        <v>0.2156842468122047</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>1.954700000002049</v>
+        <v>2.284999999997672</v>
       </c>
       <c r="F77" t="n">
-        <v>0.04482955043391823</v>
+        <v>0.0533651739549718</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2830000000001746</v>
+        <v>0.2476000000002387</v>
       </c>
       <c r="F78" t="n">
-        <v>0.004564208354813801</v>
+        <v>0.01824394017535931</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2620,10 +2620,10 @@
         <v>44355</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>0.04640000000072177</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>0.0007069805752130843</v>
       </c>
       <c r="G81" t="n">
         <v>1456.899999999996</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.08349999999991269</v>
+        <v>0.04169999999994616</v>
       </c>
       <c r="F83" t="n">
-        <v>0.09999999999982162</v>
+        <v>0.0744769874476487</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2755,7 +2755,7 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7495999999984633</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1725999999998749</v>
+        <v>0.159400000000096</v>
       </c>
       <c r="F87" t="n">
-        <v>0.354000000000559</v>
+        <v>0.1773333333330744</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2893,7 +2893,7 @@
         <v>2.54100000000326</v>
       </c>
       <c r="F91" t="n">
-        <v>0.06433074255052718</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>3949.89999999998</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>0.03669999999983702</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>0.09483204134324799</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>5.636200000002281</v>
+        <v>5.345300000003772</v>
       </c>
       <c r="F94" t="n">
-        <v>1.52231054584147</v>
+        <v>1.310386857446594</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>9.110500000009779</v>
+        <v>6.485499999998138</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2682939132387917</v>
+        <v>0.09520233157671479</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3052,7 +3052,7 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0.02669999999998254</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>1.863699999998789</v>
+        <v>1.130499999999302</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01781207133055072</v>
+        <v>0.02095679012347196</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.02699999999999818</v>
+        <v>0.03039999999996326</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1298076923074659</v>
+        <v>0.1624999999998753</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.286600000000908</v>
+        <v>0.1432999999989988</v>
       </c>
       <c r="F102" t="n">
-        <v>0.01812665908239604</v>
+        <v>0.03621539628316927</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7501000000018394</v>
+        <v>2.625199999997858</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>0.09800867610922889</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1734000000000378</v>
+        <v>0.2529000000000451</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1278614457831536</v>
+        <v>0.2530120481928089</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.4119999999995343</v>
+        <v>0.3531000000017229</v>
       </c>
       <c r="F106" t="n">
-        <v>0.02586408904515621</v>
+        <v>0.02584944346827733</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>54.4640000000014</v>
+        <v>46.39530000000377</v>
       </c>
       <c r="F107" t="n">
-        <v>8.521605310803558</v>
+        <v>5.478183464092597</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.03330000000005384</v>
+        <v>0.03329999999996289</v>
       </c>
       <c r="F108" t="n">
-        <v>0.03592814371281566</v>
+        <v>0.1634730538917591</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1266999999999825</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0879250520471772</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>144.1000000000003</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>4.325499999997556</v>
+        <v>2.162799999999697</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2814313597917565</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>0.07799999999988358</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>0.01118439919700073</v>
       </c>
       <c r="G112" t="n">
         <v>348.7000000000023</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02869999999998072</v>
+        <v>0.0431999999999789</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07128712871276206</v>
+        <v>0.1425742574257493</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6776000000012573</v>
+        <v>0.7173999999999069</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1560121765607121</v>
+        <v>0.196448503296495</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>3.312199999997392</v>
+        <v>3.569899999996414</v>
       </c>
       <c r="F117" t="n">
-        <v>0.7172491039409509</v>
+        <v>0.8821684587814779</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>82.65700000000069</v>
+        <v>84.45039999999571</v>
       </c>
       <c r="F119" t="n">
-        <v>9.116215585627083</v>
+        <v>10.58756416238949</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1814000000013039</v>
+        <v>0.4083000000013272</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>0.01578727551170086</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.5519999999989522</v>
+        <v>0.5294000000023515</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4480519480534705</v>
+        <v>0.4113636363659517</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>1.635700000007637</v>
+        <v>3.057199999992736</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02816040009661079</v>
+        <v>0.06423837069151407</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>1.078299999999581</v>
+        <v>0.874900000001071</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0150277210387925</v>
+        <v>0.01688430113807768</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>17.86490000000049</v>
+        <v>15.0435999999987</v>
       </c>
       <c r="F134" t="n">
-        <v>1.108985294117548</v>
+        <v>1.103308823529334</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0217000000000553</v>
+        <v>0.03629999999993742</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>0.01497524752472679</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4135,7 +4135,7 @@
         <v>0.005799999999999273</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0185897435897414</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>31.19999999999976</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>1.759000000000015</v>
+        <v>0.4397000000000844</v>
       </c>
       <c r="F142" t="n">
-        <v>0.1278941244910076</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
         <v>343.8000000000002</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3188999999954831</v>
+        <v>0.1771999999997206</v>
       </c>
       <c r="F144" t="n">
-        <v>0.03898056472189033</v>
+        <v>0.02596259625905535</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>0.7076000000000932</v>
+        <v>0.9905999999959022</v>
       </c>
       <c r="F145" t="n">
-        <v>0.03600878030201069</v>
+        <v>0.05853216262563733</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>1.592499999998836</v>
+        <v>1.829500000001281</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5513613861388349</v>
+        <v>0.5807549504956311</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4402,10 +4402,10 @@
         <v>44724</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>0.8321000000003551</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>0.2892254220458956</v>
       </c>
       <c r="G147" t="n">
         <v>201.400000000001</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>4.831499999998778</v>
+        <v>5.121600000000035</v>
       </c>
       <c r="F151" t="n">
-        <v>2.293119266054552</v>
+        <v>2.405596330275618</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.5038000000000465</v>
+        <v>0.4356999999989057</v>
       </c>
       <c r="F157" t="n">
-        <v>0.02562707051582394</v>
+        <v>0.0259228584949316</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.01330000000016298</v>
+        <v>0.01169999999983702</v>
       </c>
       <c r="F164" t="n">
-        <v>0.003916913946953837</v>
+        <v>0.003026706230991206</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.05</v>
+        <v>0.05489999999990687</v>
       </c>
       <c r="F165" t="n">
-        <v>0.039318479685358</v>
+        <v>0.03263433813889959</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>
@@ -4915,7 +4915,7 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0184000000001106</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1376999999999953</v>
+        <v>0.07869999999998072</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07926657263750291</v>
+        <v>0.03173483779970494</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.338399999999092</v>
+        <v>0.2834999999991851</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02032722745832923</v>
+        <v>0.02345722923685945</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>44.44670000000042</v>
+        <v>56.43040000000038</v>
       </c>
       <c r="F8" t="n">
-        <v>1.426738026925575</v>
+        <v>1.686835135731652</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02240000000456348</v>
+        <v>0.01119999999646097</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0001655922880782513</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4343999999997322</v>
+        <v>0.3764999999999418</v>
       </c>
       <c r="F10" t="n">
-        <v>0.141131595676201</v>
+        <v>0.09821996185714088</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>2.582400000002235</v>
+        <v>3.019899999996414</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1792513058617585</v>
+        <v>0.2589233894366296</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004399999999998272</v>
+        <v>0.01770000000000209</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03826086956520229</v>
+        <v>0.1156521739130765</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1087000000001353</v>
+        <v>0.1069000000001324</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5783505154654276</v>
+        <v>0.5237113402059451</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.575</v>
+        <v>0.6929999999993015</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1074461343473801</v>
+        <v>0.1121356147018318</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>4.146399999999266</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.4241739130435001</v>
       </c>
       <c r="G17" t="n">
         <v>517.4999999999955</v>
@@ -922,7 +922,7 @@
         <v>0.1546000000002095</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01650433622406555</v>
+        <v>0.004122748499111164</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>20.59319999999716</v>
+        <v>23.07860000000219</v>
       </c>
       <c r="F24" t="n">
-        <v>1.068427304402687</v>
+        <v>0.7591463414637925</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1162,10 +1162,10 @@
         <v>44696</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2688999999999851</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>3.431914893616614</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>4.70000000000006</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>6.719700000000012</v>
+        <v>6.8471000000005</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6916918733616926</v>
+        <v>0.6890502117361936</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>2.688600000005681</v>
+        <v>3.295000000001164</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1983888585476216</v>
+        <v>0.2499453850352558</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>1.729200000001583</v>
+        <v>1.438500000000931</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03660659050623777</v>
+        <v>0.02272033653632119</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1297,10 +1297,10 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0.08479999999999563</v>
+        <v>0.04950000000000045</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7983870967742087</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>6.199999999999939</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4588000000003376</v>
+        <v>0.499299999998766</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07791116446579023</v>
+        <v>0.1218887555017013</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>21.76330000000307</v>
+        <v>19.53109999999869</v>
       </c>
       <c r="F39" t="n">
-        <v>0.03061182507528312</v>
+        <v>0.006590057580622986</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.219699999998556</v>
+        <v>1.238799999997718</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2547185095176033</v>
+        <v>0.2470230862692305</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5277999999998428</v>
+        <v>0.5388999999995576</v>
       </c>
       <c r="F46" t="n">
-        <v>0.210879190385535</v>
+        <v>0.1581277672359278</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>3.393499999999767</v>
+        <v>4.600099999998929</v>
       </c>
       <c r="F48" t="n">
-        <v>0.360202521971782</v>
+        <v>0.5186855177681867</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0007999999999810826</v>
+        <v>0.002399999999988722</v>
       </c>
       <c r="F49" t="n">
-        <v>0.002173913043426842</v>
+        <v>0.004347826086977257</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>8.299699999997392</v>
+        <v>7.350099999998929</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1549925871014832</v>
+        <v>0.1160118606374641</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1975,7 +1975,7 @@
         <v>0.05970000000006621</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2111111111118528</v>
+        <v>0.3919191919190962</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2056,7 +2056,7 @@
         <v>0.03699999999998908</v>
       </c>
       <c r="F60" t="n">
-        <v>0.09487179487176674</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>39.00000000000006</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>8.425600000005215</v>
+        <v>14.05879999999888</v>
       </c>
       <c r="F63" t="n">
-        <v>0.08223357412609537</v>
+        <v>0.138063525392932</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2191,7 +2191,7 @@
         <v>0.01119999999937136</v>
       </c>
       <c r="F65" t="n">
-        <v>0.002815485168268309</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>2.505899999995017</v>
+        <v>2.977400000003399</v>
       </c>
       <c r="F67" t="n">
-        <v>0.539359267734255</v>
+        <v>0.5961861174691465</v>
       </c>
       <c r="G67" t="n">
         <v>262.2000000000071</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.250800000000163</v>
+        <v>0.3811999999976251</v>
       </c>
       <c r="F69" t="n">
-        <v>0.03624969872225167</v>
+        <v>0.05562786213521149</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01490000000012515</v>
+        <v>0.01310000000012224</v>
       </c>
       <c r="F70" t="n">
-        <v>0.00211893369793976</v>
+        <v>0.002358168147624933</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1104999999999563</v>
+        <v>0.0963000000003376</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02382901318787004</v>
+        <v>0.0199636198272912</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>10.21280000000261</v>
+        <v>10.51140000000014</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7505228398460314</v>
+        <v>0.6957347275728043</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>3.486100000003353</v>
+        <v>6.972299999999814</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2156842468122047</v>
+        <v>0.5854532919675073</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>2.284999999997672</v>
+        <v>1.595600000000559</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0533651739549718</v>
+        <v>0.01654982034879434</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2476000000002387</v>
+        <v>0.3182999999997264</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01824394017535931</v>
+        <v>0.01367973182054551</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2620,10 +2620,10 @@
         <v>44355</v>
       </c>
       <c r="E81" t="n">
-        <v>0.04640000000072177</v>
+        <v>0.0411999999996624</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0007069805752130843</v>
+        <v>0.00212094172553937</v>
       </c>
       <c r="G81" t="n">
         <v>1456.899999999996</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.04169999999994616</v>
+        <v>0.05959999999995489</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0744769874476487</v>
+        <v>0.1748953974893966</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.159400000000096</v>
+        <v>0.06640000000006693</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1773333333330744</v>
+        <v>0.04400000000047369</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2890,7 +2890,7 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>2.54100000000326</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.03669999999983702</v>
+        <v>0.04129999999968277</v>
       </c>
       <c r="F92" t="n">
-        <v>0.09483204134324799</v>
+        <v>0.01188630490916213</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>5.345300000003772</v>
+        <v>5.672599999996601</v>
       </c>
       <c r="F94" t="n">
-        <v>1.310386857446594</v>
+        <v>1.69576046634644</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>6.485499999998138</v>
+        <v>7.875199999997858</v>
       </c>
       <c r="F95" t="n">
-        <v>0.09520233157671479</v>
+        <v>0.3461831633228489</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>1.130499999999302</v>
+        <v>1.069399999998859</v>
       </c>
       <c r="F98" t="n">
-        <v>0.02095679012347196</v>
+        <v>0.015716735253718</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.03039999999996326</v>
+        <v>0.03369999999999891</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1624999999998753</v>
+        <v>0.1615384615385782</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1432999999989988</v>
+        <v>0.09549999999871943</v>
       </c>
       <c r="F102" t="n">
-        <v>0.03621539628316927</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>2.625199999997858</v>
+        <v>5.062899999998626</v>
       </c>
       <c r="F104" t="n">
-        <v>0.09800867610922889</v>
+        <v>0.1666074321852715</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2529000000000451</v>
+        <v>0.3710000000000946</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2530120481928089</v>
+        <v>0.3057228915663565</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.3531000000017229</v>
+        <v>0.2647999999986496</v>
       </c>
       <c r="F106" t="n">
-        <v>0.02584944346827733</v>
+        <v>0.01293204452215186</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>46.39530000000377</v>
+        <v>28.24060000000172</v>
       </c>
       <c r="F107" t="n">
-        <v>5.478183464092597</v>
+        <v>3.043421846710962</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.03329999999996289</v>
+        <v>0.04249999999992724</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1634730538917591</v>
+        <v>0.09101796407188543</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>0.3378999999998996</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>0.2344899375433026</v>
       </c>
       <c r="G109" t="n">
         <v>144.1000000000003</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>2.162799999999697</v>
+        <v>6.779899999999907</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>0.4715940143135661</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.07799999999988358</v>
+        <v>0.1168999999994412</v>
       </c>
       <c r="F112" t="n">
-        <v>0.01118439919700073</v>
+        <v>0.02234012044723226</v>
       </c>
       <c r="G112" t="n">
         <v>348.7000000000023</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0431999999999789</v>
+        <v>0.04320000000002437</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1425742574257493</v>
+        <v>0.07128712871298719</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7173999999999069</v>
+        <v>0.688900000002468</v>
       </c>
       <c r="F116" t="n">
-        <v>0.196448503296495</v>
+        <v>0.1357686453595054</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>3.569899999996414</v>
+        <v>3.735600000002887</v>
       </c>
       <c r="F117" t="n">
-        <v>0.8821684587814779</v>
+        <v>0.7914874551983321</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>84.45039999999571</v>
+        <v>117.4668999999994</v>
       </c>
       <c r="F119" t="n">
-        <v>10.58756416238949</v>
+        <v>16.81955202986531</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.4083000000013272</v>
+        <v>0.2268000000010943</v>
       </c>
       <c r="F122" t="n">
-        <v>0.01578727551170086</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.5294000000023515</v>
+        <v>0.6448000000003958</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4113636363659517</v>
+        <v>0.6353896103879624</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>3.057199999992736</v>
+        <v>6.026699999999255</v>
       </c>
       <c r="F129" t="n">
-        <v>0.06423837069151407</v>
+        <v>0.117624728850373</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>0.874900000001071</v>
+        <v>1.037700000000768</v>
       </c>
       <c r="F133" t="n">
-        <v>0.01688430113807768</v>
+        <v>0.02096585935217512</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>15.0435999999987</v>
+        <v>15.48369999999995</v>
       </c>
       <c r="F134" t="n">
-        <v>1.103308823529334</v>
+        <v>1.173705882353028</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.03629999999993742</v>
+        <v>0.1016999999999825</v>
       </c>
       <c r="F135" t="n">
-        <v>0.01497524752472679</v>
+        <v>0.02698019801982084</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,7 +4132,7 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.005799999999999273</v>
+        <v>0.0056999999999789</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>0.0157999999999447</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>0.003053140096607699</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4267,7 +4267,7 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4397000000000844</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1771999999997206</v>
+        <v>0.1949000000022352</v>
       </c>
       <c r="F144" t="n">
-        <v>0.02596259625905535</v>
+        <v>0.04550788412316322</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>0.9905999999959022</v>
+        <v>1.132199999992736</v>
       </c>
       <c r="F145" t="n">
-        <v>0.05853216262563733</v>
+        <v>0.04952280969663109</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>1.829500000001281</v>
+        <v>2.019099999999162</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5807549504956311</v>
+        <v>0.6335396039593499</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4402,10 +4402,10 @@
         <v>44724</v>
       </c>
       <c r="E147" t="n">
-        <v>0.8321000000003551</v>
+        <v>0.5825000000004366</v>
       </c>
       <c r="F147" t="n">
-        <v>0.2892254220458956</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
         <v>201.400000000001</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>5.121600000000035</v>
+        <v>5.247000000000116</v>
       </c>
       <c r="F151" t="n">
-        <v>2.405596330275618</v>
+        <v>2.408165137614256</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.4356999999989057</v>
+        <v>0.4054999999993015</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0259228584949316</v>
+        <v>0.02205395172741833</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4699,10 +4699,10 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>1.139499999996042</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>0.08072141212527605</v>
       </c>
       <c r="G158" t="n">
         <v>651.50000000001</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.01169999999983702</v>
+        <v>0.02679999999963911</v>
       </c>
       <c r="F164" t="n">
-        <v>0.003026706230991206</v>
+        <v>0.01287833827918089</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.05489999999990687</v>
+        <v>0.04490000000005238</v>
       </c>
       <c r="F165" t="n">
-        <v>0.03263433813889959</v>
+        <v>0.0262123197903976</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07869999999998072</v>
+        <v>0.03090000000001964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03173483779970494</v>
+        <v>0.01184767277860184</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2834999999991851</v>
+        <v>0.3559000000008382</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02345722923685945</v>
+        <v>0.03282945047110929</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>56.43040000000038</v>
+        <v>30.57220000000088</v>
       </c>
       <c r="F8" t="n">
-        <v>1.686835135731652</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>1812.400000000025</v>
@@ -679,7 +679,7 @@
         <v>0.01119999999646097</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001655922880782513</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3764999999999418</v>
+        <v>0.2896000000007916</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09821996185714088</v>
+        <v>0.08588684043198529</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>3.019899999996414</v>
+        <v>3.603300000005402</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2589233894366296</v>
+        <v>0.2626523505515665</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01770000000000209</v>
+        <v>0.02210000000000036</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1156521739130765</v>
+        <v>0.07652173913040458</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1069000000001324</v>
+        <v>0.1231999999999971</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5237113402059451</v>
+        <v>0.7463917525774199</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6929999999993015</v>
+        <v>0.5897999999986496</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1121356147018318</v>
+        <v>0.07474651457530984</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>4.146399999999266</v>
+        <v>3.658600000001024</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4241739130435001</v>
+        <v>0.2828019323673322</v>
       </c>
       <c r="G17" t="n">
         <v>517.4999999999955</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1546000000002095</v>
+        <v>0.06190000000060536</v>
       </c>
       <c r="F18" t="n">
-        <v>0.004122748499111164</v>
+        <v>0.004136090727120367</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>23.07860000000219</v>
+        <v>19.17300000000396</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7591463414637925</v>
+        <v>0.7591463414633315</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>6.8471000000005</v>
+        <v>5.965499999999883</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6890502117361936</v>
+        <v>0.3193587416817774</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>3.295000000001164</v>
+        <v>3.535299999994459</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2499453850352558</v>
+        <v>0.2327553249585216</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>1.438500000000931</v>
+        <v>1.321199999999954</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02272033653632119</v>
+        <v>0.03176887862431516</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.007099999999991269</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.027099236641188</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1297,7 +1297,7 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0.04950000000000045</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.499299999998766</v>
+        <v>0.6361999999993714</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1218887555017013</v>
+        <v>0.132693077231138</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>19.53109999999869</v>
+        <v>4.017799999995622</v>
       </c>
       <c r="F39" t="n">
-        <v>0.006590057580622986</v>
+        <v>0.001062851069414476</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.238799999997718</v>
+        <v>1.33410000000149</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2470230862692305</v>
+        <v>0.293317132443391</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5388999999995576</v>
+        <v>0.7</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1581277672359278</v>
+        <v>0.2494623655911382</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>4.600099999998929</v>
+        <v>2.714799999998649</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5186855177681867</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.002399999999988722</v>
+        <v>0.002400000000034197</v>
       </c>
       <c r="F49" t="n">
-        <v>0.004347826086977257</v>
+        <v>0.002173913043550415</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>7.350099999998929</v>
+        <v>6.018400000000838</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1160118606374641</v>
+        <v>0.1023387694587651</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.05970000000006621</v>
+        <v>0.05679999999993015</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3919191919190962</v>
+        <v>0.1818181818175502</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2053,7 +2053,7 @@
         <v>44600</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03699999999998908</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>14.05879999999888</v>
+        <v>18.84450000000652</v>
       </c>
       <c r="F63" t="n">
-        <v>0.138063525392932</v>
+        <v>0.1570757008321265</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.01119999999937136</v>
+        <v>0.005599999999685678</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>0.001407742584134154</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>2.977400000003399</v>
+        <v>1.563200000004144</v>
       </c>
       <c r="F67" t="n">
-        <v>0.5961861174691465</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>262.2000000000071</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3811999999976251</v>
+        <v>0.2709000000002561</v>
       </c>
       <c r="F69" t="n">
-        <v>0.05562786213521149</v>
+        <v>0.009664979513438463</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01310000000012224</v>
+        <v>0.006899999999950524</v>
       </c>
       <c r="F70" t="n">
-        <v>0.002358168147624933</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0963000000003376</v>
+        <v>0.07000000000007275</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0199636198272912</v>
+        <v>0.01186903137783576</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>10.51140000000014</v>
+        <v>11.14839999999967</v>
       </c>
       <c r="F72" t="n">
-        <v>0.6957347275728043</v>
+        <v>0.8381673087507551</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>6.972299999999814</v>
+        <v>9.117699999990872</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5854532919675073</v>
+        <v>0.4621969435824065</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>1.595600000000559</v>
+        <v>0.3777000000001863</v>
       </c>
       <c r="F77" t="n">
-        <v>0.01654982034879434</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3182999999997264</v>
+        <v>0.4243999999998778</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01367973182054551</v>
+        <v>0.03191077875191511</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2620,10 +2620,10 @@
         <v>44355</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0411999999996624</v>
+        <v>0.030899999999383</v>
       </c>
       <c r="F81" t="n">
-        <v>0.00212094172553937</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>1456.899999999996</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.05959999999995489</v>
+        <v>0.1490999999999985</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1748953974893966</v>
+        <v>0.4489539748955233</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.06640000000006693</v>
+        <v>0.03980000000010477</v>
       </c>
       <c r="F87" t="n">
-        <v>0.04400000000047369</v>
+        <v>0.08866666666653719</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2863,7 +2863,7 @@
         <v>44731</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>2.2237999999983</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.04129999999968277</v>
+        <v>0.02750000000014552</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01188630490916213</v>
+        <v>0.05917312661576161</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>5.672599999996601</v>
+        <v>6.945299999997951</v>
       </c>
       <c r="F94" t="n">
-        <v>1.69576046634644</v>
+        <v>1.984843667198338</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>7.875199999997858</v>
+        <v>12.97100000000792</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3461831633228489</v>
+        <v>0.3808093263088166</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>1.069399999998859</v>
+        <v>1.008199999999488</v>
       </c>
       <c r="F98" t="n">
-        <v>0.015716735253718</v>
+        <v>0.01885802469139475</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.03369999999999891</v>
+        <v>0.05400000000004183</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1615384615385782</v>
+        <v>0.3576923076925973</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,7 +3187,7 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.09549999999871943</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>5.062899999998626</v>
+        <v>8.063100000002304</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1666074321852715</v>
+        <v>0.2548162859980967</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3710000000000946</v>
+        <v>0.339600000000064</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3057228915663565</v>
+        <v>0.205722891566258</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2647999999986496</v>
+        <v>0.176600000000326</v>
       </c>
       <c r="F106" t="n">
-        <v>0.01293204452215186</v>
+        <v>0.01293204452300435</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>28.24060000000172</v>
+        <v>20.17189999999828</v>
       </c>
       <c r="F107" t="n">
-        <v>3.043421846710962</v>
+        <v>3.043452021725726</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.04249999999992724</v>
+        <v>0.02430000000003929</v>
       </c>
       <c r="F108" t="n">
-        <v>0.09101796407188543</v>
+        <v>0.05449101796428278</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3378999999998996</v>
+        <v>0.3590000000000145</v>
       </c>
       <c r="F109" t="n">
-        <v>0.2344899375433026</v>
+        <v>0.0146426092991776</v>
       </c>
       <c r="G109" t="n">
         <v>144.1000000000003</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>6.779899999999907</v>
+        <v>3.624199999999837</v>
       </c>
       <c r="F111" t="n">
-        <v>0.4715940143135661</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1168999999994412</v>
+        <v>0.1947000000000116</v>
       </c>
       <c r="F112" t="n">
-        <v>0.02234012044723226</v>
+        <v>0.03349584169788111</v>
       </c>
       <c r="G112" t="n">
         <v>348.7000000000023</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.04320000000002437</v>
+        <v>0.02880000000000109</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07128712871298719</v>
+        <v>0.07128712871276206</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.688900000002468</v>
+        <v>0.6718999999982771</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1357686453595054</v>
+        <v>0.1935565702690168</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>3.735600000002887</v>
+        <v>4.103600000002189</v>
       </c>
       <c r="F117" t="n">
-        <v>0.7914874551983321</v>
+        <v>1.047043010752493</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>117.4668999999994</v>
+        <v>170.9838000000047</v>
       </c>
       <c r="F119" t="n">
-        <v>16.81955202986531</v>
+        <v>23.07400839944208</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2268000000010943</v>
+        <v>0.4082999999984168</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>0.01263399693722908</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3808,7 +3808,7 @@
         <v>44733</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>188.0115000000049</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.6448000000003958</v>
+        <v>0.7451999999990221</v>
       </c>
       <c r="F126" t="n">
-        <v>0.6353896103879624</v>
+        <v>0.5743506493507385</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>6.026699999999255</v>
+        <v>10.96310000000522</v>
       </c>
       <c r="F129" t="n">
-        <v>0.117624728850373</v>
+        <v>0.2126687153532065</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>1.037700000000768</v>
+        <v>1.312399999998161</v>
       </c>
       <c r="F133" t="n">
-        <v>0.02096585935217512</v>
+        <v>0.02690399766555773</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>15.48369999999995</v>
+        <v>16.50979999999981</v>
       </c>
       <c r="F134" t="n">
-        <v>1.173705882353028</v>
+        <v>1.254205882352843</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1016999999999825</v>
+        <v>0.0871000000001004</v>
       </c>
       <c r="F135" t="n">
-        <v>0.02698019801982084</v>
+        <v>0.008952145214544346</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4132,7 +4132,7 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0056999999999789</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0157999999999447</v>
+        <v>0.07890000000006694</v>
       </c>
       <c r="F139" t="n">
-        <v>0.003053140096607699</v>
+        <v>0.01219323671499957</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4294,10 +4294,10 @@
         <v>44734</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>0.161799999998766</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>0.6014869888429841</v>
       </c>
       <c r="G143" t="n">
         <v>26.90000000000055</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1949000000022352</v>
+        <v>0.2304000000003725</v>
       </c>
       <c r="F144" t="n">
-        <v>0.04550788412316322</v>
+        <v>0.03898056472189033</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>1.132199999992736</v>
+        <v>1.603899999998976</v>
       </c>
       <c r="F145" t="n">
-        <v>0.04952280969663109</v>
+        <v>0.1035502958577653</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>2.019099999999162</v>
+        <v>2.21820000000007</v>
       </c>
       <c r="F146" t="n">
-        <v>0.6335396039593499</v>
+        <v>0.7391089108921909</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4402,7 +4402,7 @@
         <v>44724</v>
       </c>
       <c r="E147" t="n">
-        <v>0.5825000000004366</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>5.247000000000116</v>
+        <v>5.136900000000606</v>
       </c>
       <c r="F151" t="n">
-        <v>2.408165137614256</v>
+        <v>2.304587155964143</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.4054999999993015</v>
+        <v>0.2720000000001164</v>
       </c>
       <c r="F157" t="n">
-        <v>0.02205395172741833</v>
+        <v>0.01012778040700151</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4699,10 +4699,10 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>1.139499999996042</v>
+        <v>0.7010999999998603</v>
       </c>
       <c r="F158" t="n">
-        <v>0.08072141212527605</v>
+        <v>0.02690713737568765</v>
       </c>
       <c r="G158" t="n">
         <v>651.50000000001</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.02679999999963911</v>
+        <v>0.03500000000058208</v>
       </c>
       <c r="F164" t="n">
-        <v>0.01287833827918089</v>
+        <v>0.007893175074280957</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.04490000000005238</v>
+        <v>0.06500000000014552</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0262123197903976</v>
+        <v>0.05897771952827539</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03090000000001964</v>
+        <v>0.03369999999999891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01184767277860184</v>
+        <v>0.03568406205919613</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3559000000008382</v>
+        <v>0.386699999999837</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03282945047110929</v>
+        <v>0.02539569624781171</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -649,7 +649,7 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>30.57220000000088</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01119999999646097</v>
+        <v>0.03350000000791624</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.000495298361936175</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2896000000007916</v>
+        <v>0.231699999999546</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08588684043198529</v>
+        <v>0.06141131595679352</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>3.603300000005402</v>
+        <v>3.980800000001909</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2626523505515665</v>
+        <v>0.3124492164826704</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02210000000000036</v>
+        <v>0.008799999999996543</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07652173913040458</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>11.50000000000002</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1231999999999971</v>
+        <v>0.1565999999998894</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7463917525774199</v>
+        <v>0.8680412371120216</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5897999999986496</v>
+        <v>0.6339999999996507</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07474651457530984</v>
+        <v>0.1261406844106411</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>3.658600000001024</v>
+        <v>3.170900000000256</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2828019323673322</v>
+        <v>0.1885410628018913</v>
       </c>
       <c r="G17" t="n">
         <v>517.4999999999955</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06190000000060536</v>
+        <v>0.03099999999976717</v>
       </c>
       <c r="F18" t="n">
-        <v>0.004136090727120367</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>749.5000000000005</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>19.17300000000396</v>
+        <v>23.07859999999637</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7591463414633315</v>
+        <v>1.068427304402687</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>5.965499999999883</v>
+        <v>1.981500000000233</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3193587416817774</v>
+        <v>0.08021778584397551</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>3.535299999994459</v>
+        <v>3.672599999996601</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2327553249585216</v>
+        <v>0.2686919716002668</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>1.321199999999954</v>
+        <v>1.214100000000326</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03176887862431516</v>
+        <v>0.01830329525287882</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1273,7 +1273,7 @@
         <v>0.007099999999991269</v>
       </c>
       <c r="F31" t="n">
-        <v>0.027099236641188</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1297,7 +1297,7 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.0009999999999990906</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6361999999993714</v>
+        <v>0.7306000000011409</v>
       </c>
       <c r="F33" t="n">
-        <v>0.132693077231138</v>
+        <v>0.1596638655464266</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>4.017799999995622</v>
+        <v>0.5579999999958091</v>
       </c>
       <c r="F39" t="n">
-        <v>0.001062851069414476</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>52500.30000000006</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.33410000000149</v>
+        <v>1.362700000003679</v>
       </c>
       <c r="F40" t="n">
-        <v>0.293317132443391</v>
+        <v>0.2586067233701572</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7</v>
+        <v>0.7387999999999011</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2494623655911382</v>
+        <v>0.2178368121444129</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>2.714799999998649</v>
+        <v>3.318100000004051</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.6339510890340274</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.002400000000034197</v>
+        <v>0.0008000000000265572</v>
       </c>
       <c r="F49" t="n">
-        <v>0.002173913043550415</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>6.018400000000838</v>
+        <v>6.550199999997858</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1023387694587651</v>
+        <v>0.1206745737581924</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1.976299999997718</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.1499264804164732</v>
       </c>
       <c r="G56" t="n">
         <v>748.1000000000222</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.05679999999993015</v>
+        <v>0.03889999999992142</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1818181818175502</v>
+        <v>0.2111111111109341</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>18.84450000000652</v>
+        <v>22.4844000000041</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1570757008321265</v>
+        <v>0.1949480545936546</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.005599999999685678</v>
+        <v>0.02810000000026775</v>
       </c>
       <c r="F65" t="n">
-        <v>0.001407742584134154</v>
+        <v>0.00565610859743138</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2242,7 +2242,7 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>1.563200000004144</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2709000000002561</v>
+        <v>0.1906000000017229</v>
       </c>
       <c r="F69" t="n">
-        <v>0.009664979513438463</v>
+        <v>0.03627380091599457</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.006899999999950524</v>
+        <v>0.01019999999989523</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>0.003485987696478219</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.07000000000007275</v>
+        <v>0.05159999999996216</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01186903137783576</v>
+        <v>0.01159618008190195</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>11.14839999999967</v>
+        <v>16.06570000000065</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8381673087507551</v>
+        <v>1.372303247110636</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>9.117699999990872</v>
+        <v>8.045000000006985</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4621969435824065</v>
+        <v>0.4621969435837441</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,7 +2512,7 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3777000000001863</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.4243999999998778</v>
+        <v>0.6366000000001805</v>
       </c>
       <c r="F78" t="n">
-        <v>0.03191077875191511</v>
+        <v>0.03192367199590481</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2620,7 +2620,7 @@
         <v>44355</v>
       </c>
       <c r="E81" t="n">
-        <v>0.030899999999383</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1490999999999985</v>
+        <v>0.2802999999999883</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4489539748955233</v>
+        <v>0.7238493723847415</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.03980000000010477</v>
+        <v>0.03989999999976135</v>
       </c>
       <c r="F87" t="n">
-        <v>0.08866666666653719</v>
+        <v>0.04433333333266227</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2863,7 +2863,7 @@
         <v>44731</v>
       </c>
       <c r="E90" t="n">
-        <v>2.2237999999983</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2890,10 +2890,10 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2.540999999991618</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.06433074255023244</v>
       </c>
       <c r="G91" t="n">
         <v>3949.89999999998</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.02750000000014552</v>
+        <v>0.02290000000029977</v>
       </c>
       <c r="F92" t="n">
-        <v>0.05917312661576161</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>6.945299999997951</v>
+        <v>6.654400000005262</v>
       </c>
       <c r="F94" t="n">
-        <v>1.984843667198338</v>
+        <v>1.541600423954954</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>12.97100000000792</v>
+        <v>12.81659999999683</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3808093263088166</v>
+        <v>0.3375294249520897</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>1.008199999999488</v>
+        <v>1.436000000001513</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01885802469139475</v>
+        <v>0.03038751714679158</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.05400000000004183</v>
+        <v>0.04729999999999564</v>
       </c>
       <c r="F99" t="n">
-        <v>0.3576923076925973</v>
+        <v>0.09711538461505655</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>0.5254000000015366</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>0.1086841107322343</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>8.063100000002304</v>
+        <v>11.25089999999909</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2548162859980967</v>
+        <v>0.3332200909422264</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.339600000000064</v>
+        <v>0.2639999999999418</v>
       </c>
       <c r="F105" t="n">
-        <v>0.205722891566258</v>
+        <v>0.1918674698794281</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3298,7 +3298,7 @@
         <v>0.176600000000326</v>
       </c>
       <c r="F106" t="n">
-        <v>0.01293204452300435</v>
+        <v>0.01293204452215186</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>20.17189999999828</v>
+        <v>10.0859999999986</v>
       </c>
       <c r="F107" t="n">
-        <v>3.043452021725726</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.02430000000003929</v>
+        <v>0.03940000000002328</v>
       </c>
       <c r="F108" t="n">
-        <v>0.05449101796428278</v>
+        <v>0.1814371257484393</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3590000000000145</v>
+        <v>0.04220000000004802</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0146426092991776</v>
+        <v>0.01464260929905137</v>
       </c>
       <c r="G109" t="n">
         <v>144.1000000000003</v>
@@ -3430,7 +3430,7 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>3.624199999999837</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1947000000000116</v>
+        <v>0.1168000000005122</v>
       </c>
       <c r="F112" t="n">
-        <v>0.03349584169788111</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>348.7000000000023</v>
@@ -3538,7 +3538,7 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02880000000000109</v>
+        <v>0.02879999999995562</v>
       </c>
       <c r="F115" t="n">
         <v>0.07128712871276206</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6718999999982771</v>
+        <v>0.7743000000016764</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1935565702690168</v>
+        <v>0.1992897006602957</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>4.103600000002189</v>
+        <v>5.097200000000885</v>
       </c>
       <c r="F117" t="n">
-        <v>1.047043010752493</v>
+        <v>1.236648745520334</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>170.9838000000047</v>
+        <v>222.8420000000042</v>
       </c>
       <c r="F119" t="n">
-        <v>23.07400839944208</v>
+        <v>28.91899206719651</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.4082999999984168</v>
+        <v>0.1815000000002328</v>
       </c>
       <c r="F122" t="n">
-        <v>0.01263399693722908</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>1436.599999999999</v>
@@ -3808,7 +3808,7 @@
         <v>44733</v>
       </c>
       <c r="E125" t="n">
-        <v>188.0115000000049</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.7451999999990221</v>
+        <v>0.6673999999999068</v>
       </c>
       <c r="F126" t="n">
-        <v>0.5743506493507385</v>
+        <v>0.5090909090906944</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>10.96310000000522</v>
+        <v>18.01210000000428</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2126687153532065</v>
+        <v>0.3297029404674001</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>1.312399999998161</v>
+        <v>1.765100000001257</v>
       </c>
       <c r="F133" t="n">
-        <v>0.02690399766555773</v>
+        <v>0.03747811496944596</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>16.50979999999981</v>
+        <v>17.05510000000067</v>
       </c>
       <c r="F134" t="n">
-        <v>1.254205882352843</v>
+        <v>1.253897058823743</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0871000000001004</v>
+        <v>0.0217000000000553</v>
       </c>
       <c r="F135" t="n">
-        <v>0.008952145214544346</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
         <v>242.3999999999978</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.07890000000006694</v>
+        <v>0.1263000000002648</v>
       </c>
       <c r="F139" t="n">
-        <v>0.01219323671499957</v>
+        <v>0.006106280193285697</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4297,7 +4297,7 @@
         <v>0.161799999998766</v>
       </c>
       <c r="F143" t="n">
-        <v>0.6014869888429841</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>26.90000000000055</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2304000000003725</v>
+        <v>0.2480999999970663</v>
       </c>
       <c r="F144" t="n">
-        <v>0.03898056472189033</v>
+        <v>0.05199853318685982</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>1.603899999998976</v>
+        <v>2.170000000006985</v>
       </c>
       <c r="F145" t="n">
-        <v>0.1035502958577653</v>
+        <v>0.1035502958588764</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>2.21820000000007</v>
+        <v>2.113900000002468</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7391089108921909</v>
+        <v>0.5689975247529127</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>5.136900000000606</v>
+        <v>5.110400000000664</v>
       </c>
       <c r="F151" t="n">
-        <v>2.304587155964143</v>
+        <v>2.383853211008806</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.2720000000001164</v>
+        <v>0.1562000000005355</v>
       </c>
       <c r="F157" t="n">
-        <v>0.01012778040700151</v>
+        <v>0.008353052532011218</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4699,10 +4699,10 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>0.7010999999998603</v>
+        <v>0.4674999999988358</v>
       </c>
       <c r="F158" t="n">
-        <v>0.02690713737568765</v>
+        <v>0.04485034535718257</v>
       </c>
       <c r="G158" t="n">
         <v>651.50000000001</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.03500000000058208</v>
+        <v>0.0217000000004191</v>
       </c>
       <c r="F164" t="n">
-        <v>0.007893175074280957</v>
+        <v>0.002017804154282009</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.06500000000014552</v>
+        <v>0.04500000000007276</v>
       </c>
       <c r="F165" t="n">
-        <v>0.05897771952827539</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03369999999999891</v>
+        <v>0.03930000000000291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03568406205919613</v>
+        <v>0.01974612129764835</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.386699999999837</v>
+        <v>0.3581999999994878</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02539569624781171</v>
+        <v>0.02852569802582434</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03350000000791624</v>
+        <v>0.06709999999729917</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000495298361936175</v>
+        <v>0.0004967768642347538</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.231699999999546</v>
+        <v>0.2607000000003609</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06141131595679352</v>
+        <v>0.1043229497777038</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>3.980800000001909</v>
+        <v>5.739599999994971</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3124492164826704</v>
+        <v>0.5178467788732593</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,7 +784,7 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008799999999996543</v>
+        <v>0.004400000000009641</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1565999999998894</v>
+        <v>0.1962999999999738</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8680412371120216</v>
+        <v>1.155670103093718</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6339999999996507</v>
+        <v>0.7668000000005122</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1261406844106411</v>
+        <v>0.1168250950572058</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>3.170900000000256</v>
+        <v>4.146499999999651</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1885410628018913</v>
+        <v>0.6127149758453913</v>
       </c>
       <c r="G17" t="n">
         <v>517.4999999999955</v>
@@ -919,7 +919,7 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03099999999976717</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>23.07859999999637</v>
+        <v>28.04940000000061</v>
       </c>
       <c r="F24" t="n">
-        <v>1.068427304402687</v>
+        <v>1.152779537535883</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>1.981500000000233</v>
+        <v>0.3978000000002794</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08021778584397551</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>495.900000000006</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>3.672599999996601</v>
+        <v>4.496299999998882</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2686919716002668</v>
+        <v>0.345234844347793</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>1.214100000000326</v>
+        <v>0.734599999996135</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01830329525287882</v>
+        <v>0.01199323627663546</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.007099999999991269</v>
+        <v>0.003600000000005821</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.01374045801528937</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1297,7 +1297,7 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0009999999999990906</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7306000000011409</v>
+        <v>0.9099000000001979</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1596638655464266</v>
+        <v>0.2044417767105519</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1486,7 +1486,7 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5579999999958091</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.362700000003679</v>
+        <v>1.553299999999581</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2586067233701572</v>
+        <v>0.3705143782902514</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7387999999999011</v>
+        <v>0.9166000000004715</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2178368121444129</v>
+        <v>0.3619228336496908</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1732,7 +1732,7 @@
         <v>3.318100000004051</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6339510890340274</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>523.3999999999924</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0008000000000265572</v>
+        <v>0.0007999999999810826</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.002173913043426842</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>6.550199999997858</v>
+        <v>7.616800000000512</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1206745737581924</v>
+        <v>0.1514232765012957</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>1.976299999997718</v>
+        <v>1.121599999995669</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1499264804164732</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>748.1000000000222</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.03889999999992142</v>
+        <v>0.02390000000004875</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2111111111109341</v>
+        <v>0.03030303030369061</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>22.4844000000041</v>
+        <v>31.03519999999553</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1949480545936546</v>
+        <v>0.2910650767036252</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.02810000000026775</v>
+        <v>0.02250000000058208</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00565610859743138</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>397.8000000000009</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1906000000017229</v>
+        <v>0.2106999999989057</v>
       </c>
       <c r="F69" t="n">
-        <v>0.03627380091599457</v>
+        <v>0.01450952036597695</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01019999999989523</v>
+        <v>0.03300000000017463</v>
       </c>
       <c r="F70" t="n">
-        <v>0.003485987696478219</v>
+        <v>0.007792207792303312</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.05159999999996216</v>
+        <v>0.03709999999991851</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01159618008190195</v>
+        <v>0.005275125056760747</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>16.06570000000065</v>
+        <v>18.83300000000163</v>
       </c>
       <c r="F72" t="n">
-        <v>1.372303247110636</v>
+        <v>1.218918547055786</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>8.045000000006985</v>
+        <v>9.117700000002515</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4621969435837441</v>
+        <v>0.5854532919675073</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>4.700400000001537</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>0.1131846463938544</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2542,7 +2542,7 @@
         <v>0.6366000000001805</v>
       </c>
       <c r="F78" t="n">
-        <v>0.03192367199590481</v>
+        <v>0.03191077875191511</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2802999999999883</v>
+        <v>0.4056000000000495</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7238493723847415</v>
+        <v>0.9732217573225478</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.03989999999976135</v>
+        <v>0.03980000000010477</v>
       </c>
       <c r="F87" t="n">
-        <v>0.04433333333266227</v>
+        <v>0.08833333333434862</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2893,7 +2893,7 @@
         <v>2.540999999991618</v>
       </c>
       <c r="F91" t="n">
-        <v>0.06433074255023244</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>3949.89999999998</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.02290000000029977</v>
+        <v>0.05039999999971769</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>0.1302325581388052</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>6.654400000005262</v>
+        <v>5.745299999997951</v>
       </c>
       <c r="F94" t="n">
-        <v>1.541600423954954</v>
+        <v>1.503073661894974</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>12.81659999999683</v>
+        <v>16.98569999999599</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3375294249520897</v>
+        <v>0.6144770765609882</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>1.436000000001513</v>
+        <v>1.34429999999993</v>
       </c>
       <c r="F98" t="n">
-        <v>0.03038751714679158</v>
+        <v>0.01571330589847352</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.04729999999999564</v>
+        <v>0.02019999999997708</v>
       </c>
       <c r="F99" t="n">
-        <v>0.09711538461505655</v>
+        <v>0.09711538461549379</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.5254000000015366</v>
+        <v>0.4777000000001863</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1086841107322343</v>
+        <v>0.07246871444796135</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>11.25089999999909</v>
+        <v>13.50099999999802</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3332200909422264</v>
+        <v>0.3724193801286017</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2639999999999418</v>
+        <v>0.2436999999999898</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1918674698794281</v>
+        <v>0.1751506024097045</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.176600000000326</v>
+        <v>0.2353999999992084</v>
       </c>
       <c r="F106" t="n">
-        <v>0.01293204452215186</v>
+        <v>0.02154364381985301</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>10.0859999999986</v>
+        <v>16.1375</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>3.043452021725726</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.03940000000002328</v>
+        <v>0.04250000000001819</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1814371257484393</v>
+        <v>0.0730538922157499</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0.04220000000004802</v>
+        <v>0.02109999999993306</v>
       </c>
       <c r="F109" t="n">
-        <v>0.01464260929905137</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>144.1000000000003</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>11.34120000000112</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>0.7932856213403493</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3457,7 +3457,7 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1168000000005122</v>
+        <v>0.2726999999998952</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3484,10 +3484,10 @@
         <v>44696</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>0.003800000000001092</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>0.0690909090909293</v>
       </c>
       <c r="G113" t="n">
         <v>5.499999999999972</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02879999999995562</v>
+        <v>0.0431999999999789</v>
       </c>
       <c r="F115" t="n">
-        <v>0.07128712871276206</v>
+        <v>0.1425742574257493</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7743000000016764</v>
+        <v>1.007699999999022</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1992897006602957</v>
+        <v>0.2773211567710139</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>5.097200000000885</v>
+        <v>6.127700000000186</v>
       </c>
       <c r="F117" t="n">
-        <v>1.236648745520334</v>
+        <v>1.508736559139283</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>222.8420000000042</v>
+        <v>220.932699999999</v>
       </c>
       <c r="F119" t="n">
-        <v>28.91899206719651</v>
+        <v>22.62853476434986</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3727,7 +3727,7 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1815000000002328</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.6673999999999068</v>
+        <v>0.7426000000006752</v>
       </c>
       <c r="F126" t="n">
-        <v>0.5090909090906944</v>
+        <v>0.6964285714299108</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>18.01210000000428</v>
+        <v>26.65789999999106</v>
       </c>
       <c r="F129" t="n">
-        <v>0.3297029404674001</v>
+        <v>0.474611352132856</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>1.765100000001257</v>
+        <v>2.212700000000768</v>
       </c>
       <c r="F133" t="n">
-        <v>0.03747811496944596</v>
+        <v>0.04323023052226592</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>17.05510000000067</v>
+        <v>16.6122000000003</v>
       </c>
       <c r="F134" t="n">
-        <v>1.253897058823743</v>
+        <v>1.189073529411611</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,7 +4078,7 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0217000000000553</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -4132,10 +4132,10 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>0.06349999999993088</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>0.1108974358972922</v>
       </c>
       <c r="G137" t="n">
         <v>31.19999999999976</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1263000000002648</v>
+        <v>0.09470000000001164</v>
       </c>
       <c r="F139" t="n">
-        <v>0.006106280193285697</v>
+        <v>0.006106280193215398</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4294,7 +4294,7 @@
         <v>44734</v>
       </c>
       <c r="E143" t="n">
-        <v>0.161799999998766</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2480999999970663</v>
+        <v>0.3367000000027474</v>
       </c>
       <c r="F144" t="n">
-        <v>0.05199853318685982</v>
+        <v>0.07147048038221858</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4351,7 +4351,7 @@
         <v>2.170000000006985</v>
       </c>
       <c r="F145" t="n">
-        <v>0.1035502958588764</v>
+        <v>0.1035502958577653</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>2.113900000002468</v>
+        <v>2.028500000000349</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5689975247529127</v>
+        <v>0.6862623762374138</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>5.110400000000664</v>
+        <v>6.450699999999779</v>
       </c>
       <c r="F151" t="n">
-        <v>2.383853211008806</v>
+        <v>3.534220183486231</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4645,7 +4645,7 @@
         <v>44699</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>0.002100000000018554</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.1562000000005355</v>
+        <v>0.1334999999991851</v>
       </c>
       <c r="F157" t="n">
-        <v>0.008353052532011218</v>
+        <v>0.007442025555918874</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4699,7 +4699,7 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>0.4674999999988358</v>
+        <v>0.6135000000009313</v>
       </c>
       <c r="F158" t="n">
         <v>0.04485034535718257</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.0217000000004191</v>
+        <v>0.018399999999383</v>
       </c>
       <c r="F164" t="n">
-        <v>0.002017804154282009</v>
+        <v>0.006943620177945043</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.04500000000007276</v>
+        <v>0.03989999999976135</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>0.05229357798134018</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03930000000000291</v>
+        <v>0.01400000000003274</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01974612129764835</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>70.90000000000032</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3581999999994878</v>
+        <v>0.1603999999992084</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02852569802582434</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>562.2999999999934</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06709999999729917</v>
+        <v>0.05589999998919666</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0004967768642347538</v>
+        <v>0.0003297060736858034</v>
       </c>
       <c r="G9" t="n">
         <v>6763.600000000224</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2607000000003609</v>
+        <v>0.3281999999991967</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1043229497777038</v>
+        <v>0.1043229497767787</v>
       </c>
       <c r="G10" t="n">
         <v>157.2999999999979</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>5.739599999994971</v>
+        <v>9.085499999998138</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5178467788732593</v>
+        <v>0.8004207777138516</v>
       </c>
       <c r="G12" t="n">
         <v>689.1999999999825</v>
@@ -784,7 +784,7 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004400000000009641</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1962999999999738</v>
+        <v>0.1886000000000422</v>
       </c>
       <c r="F14" t="n">
-        <v>1.155670103093718</v>
+        <v>0.7886597938137645</v>
       </c>
       <c r="G14" t="n">
         <v>9.700000000000841</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7668000000005122</v>
+        <v>0.7225000000005821</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1168250950572058</v>
+        <v>0.1121039290240977</v>
       </c>
       <c r="G15" t="n">
         <v>315.5999999999949</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>4.146499999999651</v>
+        <v>6.829400000000897</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6127149758453913</v>
+        <v>0.7069758454108322</v>
       </c>
       <c r="G17" t="n">
         <v>517.4999999999955</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>28.04940000000061</v>
+        <v>14.55730000000331</v>
       </c>
       <c r="F24" t="n">
-        <v>1.152779537535883</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>1262.800000000016</v>
@@ -1189,7 +1189,7 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3978000000002794</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>4.496299999998882</v>
+        <v>5.194200000003912</v>
       </c>
       <c r="F29" t="n">
-        <v>0.345234844347793</v>
+        <v>0.3639677771710304</v>
       </c>
       <c r="G29" t="n">
         <v>732.4000000000069</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>0.734599999996135</v>
+        <v>0.2907999999995809</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01199323627663546</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>2424.700000000007</v>
@@ -1273,7 +1273,7 @@
         <v>0.003600000000005821</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01374045801528937</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>26.20000000000005</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9099000000001979</v>
+        <v>0.5108999999996741</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2044417767105519</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>249.9000000000024</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>1.553299999999581</v>
+        <v>2.401399999996647</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3705143782902514</v>
+        <v>0.6021061158355476</v>
       </c>
       <c r="G40" t="n">
         <v>246.9000000000051</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9166000000004715</v>
+        <v>0.5722000000001571</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3619228336496908</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>158.0999999999989</v>
@@ -1729,7 +1729,7 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>3.318100000004051</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0.0007999999999810826</v>
       </c>
       <c r="F49" t="n">
-        <v>0.002173913043426842</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>36.80000000000021</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>7.616800000000512</v>
+        <v>7.926300000003539</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1514232765012957</v>
+        <v>0.1423610081541306</v>
       </c>
       <c r="G55" t="n">
         <v>2698.000000000047</v>
@@ -1945,7 +1945,7 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>1.121599999995669</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.02390000000004875</v>
+        <v>0.003000000000065484</v>
       </c>
       <c r="F57" t="n">
-        <v>0.03030303030369061</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>9.900000000000375</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>31.03519999999553</v>
+        <v>38.90239999999758</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2910650767036252</v>
+        <v>0.3185279784383836</v>
       </c>
       <c r="G63" t="n">
         <v>6381.700000000001</v>
@@ -2188,7 +2188,7 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.02250000000058208</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2106999999989057</v>
+        <v>0.1505000000004657</v>
       </c>
       <c r="F69" t="n">
-        <v>0.01450952036597695</v>
+        <v>0.02176428055001763</v>
       </c>
       <c r="G69" t="n">
         <v>414.9000000000115</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.03300000000017463</v>
+        <v>0.0228000000002794</v>
       </c>
       <c r="F70" t="n">
-        <v>0.007792207792303312</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>292.5999999999988</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.03709999999991851</v>
+        <v>0.01430000000000291</v>
       </c>
       <c r="F71" t="n">
-        <v>0.005275125056760747</v>
+        <v>0.001227830832281182</v>
       </c>
       <c r="G71" t="n">
         <v>219.8999999999955</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>18.83300000000163</v>
+        <v>21.69980000000214</v>
       </c>
       <c r="F72" t="n">
-        <v>1.218918547055786</v>
+        <v>1.76674463401219</v>
       </c>
       <c r="G72" t="n">
         <v>726.8000000000029</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>9.117700000002515</v>
+        <v>5.095199999993201</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5854532919675073</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>870.2999999999975</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>4.700400000001537</v>
+        <v>3.429999999998836</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1131846463938544</v>
+        <v>0.03710892997976833</v>
       </c>
       <c r="G77" t="n">
         <v>2282.200000000012</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6366000000001805</v>
+        <v>0.2474999999998545</v>
       </c>
       <c r="F78" t="n">
-        <v>0.03191077875191511</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>775.6000000000029</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4056000000000495</v>
+        <v>0.4890000000001237</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9732217573225478</v>
+        <v>1.072803347280443</v>
       </c>
       <c r="G83" t="n">
         <v>23.90000000000043</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.03980000000010477</v>
+        <v>0.02650000000030559</v>
       </c>
       <c r="F87" t="n">
-        <v>0.08833333333434862</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2890,10 +2890,10 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>2.540999999991618</v>
+        <v>2.54100000000326</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.06433074255052718</v>
       </c>
       <c r="G91" t="n">
         <v>3949.89999999998</v>
@@ -2920,7 +2920,7 @@
         <v>0.05039999999971769</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1302325581388052</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>38.70000000000005</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>5.745299999997951</v>
+        <v>6.654399999999441</v>
       </c>
       <c r="F94" t="n">
-        <v>1.503073661894974</v>
+        <v>2.023370429255233</v>
       </c>
       <c r="G94" t="n">
         <v>188.6999999999716</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>16.98569999999599</v>
+        <v>33.50829999999841</v>
       </c>
       <c r="F95" t="n">
-        <v>0.6144770765609882</v>
+        <v>1.263580316107944</v>
       </c>
       <c r="G95" t="n">
         <v>1784.199999999964</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>1.34429999999993</v>
+        <v>1.099899999998161</v>
       </c>
       <c r="F98" t="n">
-        <v>0.01571330589847352</v>
+        <v>0.02200617283946066</v>
       </c>
       <c r="G98" t="n">
         <v>2916</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.02019999999997708</v>
+        <v>0.01010000000001128</v>
       </c>
       <c r="F99" t="n">
-        <v>0.09711538461549379</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>10.39999999999992</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.4777000000001863</v>
+        <v>0.1910999999992782</v>
       </c>
       <c r="F102" t="n">
-        <v>0.07246871444796135</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
         <v>263.7000000000057</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>13.50099999999802</v>
+        <v>21.37660000000033</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3724193801286017</v>
+        <v>0.7448439868290389</v>
       </c>
       <c r="G104" t="n">
         <v>1913.299999999981</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2436999999999898</v>
+        <v>0.2510000000000218</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1751506024097045</v>
+        <v>0.2028614457830905</v>
       </c>
       <c r="G105" t="n">
         <v>66.40000000000157</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2353999999992084</v>
+        <v>0.1471000000019558</v>
       </c>
       <c r="F106" t="n">
-        <v>0.02154364381985301</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>682.7999999999975</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>16.1375</v>
+        <v>10.0859999999986</v>
       </c>
       <c r="F107" t="n">
-        <v>3.043452021725726</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
         <v>331.3999999999851</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.04250000000001819</v>
+        <v>0.01220000000002983</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0730538922157499</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>16.69999999999945</v>
@@ -3376,7 +3376,7 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0.02109999999993306</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>11.34120000000112</v>
+        <v>6.096400000000722</v>
       </c>
       <c r="F111" t="n">
-        <v>0.7932856213403493</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>768.5000000000173</v>
@@ -3457,7 +3457,7 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.2726999999998952</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3487,7 +3487,7 @@
         <v>0.003800000000001092</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0690909090909293</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>5.499999999999972</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0431999999999789</v>
+        <v>0.02880000000000109</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1425742574257493</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
         <v>20.19999999999982</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>1.007699999999022</v>
+        <v>1.360800000000745</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2773211567710139</v>
+        <v>0.4130898021334725</v>
       </c>
       <c r="G116" t="n">
         <v>197.1000000000004</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>6.127700000000186</v>
+        <v>8.023099999997067</v>
       </c>
       <c r="F117" t="n">
-        <v>1.508736559139283</v>
+        <v>2.085842293906044</v>
       </c>
       <c r="G117" t="n">
         <v>223.1999999999971</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>220.932699999999</v>
+        <v>190.9054000000004</v>
       </c>
       <c r="F119" t="n">
-        <v>22.62853476434986</v>
+        <v>21.91308912739254</v>
       </c>
       <c r="G119" t="n">
         <v>428.5999999999831</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>0.7426000000006752</v>
+        <v>1.068799999999464</v>
       </c>
       <c r="F126" t="n">
-        <v>0.6964285714299108</v>
+        <v>1.038636363634196</v>
       </c>
       <c r="G126" t="n">
         <v>61.59999999999854</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>26.65789999999106</v>
+        <v>37.36790000000038</v>
       </c>
       <c r="F129" t="n">
-        <v>0.474611352132856</v>
+        <v>0.6511990841168537</v>
       </c>
       <c r="G129" t="n">
         <v>3319.200000000001</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>2.212700000000768</v>
+        <v>2.385599999999977</v>
       </c>
       <c r="F133" t="n">
-        <v>0.04323023052226592</v>
+        <v>0.04378465129856796</v>
       </c>
       <c r="G133" t="n">
         <v>2741.599999999994</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>16.6122000000003</v>
+        <v>13.72999999999884</v>
       </c>
       <c r="F134" t="n">
-        <v>1.189073529411611</v>
+        <v>0.8300441176470541</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4132,10 +4132,10 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.06349999999993088</v>
+        <v>0.04619999999995343</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1108974358972922</v>
+        <v>0.0371794871794828</v>
       </c>
       <c r="G137" t="n">
         <v>31.19999999999976</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.09470000000001164</v>
+        <v>0.0315999999998894</v>
       </c>
       <c r="F139" t="n">
-        <v>0.006106280193215398</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>517.4999999999955</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3367000000027474</v>
+        <v>0.3721000000019558</v>
       </c>
       <c r="F144" t="n">
-        <v>0.07147048038221858</v>
+        <v>0.06497983131638749</v>
       </c>
       <c r="G144" t="n">
         <v>272.6999999998952</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>2.170000000006985</v>
+        <v>2.641699999989942</v>
       </c>
       <c r="F145" t="n">
-        <v>0.1035502958577653</v>
+        <v>0.1485684290887822</v>
       </c>
       <c r="G145" t="n">
         <v>1047.800000000007</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>2.028500000000349</v>
+        <v>1.108999999999651</v>
       </c>
       <c r="F146" t="n">
-        <v>0.6862623762374138</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
         <v>161.5999999999985</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>6.450699999999779</v>
+        <v>7.870600000000559</v>
       </c>
       <c r="F151" t="n">
-        <v>3.534220183486231</v>
+        <v>3.686513761468199</v>
       </c>
       <c r="G151" t="n">
         <v>109.0000000000032</v>
@@ -4645,7 +4645,7 @@
         <v>44699</v>
       </c>
       <c r="E156" t="n">
-        <v>0.002100000000018554</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.1334999999991851</v>
+        <v>0.100700000001234</v>
       </c>
       <c r="F157" t="n">
-        <v>0.007442025555918874</v>
+        <v>0.00447231424545761</v>
       </c>
       <c r="G157" t="n">
         <v>845.1999999999998</v>
@@ -4699,10 +4699,10 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>0.6135000000009313</v>
+        <v>0.2922000000020489</v>
       </c>
       <c r="F158" t="n">
-        <v>0.04485034535718257</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
         <v>651.50000000001</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.018399999999383</v>
+        <v>0.01169999999983702</v>
       </c>
       <c r="F164" t="n">
-        <v>0.006943620177945043</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
         <v>168.4999999999945</v>
@@ -4891,7 +4891,7 @@
         <v>0.03989999999976135</v>
       </c>
       <c r="F165" t="n">
-        <v>0.05229357798134018</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>76.29999999999768</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,13 +487,13 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01400000000003274</v>
+        <v>-0.3150000000000091</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.2267605633802993</v>
       </c>
       <c r="G2" t="n">
-        <v>70.90000000000032</v>
+        <v>71.00000000000009</v>
       </c>
     </row>
     <row r="3">
@@ -514,13 +514,13 @@
         <v>44734</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3.335000000000582</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.815217391303888</v>
       </c>
       <c r="G3" t="n">
-        <v>91.89999999999827</v>
+        <v>92.00000000000728</v>
       </c>
     </row>
     <row r="4">
@@ -541,13 +541,13 @@
         <v>44609</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-26.73999999999069</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.207839562443048</v>
       </c>
       <c r="G4" t="n">
-        <v>1097.000000000025</v>
+        <v>1096.99999999998</v>
       </c>
     </row>
     <row r="5">
@@ -568,13 +568,13 @@
         <v>44735</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-10.87900000000081</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.02283206204457414</v>
       </c>
       <c r="G5" t="n">
-        <v>23467.39999999991</v>
+        <v>23466.99999999983</v>
       </c>
     </row>
     <row r="6">
@@ -595,13 +595,13 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1603999999992084</v>
+        <v>-2.332999999998719</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.2087033747779753</v>
       </c>
       <c r="G6" t="n">
-        <v>562.2999999999934</v>
+        <v>562.9999999999995</v>
       </c>
     </row>
     <row r="7">
@@ -622,10 +622,10 @@
         <v>44711</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3.487000000002445</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.5722826086963699</v>
       </c>
       <c r="G7" t="n">
         <v>368.0000000000064</v>
@@ -649,13 +649,13 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-16.625</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.4586092715230531</v>
       </c>
       <c r="G8" t="n">
-        <v>1812.400000000025</v>
+        <v>1811.999999999989</v>
       </c>
     </row>
     <row r="9">
@@ -676,13 +676,13 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05589999998919666</v>
+        <v>2.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0003297060736858034</v>
+        <v>0.01700428803785277</v>
       </c>
       <c r="G9" t="n">
-        <v>6763.600000000224</v>
+        <v>6763.000000000102</v>
       </c>
     </row>
     <row r="10">
@@ -703,13 +703,13 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3281999999991967</v>
+        <v>-1.480999999999767</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1043229497767787</v>
+        <v>-0.5840764331209316</v>
       </c>
       <c r="G10" t="n">
-        <v>157.2999999999979</v>
+        <v>156.9999999999936</v>
       </c>
     </row>
     <row r="11">
@@ -730,13 +730,13 @@
         <v>44632</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0.3640000000000327</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0.1381679389312933</v>
       </c>
       <c r="G11" t="n">
-        <v>131.3999999999993</v>
+        <v>131.0000000000002</v>
       </c>
     </row>
     <row r="12">
@@ -757,13 +757,13 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>9.085499999998138</v>
+        <v>19.75</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8004207777138516</v>
+        <v>1.718577648765988</v>
       </c>
       <c r="G12" t="n">
-        <v>689.1999999999825</v>
+        <v>688.9999999999873</v>
       </c>
     </row>
     <row r="13">
@@ -784,13 +784,13 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.0759999999999991</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.05000000000004959</v>
       </c>
       <c r="G13" t="n">
-        <v>11.50000000000002</v>
+        <v>11.99999999999992</v>
       </c>
     </row>
     <row r="14">
@@ -811,13 +811,13 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1886000000000422</v>
+        <v>-0.4260000000000218</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7886597938137645</v>
+        <v>-2.190000000000634</v>
       </c>
       <c r="G14" t="n">
-        <v>9.700000000000841</v>
+        <v>9.999999999999432</v>
       </c>
     </row>
     <row r="15">
@@ -838,13 +838,13 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7225000000005821</v>
+        <v>5.575</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1121039290240977</v>
+        <v>0.9117088607593964</v>
       </c>
       <c r="G15" t="n">
-        <v>315.5999999999949</v>
+        <v>316.0000000000082</v>
       </c>
     </row>
     <row r="16">
@@ -865,13 +865,13 @@
         <v>44735</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-37.5820000000007</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.6300840336134844</v>
       </c>
       <c r="G16" t="n">
-        <v>2975.399999999991</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="17">
@@ -892,13 +892,13 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>6.829400000000897</v>
+        <v>51.1929999999993</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7069758454108322</v>
+        <v>4.999032882011589</v>
       </c>
       <c r="G17" t="n">
-        <v>517.4999999999955</v>
+        <v>516.9999999999959</v>
       </c>
     </row>
     <row r="18">
@@ -919,13 +919,13 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3.952000000000408</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.2790387182909767</v>
       </c>
       <c r="G18" t="n">
-        <v>749.5000000000005</v>
+        <v>749.0000000000009</v>
       </c>
     </row>
     <row r="19">
@@ -946,13 +946,13 @@
         <v>44688</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2.745999999999185</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.2886554621846789</v>
       </c>
       <c r="G19" t="n">
-        <v>475.4000000000133</v>
+        <v>475.9999999999991</v>
       </c>
     </row>
     <row r="20">
@@ -973,13 +973,13 @@
         <v>44655</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-8.976999999998952</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.4124763705102568</v>
       </c>
       <c r="G20" t="n">
-        <v>1057.7</v>
+        <v>1057.999999999993</v>
       </c>
     </row>
     <row r="21">
@@ -1000,13 +1000,13 @@
         <v>44720</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1.426000000000931</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.005063467708194528</v>
       </c>
       <c r="G21" t="n">
-        <v>14338.3</v>
+        <v>14338</v>
       </c>
     </row>
     <row r="22">
@@ -1027,13 +1027,13 @@
         <v>44729</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-5.075</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0.6958791208791605</v>
       </c>
       <c r="G22" t="n">
-        <v>363.7</v>
+        <v>364.0000000000043</v>
       </c>
     </row>
     <row r="23">
@@ -1054,13 +1054,13 @@
         <v>44607</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-2.614000000001397</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0.1431868131868</v>
       </c>
       <c r="G23" t="n">
-        <v>910.3000000000009</v>
+        <v>910.0000000000023</v>
       </c>
     </row>
     <row r="24">
@@ -1081,13 +1081,13 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>14.55730000000331</v>
+        <v>-0.771999999997206</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0.03095803642101627</v>
       </c>
       <c r="G24" t="n">
-        <v>1262.800000000016</v>
+        <v>1263.000000000011</v>
       </c>
     </row>
     <row r="25">
@@ -1108,13 +1108,13 @@
         <v>44619</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-1.977999999999884</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0.01309066843150151</v>
       </c>
       <c r="G25" t="n">
-        <v>7555.500000000029</v>
+        <v>7555.000000000018</v>
       </c>
     </row>
     <row r="26">
@@ -1135,13 +1135,13 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-8.170000000001163</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0.1163065843622175</v>
       </c>
       <c r="G26" t="n">
-        <v>1943.100000000004</v>
+        <v>1944.000000000005</v>
       </c>
     </row>
     <row r="27">
@@ -1162,13 +1162,13 @@
         <v>44696</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0.3609999999999672</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-4.275000000000182</v>
       </c>
       <c r="G27" t="n">
-        <v>4.70000000000006</v>
+        <v>3.999999999999915</v>
       </c>
     </row>
     <row r="28">
@@ -1189,13 +1189,13 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-0.4500000000001581</v>
       </c>
       <c r="G28" t="n">
-        <v>495.900000000006</v>
+        <v>495.9999999999809</v>
       </c>
     </row>
     <row r="29">
@@ -1216,13 +1216,13 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>5.194200000003912</v>
+        <v>0.1540000000037253</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3639677771710304</v>
+        <v>0.08840381991868548</v>
       </c>
       <c r="G29" t="n">
-        <v>732.4000000000069</v>
+        <v>732.9999999999927</v>
       </c>
     </row>
     <row r="30">
@@ -1243,13 +1243,13 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2907999999995809</v>
+        <v>-4.503999999997904</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.0888613861385274</v>
       </c>
       <c r="G30" t="n">
-        <v>2424.700000000007</v>
+        <v>2424.000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1270,13 +1270,13 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003600000000005821</v>
+        <v>-0.2579999999999927</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-0.4846153846152841</v>
       </c>
       <c r="G31" t="n">
-        <v>26.20000000000005</v>
+        <v>26.00000000000051</v>
       </c>
     </row>
     <row r="32">
@@ -1297,13 +1297,13 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-0.09500000000000455</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>3.149999999999951</v>
       </c>
       <c r="G32" t="n">
-        <v>6.199999999999939</v>
+        <v>6.00000000000005</v>
       </c>
     </row>
     <row r="33">
@@ -1324,13 +1324,13 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5108999999996741</v>
+        <v>-1.941999999999825</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-0.3455999999999767</v>
       </c>
       <c r="G33" t="n">
-        <v>249.9000000000024</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34">
@@ -1351,13 +1351,13 @@
         <v>44175</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-2.208000000000175</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-0.2859740259738899</v>
       </c>
       <c r="G34" t="n">
-        <v>385.9</v>
+        <v>385</v>
       </c>
     </row>
     <row r="35">
@@ -1378,13 +1378,13 @@
         <v>44710</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>-4.148000000001048</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-0.1287227414330439</v>
       </c>
       <c r="G35" t="n">
-        <v>1605.3</v>
+        <v>1604.999999999995</v>
       </c>
     </row>
     <row r="36">
@@ -1405,13 +1405,13 @@
         <v>44381</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1.502000000000407</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.03405600722677576</v>
       </c>
       <c r="G36" t="n">
-        <v>2214.000000000005</v>
+        <v>2213.999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1432,13 +1432,13 @@
         <v>44701</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>-0.07799999999988358</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-0.002892561983278653</v>
       </c>
       <c r="G37" t="n">
-        <v>1209.899999999999</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="38">
@@ -1459,13 +1459,13 @@
         <v>44707</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>-30.19199999999837</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-0.3814636616865382</v>
       </c>
       <c r="G38" t="n">
-        <v>3949.499999999999</v>
+        <v>3949.000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1486,13 +1486,13 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>57.16599999999744</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.05969600579036079</v>
       </c>
       <c r="G39" t="n">
-        <v>52500.30000000006</v>
+        <v>52501.0000000002</v>
       </c>
     </row>
     <row r="40">
@@ -1513,13 +1513,13 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>2.401399999996647</v>
+        <v>23.49400000000023</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6021061158355476</v>
+        <v>5.134412955467231</v>
       </c>
       <c r="G40" t="n">
-        <v>246.9000000000051</v>
+        <v>246.9999999999345</v>
       </c>
     </row>
     <row r="41">
@@ -1540,13 +1540,13 @@
         <v>44724</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>9.134000000002562</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.6633423180589162</v>
       </c>
       <c r="G41" t="n">
-        <v>742.4999999999955</v>
+        <v>742.0000000000073</v>
       </c>
     </row>
     <row r="42">
@@ -1567,13 +1567,13 @@
         <v>44682</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>-0.6780000000000654</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-0.1857142857142424</v>
       </c>
       <c r="G42" t="n">
-        <v>182.4000000000012</v>
+        <v>181.9999999999993</v>
       </c>
     </row>
     <row r="43">
@@ -1594,13 +1594,13 @@
         <v>44712</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>4.660999999998603</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.06527429685325098</v>
       </c>
       <c r="G43" t="n">
-        <v>3590.599999999995</v>
+        <v>3590.999999999985</v>
       </c>
     </row>
     <row r="44">
@@ -1621,13 +1621,13 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-9.368999999994411</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-0.5400932400928649</v>
       </c>
       <c r="G44" t="n">
-        <v>858.4000000000742</v>
+        <v>857.9999999999927</v>
       </c>
     </row>
     <row r="45">
@@ -1648,13 +1648,13 @@
         <v>44725</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-1.808000000000175</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-0.2708708708709899</v>
       </c>
       <c r="G45" t="n">
-        <v>332.4000000000012</v>
+        <v>333.0000000000041</v>
       </c>
     </row>
     <row r="46">
@@ -1675,13 +1675,13 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5722000000001571</v>
+        <v>-0.930000000000291</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-0.3272151898733105</v>
       </c>
       <c r="G46" t="n">
-        <v>158.0999999999989</v>
+        <v>157.9999999999984</v>
       </c>
     </row>
     <row r="47">
@@ -1702,13 +1702,13 @@
         <v>44729</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>0.4470000000030268</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.03742236024805052</v>
       </c>
       <c r="G47" t="n">
-        <v>644.0000000000055</v>
+        <v>643.9999999999827</v>
       </c>
     </row>
     <row r="48">
@@ -1729,13 +1729,13 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>19.77200000000303</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1.970229007634432</v>
       </c>
       <c r="G48" t="n">
-        <v>523.3999999999924</v>
+        <v>524.0000000000236</v>
       </c>
     </row>
     <row r="49">
@@ -1756,13 +1756,13 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0007999999999810826</v>
+        <v>-0.3730000000000018</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>-0.4918918918918166</v>
       </c>
       <c r="G49" t="n">
-        <v>36.80000000000021</v>
+        <v>36.99999999999974</v>
       </c>
     </row>
     <row r="50">
@@ -1783,13 +1783,13 @@
         <v>44732</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-1.228000000002794</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-0.1086956521739142</v>
       </c>
       <c r="G50" t="n">
-        <v>505.8999999999969</v>
+        <v>505.9999999999945</v>
       </c>
     </row>
     <row r="51">
@@ -1810,13 +1810,13 @@
         <v>44731</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>-1.344000000000233</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-0.1457516339869778</v>
       </c>
       <c r="G51" t="n">
-        <v>459.1000000000008</v>
+        <v>459.0000000000032</v>
       </c>
     </row>
     <row r="52">
@@ -1837,10 +1837,10 @@
         <v>44730</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>-3.687999999988824</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-0.08777459407778697</v>
       </c>
       <c r="G52" t="n">
         <v>2093.99999999996</v>
@@ -1864,13 +1864,13 @@
         <v>44616</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>-26.40399999999208</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-0.1707110241356521</v>
       </c>
       <c r="G53" t="n">
-        <v>7665.300000000025</v>
+        <v>7664.999999999964</v>
       </c>
     </row>
     <row r="54">
@@ -1891,13 +1891,13 @@
         <v>44682</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>-1.579999999999927</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-1.645833333332816</v>
       </c>
       <c r="G54" t="n">
-        <v>48.19999999999709</v>
+        <v>48.00000000000182</v>
       </c>
     </row>
     <row r="55">
@@ -1918,13 +1918,13 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>7.926300000003539</v>
+        <v>3.168000000005122</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1423610081541306</v>
+        <v>0.03358042994810163</v>
       </c>
       <c r="G55" t="n">
-        <v>2698.000000000047</v>
+        <v>2697.999999999956</v>
       </c>
     </row>
     <row r="56">
@@ -1945,13 +1945,13 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.03262032085564602</v>
       </c>
       <c r="G56" t="n">
-        <v>748.1000000000222</v>
+        <v>748.0000000000018</v>
       </c>
     </row>
     <row r="57">
@@ -1972,13 +1972,13 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.003000000000065484</v>
+        <v>-0.3489999999999782</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-1.630000000000202</v>
       </c>
       <c r="G57" t="n">
-        <v>9.900000000000375</v>
+        <v>9.999999999999432</v>
       </c>
     </row>
     <row r="58">
@@ -1999,13 +1999,13 @@
         <v>44638</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-40.98699999999953</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-0.1660613956517751</v>
       </c>
       <c r="G58" t="n">
-        <v>12280.40000000001</v>
+        <v>12280.99999999995</v>
       </c>
     </row>
     <row r="59">
@@ -2026,10 +2026,10 @@
         <v>44724</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>-0.2339999999999691</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-1.462499999999554</v>
       </c>
       <c r="G59" t="n">
         <v>7.999999999999829</v>
@@ -2053,10 +2053,10 @@
         <v>44600</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-0.39399999999996</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>-0.5051282051282697</v>
       </c>
       <c r="G60" t="n">
         <v>39.00000000000006</v>
@@ -2080,13 +2080,13 @@
         <v>44724</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>-0.3660000000000764</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-0.4255813953488276</v>
       </c>
       <c r="G61" t="n">
-        <v>42.60000000000019</v>
+        <v>42.99999999999926</v>
       </c>
     </row>
     <row r="62">
@@ -2107,13 +2107,13 @@
         <v>44620</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>-0.8399999999999637</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>-0.003885914712939936</v>
       </c>
       <c r="G62" t="n">
-        <v>10833.5</v>
+        <v>10834</v>
       </c>
     </row>
     <row r="63">
@@ -2134,13 +2134,13 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>38.90239999999758</v>
+        <v>110.9260000000009</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3185279784383836</v>
+        <v>0.8897837668444141</v>
       </c>
       <c r="G63" t="n">
-        <v>6381.700000000001</v>
+        <v>6381.999999999971</v>
       </c>
     </row>
     <row r="64">
@@ -2161,13 +2161,13 @@
         <v>44720</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>-0.5589999999996508</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>-0.01948972360028331</v>
       </c>
       <c r="G64" t="n">
-        <v>1410.799999999995</v>
+        <v>1411.000000000013</v>
       </c>
     </row>
     <row r="65">
@@ -2188,13 +2188,13 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>-3.966999999999826</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>-0.4962311557788958</v>
       </c>
       <c r="G65" t="n">
-        <v>397.8000000000009</v>
+        <v>397.999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2215,13 +2215,13 @@
         <v>44730</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>-8.75</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>-0.2187875751502185</v>
       </c>
       <c r="G66" t="n">
-        <v>1995.499999999993</v>
+        <v>1996.000000000004</v>
       </c>
     </row>
     <row r="67">
@@ -2242,13 +2242,13 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>8.984000000002561</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1.745038167937786</v>
       </c>
       <c r="G67" t="n">
-        <v>262.2000000000071</v>
+        <v>262.0000000000118</v>
       </c>
     </row>
     <row r="68">
@@ -2269,13 +2269,13 @@
         <v>44707</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>-0.1269999999999982</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>-0.4500000000000761</v>
       </c>
       <c r="G68" t="n">
-        <v>13.40000000000003</v>
+        <v>14.00000000000006</v>
       </c>
     </row>
     <row r="69">
@@ -2296,13 +2296,13 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1505000000004657</v>
+        <v>4.004000000000815</v>
       </c>
       <c r="F69" t="n">
-        <v>0.02176428055001763</v>
+        <v>0.4826506024096264</v>
       </c>
       <c r="G69" t="n">
-        <v>414.9000000000115</v>
+        <v>414.9999999999864</v>
       </c>
     </row>
     <row r="70">
@@ -2323,13 +2323,13 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0228000000002794</v>
+        <v>-0.69900000000016</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>-0.1191780821917652</v>
       </c>
       <c r="G70" t="n">
-        <v>292.5999999999988</v>
+        <v>292.0000000000016</v>
       </c>
     </row>
     <row r="71">
@@ -2350,13 +2350,13 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.01430000000000291</v>
+        <v>-1.05099999999984</v>
       </c>
       <c r="F71" t="n">
-        <v>0.001227830832281182</v>
+        <v>-0.2413636363635256</v>
       </c>
       <c r="G71" t="n">
-        <v>219.8999999999955</v>
+        <v>220.0000000000045</v>
       </c>
     </row>
     <row r="72">
@@ -2377,13 +2377,13 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>21.69980000000214</v>
+        <v>21.79400000000023</v>
       </c>
       <c r="F72" t="n">
-        <v>1.76674463401219</v>
+        <v>1.334662998624872</v>
       </c>
       <c r="G72" t="n">
-        <v>726.8000000000029</v>
+        <v>726.9999999999982</v>
       </c>
     </row>
     <row r="73">
@@ -2404,13 +2404,13 @@
         <v>44713</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>-2.991999999999825</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>-0.7300492610840977</v>
       </c>
       <c r="G73" t="n">
-        <v>203.3000000000015</v>
+        <v>202.9999999999973</v>
       </c>
     </row>
     <row r="74">
@@ -2431,13 +2431,13 @@
         <v>44614</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>-4.359000000000378</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>-0.787364620938812</v>
       </c>
       <c r="G74" t="n">
-        <v>276.9000000000005</v>
+        <v>276.9999999999982</v>
       </c>
     </row>
     <row r="75">
@@ -2458,13 +2458,13 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>5.095199999993201</v>
+        <v>5.05</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>0.5885057471272211</v>
       </c>
       <c r="G75" t="n">
-        <v>870.2999999999975</v>
+        <v>870.0000000000273</v>
       </c>
     </row>
     <row r="76">
@@ -2485,13 +2485,13 @@
         <v>44734</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>-27.4219999999972</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>-0.6935728744938605</v>
       </c>
       <c r="G76" t="n">
-        <v>1975.999999999931</v>
+        <v>1976.000000000022</v>
       </c>
     </row>
     <row r="77">
@@ -2512,13 +2512,13 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>3.429999999998836</v>
+        <v>5.637999999994645</v>
       </c>
       <c r="F77" t="n">
-        <v>0.03710892997976833</v>
+        <v>0.1253286590708874</v>
       </c>
       <c r="G77" t="n">
-        <v>2282.200000000012</v>
+        <v>2282.000000000016</v>
       </c>
     </row>
     <row r="78">
@@ -2539,13 +2539,13 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2474999999998545</v>
+        <v>3.354000000000087</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>0.25064432989687</v>
       </c>
       <c r="G78" t="n">
-        <v>775.6000000000029</v>
+        <v>775.9999999999991</v>
       </c>
     </row>
     <row r="79">
@@ -2566,13 +2566,13 @@
         <v>44701</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1.095000000001164</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>0.5050000000010474</v>
       </c>
       <c r="G79" t="n">
-        <v>159.5000000000027</v>
+        <v>159.9999999999909</v>
       </c>
     </row>
     <row r="80">
@@ -2593,13 +2593,13 @@
         <v>44734</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>5.478000000002794</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>0.5159474671669809</v>
       </c>
       <c r="G80" t="n">
-        <v>533.1999999999994</v>
+        <v>532.9999999999984</v>
       </c>
     </row>
     <row r="81">
@@ -2620,13 +2620,13 @@
         <v>44355</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>-3.427000000000407</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>-0.1173076923077047</v>
       </c>
       <c r="G81" t="n">
-        <v>1456.899999999996</v>
+        <v>1455.999999999995</v>
       </c>
     </row>
     <row r="82">
@@ -2647,13 +2647,13 @@
         <v>44699</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>-0.4550000000000182</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-0.7062500000000833</v>
       </c>
       <c r="G82" t="n">
-        <v>32.19999999999885</v>
+        <v>31.99999999999932</v>
       </c>
     </row>
     <row r="83">
@@ -2674,13 +2674,13 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4890000000001237</v>
+        <v>-0.275</v>
       </c>
       <c r="F83" t="n">
-        <v>1.072803347280443</v>
+        <v>-0.6041666666665679</v>
       </c>
       <c r="G83" t="n">
-        <v>23.90000000000043</v>
+        <v>24.00000000000091</v>
       </c>
     </row>
     <row r="84">
@@ -2701,13 +2701,13 @@
         <v>44735</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>-0.8939999999973225</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>-0.004955910257811395</v>
       </c>
       <c r="G84" t="n">
-        <v>8959.000000000015</v>
+        <v>8958.999999999993</v>
       </c>
     </row>
     <row r="85">
@@ -2728,10 +2728,10 @@
         <v>44727</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>2.440000000002328</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>0.07974603174638653</v>
       </c>
       <c r="G85" t="n">
         <v>1575</v>
@@ -2755,13 +2755,13 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>-9.648000000001048</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-0.4109401709400679</v>
       </c>
       <c r="G86" t="n">
-        <v>1170.500000000015</v>
+        <v>1169.999999999982</v>
       </c>
     </row>
     <row r="87">
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>0.02650000000030559</v>
+        <v>-1.386000000000058</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>-2.39333333333334</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2809,13 +2809,13 @@
         <v>44361</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>-6.01700000000128</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>-0.2000000000000905</v>
       </c>
       <c r="G88" t="n">
-        <v>1532.600000000002</v>
+        <v>1532.000000000005</v>
       </c>
     </row>
     <row r="89">
@@ -2836,13 +2836,13 @@
         <v>44147</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>-2.761000000000058</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>-0.3629921259842978</v>
       </c>
       <c r="G89" t="n">
-        <v>381.3</v>
+        <v>381</v>
       </c>
     </row>
     <row r="90">
@@ -2863,13 +2863,13 @@
         <v>44731</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>-0.3549999999988359</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>-0.02861952861923438</v>
       </c>
       <c r="G90" t="n">
-        <v>593.9000000000078</v>
+        <v>594.0000000000055</v>
       </c>
     </row>
     <row r="91">
@@ -2890,13 +2890,13 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>2.54100000000326</v>
+        <v>-0.9800000000046566</v>
       </c>
       <c r="F91" t="n">
-        <v>0.06433074255052718</v>
+        <v>-0.1069367088607359</v>
       </c>
       <c r="G91" t="n">
-        <v>3949.89999999998</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="92">
@@ -2917,13 +2917,13 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.05039999999971769</v>
+        <v>-0.6110000000000582</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>-0.7820512820519416</v>
       </c>
       <c r="G92" t="n">
-        <v>38.70000000000005</v>
+        <v>39.00000000000432</v>
       </c>
     </row>
     <row r="93">
@@ -2944,13 +2944,13 @@
         <v>44717</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>-0.6569999999999709</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>-0.6560000000001309</v>
       </c>
       <c r="G93" t="n">
-        <v>49.2999999999995</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94">
@@ -2971,13 +2971,13 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>6.654399999999441</v>
+        <v>31.93499999999767</v>
       </c>
       <c r="F94" t="n">
-        <v>2.023370429255233</v>
+        <v>9.913829787233716</v>
       </c>
       <c r="G94" t="n">
-        <v>188.6999999999716</v>
+        <v>188.0000000000109</v>
       </c>
     </row>
     <row r="95">
@@ -2998,13 +2998,13 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>33.50829999999841</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F95" t="n">
-        <v>1.263580316107944</v>
+        <v>2.240414798206061</v>
       </c>
       <c r="G95" t="n">
-        <v>1784.199999999964</v>
+        <v>1783.999999999924</v>
       </c>
     </row>
     <row r="96">
@@ -3025,13 +3025,13 @@
         <v>44734</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>19.01199999999954</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1.388951841359751</v>
       </c>
       <c r="G96" t="n">
-        <v>705.3000000000338</v>
+        <v>705.9999999999945</v>
       </c>
     </row>
     <row r="97">
@@ -3052,13 +3052,13 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>-1.186999999999534</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>-0.5230088495571893</v>
       </c>
       <c r="G97" t="n">
-        <v>113.1000000000029</v>
+        <v>112.9999999999995</v>
       </c>
     </row>
     <row r="98">
@@ -3079,13 +3079,13 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>1.099899999998161</v>
+        <v>16.79100000000035</v>
       </c>
       <c r="F98" t="n">
-        <v>0.02200617283946066</v>
+        <v>0.339451114922853</v>
       </c>
       <c r="G98" t="n">
-        <v>2916</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="99">
@@ -3106,13 +3106,13 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.01010000000001128</v>
+        <v>-0.1929999999999836</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>-0.7800000000002029</v>
       </c>
       <c r="G99" t="n">
-        <v>10.39999999999992</v>
+        <v>9.999999999999964</v>
       </c>
     </row>
     <row r="100">
@@ -3133,13 +3133,13 @@
         <v>44634</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>-4.811999999999534</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>-0.09606205250605795</v>
       </c>
       <c r="G100" t="n">
-        <v>2514.300000000003</v>
+        <v>2514.000000000033</v>
       </c>
     </row>
     <row r="101">
@@ -3160,13 +3160,13 @@
         <v>44730</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>-1.151000000000204</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>-0.7710144927546381</v>
       </c>
       <c r="G101" t="n">
-        <v>68.6000000000007</v>
+        <v>68.99999999999977</v>
       </c>
     </row>
     <row r="102">
@@ -3187,13 +3187,13 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1910999999992782</v>
+        <v>6.185000000000582</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>1.329924242424823</v>
       </c>
       <c r="G102" t="n">
-        <v>263.7000000000057</v>
+        <v>263.9999999999986</v>
       </c>
     </row>
     <row r="103">
@@ -3214,13 +3214,13 @@
         <v>44724</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>-0.1519999999999982</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>-0.357894736842143</v>
       </c>
       <c r="G103" t="n">
-        <v>19.20000000000002</v>
+        <v>18.99999999999977</v>
       </c>
     </row>
     <row r="104">
@@ -3241,13 +3241,13 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>21.37660000000033</v>
+        <v>86.93699999999953</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7448439868290389</v>
+        <v>2.216204913747985</v>
       </c>
       <c r="G104" t="n">
-        <v>1913.299999999981</v>
+        <v>1913.000000000011</v>
       </c>
     </row>
     <row r="105">
@@ -3268,13 +3268,13 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2510000000000218</v>
+        <v>-0.1339999999998326</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2028614457830905</v>
+        <v>-0.105970149253603</v>
       </c>
       <c r="G105" t="n">
-        <v>66.40000000000157</v>
+        <v>66.99999999999875</v>
       </c>
     </row>
     <row r="106">
@@ -3295,13 +3295,13 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>0.1471000000019558</v>
+        <v>-13.38799999999464</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>-0.9768667642747925</v>
       </c>
       <c r="G106" t="n">
-        <v>682.7999999999975</v>
+        <v>683.0000000000382</v>
       </c>
     </row>
     <row r="107">
@@ -3322,13 +3322,13 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>10.0859999999986</v>
+        <v>125.3700000000012</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>22.99697885196448</v>
       </c>
       <c r="G107" t="n">
-        <v>331.3999999999851</v>
+        <v>330.9999999999945</v>
       </c>
     </row>
     <row r="108">
@@ -3349,13 +3349,13 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.01220000000002983</v>
+        <v>-0.7469999999999345</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>-2.318749999999969</v>
       </c>
       <c r="G108" t="n">
-        <v>16.69999999999945</v>
+        <v>16.00000000000037</v>
       </c>
     </row>
     <row r="109">
@@ -3376,13 +3376,13 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>-1.315999999999985</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>-0.4500000000000967</v>
       </c>
       <c r="G109" t="n">
-        <v>144.1000000000003</v>
+        <v>143.9999999999998</v>
       </c>
     </row>
     <row r="110">
@@ -3403,13 +3403,13 @@
         <v>44724</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>-0.4079999999999927</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>-2.049999999999316</v>
       </c>
       <c r="G110" t="n">
-        <v>10.50000000000004</v>
+        <v>9.999999999999787</v>
       </c>
     </row>
     <row r="111">
@@ -3430,13 +3430,13 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>6.096400000000722</v>
+        <v>3.551999999998952</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>-0.4398437499999812</v>
       </c>
       <c r="G111" t="n">
-        <v>768.5000000000173</v>
+        <v>768.0000000000064</v>
       </c>
     </row>
     <row r="112">
@@ -3457,13 +3457,13 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>-4.108000000000175</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>-0.5237822349569853</v>
       </c>
       <c r="G112" t="n">
-        <v>348.7000000000023</v>
+        <v>349.0000000000009</v>
       </c>
     </row>
     <row r="113">
@@ -3484,13 +3484,13 @@
         <v>44696</v>
       </c>
       <c r="E113" t="n">
-        <v>0.003800000000001092</v>
+        <v>-0.04399999999999978</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>-0.3666666666667199</v>
       </c>
       <c r="G113" t="n">
-        <v>5.499999999999972</v>
+        <v>5.999999999999872</v>
       </c>
     </row>
     <row r="114">
@@ -3511,13 +3511,13 @@
         <v>44622</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>-0.09099999999998545</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>-0.07796610169492144</v>
       </c>
       <c r="G114" t="n">
-        <v>58.8000000000001</v>
+        <v>58.99999999999999</v>
       </c>
     </row>
     <row r="115">
@@ -3538,13 +3538,13 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02880000000000109</v>
+        <v>0.02600000000002183</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>-0.009523809523800825</v>
       </c>
       <c r="G115" t="n">
-        <v>20.19999999999982</v>
+        <v>21.00000000000009</v>
       </c>
     </row>
     <row r="116">
@@ -3565,13 +3565,13 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>1.360800000000745</v>
+        <v>-7.284999999997671</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4130898021334725</v>
+        <v>-1.551776649743571</v>
       </c>
       <c r="G116" t="n">
-        <v>197.1000000000004</v>
+        <v>197.0000000000027</v>
       </c>
     </row>
     <row r="117">
@@ -3592,13 +3592,13 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>8.023099999997067</v>
+        <v>12.62199999999721</v>
       </c>
       <c r="F117" t="n">
-        <v>2.085842293906044</v>
+        <v>3.513452914797134</v>
       </c>
       <c r="G117" t="n">
-        <v>223.1999999999971</v>
+        <v>223.0000000000018</v>
       </c>
     </row>
     <row r="118">
@@ -3619,13 +3619,13 @@
         <v>44732</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>0.1470000000001164</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>0.1044117647068229</v>
       </c>
       <c r="G118" t="n">
-        <v>68.6000000000007</v>
+        <v>68.00000000000068</v>
       </c>
     </row>
     <row r="119">
@@ -3646,13 +3646,13 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>190.9054000000004</v>
+        <v>107.9030000000028</v>
       </c>
       <c r="F119" t="n">
-        <v>21.91308912739254</v>
+        <v>12.52843822843768</v>
       </c>
       <c r="G119" t="n">
-        <v>428.5999999999831</v>
+        <v>428.9999999999964</v>
       </c>
     </row>
     <row r="120">
@@ -3673,13 +3673,13 @@
         <v>44733</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>4.075</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>2.355952380953581</v>
       </c>
       <c r="G120" t="n">
-        <v>84.10000000001219</v>
+        <v>83.99999999999181</v>
       </c>
     </row>
     <row r="121">
@@ -3700,13 +3700,13 @@
         <v>44735</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>-0.3780000000000655</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>-0.5250000000000917</v>
       </c>
       <c r="G121" t="n">
-        <v>35.69999999999993</v>
+        <v>35.99999999999994</v>
       </c>
     </row>
     <row r="122">
@@ -3727,13 +3727,13 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>-8.194000000000234</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>-0.2770891364901023</v>
       </c>
       <c r="G122" t="n">
-        <v>1436.599999999999</v>
+        <v>1436.000000000013</v>
       </c>
     </row>
     <row r="123">
@@ -3754,13 +3754,13 @@
         <v>44656</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>-5.332000000000699</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>-0.2604309500492244</v>
       </c>
       <c r="G123" t="n">
-        <v>1020.900000000006</v>
+        <v>1020.999999999992</v>
       </c>
     </row>
     <row r="124">
@@ -3781,13 +3781,13 @@
         <v>44680</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>-1.116000000000349</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>-0.4455999999999767</v>
       </c>
       <c r="G124" t="n">
-        <v>124.8999999999995</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125">
@@ -3808,13 +3808,13 @@
         <v>44733</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>2.484999999997672</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>0.02745792736927616</v>
       </c>
       <c r="G125" t="n">
-        <v>4516.199999999981</v>
+        <v>4515.999999999985</v>
       </c>
     </row>
     <row r="126">
@@ -3835,13 +3835,13 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>1.068799999999464</v>
+        <v>10.03400000000256</v>
       </c>
       <c r="F126" t="n">
-        <v>1.038636363634196</v>
+        <v>8.830645161290258</v>
       </c>
       <c r="G126" t="n">
-        <v>61.59999999999854</v>
+        <v>62.00000000000045</v>
       </c>
     </row>
     <row r="127">
@@ -3862,13 +3862,13 @@
         <v>44730</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>2.930000000004656</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>0.2548387096781686</v>
       </c>
       <c r="G127" t="n">
-        <v>620.1000000000022</v>
+        <v>620.0000000000045</v>
       </c>
     </row>
     <row r="128">
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>5.600000000000005</v>
+        <v>6.000000000000005</v>
       </c>
     </row>
     <row r="129">
@@ -3916,13 +3916,13 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>37.36790000000038</v>
+        <v>50.56000000000931</v>
       </c>
       <c r="F129" t="n">
-        <v>0.6511990841168537</v>
+        <v>0.7047303404640545</v>
       </c>
       <c r="G129" t="n">
-        <v>3319.200000000001</v>
+        <v>3319.000000000051</v>
       </c>
     </row>
     <row r="130">
@@ -3943,13 +3943,13 @@
         <v>44647</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>-4.933999999999651</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>-1.339130434782554</v>
       </c>
       <c r="G130" t="n">
-        <v>183.9999999999975</v>
+        <v>184.0000000000032</v>
       </c>
     </row>
     <row r="131">
@@ -3970,13 +3970,13 @@
         <v>44635</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>-8.355000000000292</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>-2.387500000000231</v>
       </c>
       <c r="G131" t="n">
-        <v>175.7</v>
+        <v>176</v>
       </c>
     </row>
     <row r="132">
@@ -3997,13 +3997,13 @@
         <v>44734</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>-14.3429999999993</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>-0.1918744971842007</v>
       </c>
       <c r="G132" t="n">
-        <v>3729.100000000017</v>
+        <v>3728.999999999996</v>
       </c>
     </row>
     <row r="133">
@@ -4024,13 +4024,13 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>2.385599999999977</v>
+        <v>13.12000000000116</v>
       </c>
       <c r="F133" t="n">
-        <v>0.04378465129856796</v>
+        <v>0.2863967906637441</v>
       </c>
       <c r="G133" t="n">
-        <v>2741.599999999994</v>
+        <v>2742.000000000007</v>
       </c>
     </row>
     <row r="134">
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>13.72999999999884</v>
+        <v>11.3179999999993</v>
       </c>
       <c r="F134" t="n">
-        <v>0.8300441176470541</v>
+        <v>0.8117647058821016</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,13 +4078,13 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>-0.76299999999992</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>-0.153086419753059</v>
       </c>
       <c r="G135" t="n">
-        <v>242.3999999999978</v>
+        <v>243.0000000000007</v>
       </c>
     </row>
     <row r="136">
@@ -4105,13 +4105,13 @@
         <v>44734</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>-1.705999999999767</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>-0.1478108581435838</v>
       </c>
       <c r="G136" t="n">
-        <v>571.9000000000051</v>
+        <v>571.0000000000036</v>
       </c>
     </row>
     <row r="137">
@@ -4132,13 +4132,13 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.04619999999995343</v>
+        <v>-0.4139999999999418</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0371794871794828</v>
+        <v>-0.3645161290319972</v>
       </c>
       <c r="G137" t="n">
-        <v>31.19999999999976</v>
+        <v>31.00000000000023</v>
       </c>
     </row>
     <row r="138">
@@ -4159,13 +4159,13 @@
         <v>44732</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>-13.11900000000023</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>-0.2110389610389611</v>
       </c>
       <c r="G138" t="n">
-        <v>3080.7</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="139">
@@ -4186,13 +4186,13 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0315999999998894</v>
+        <v>-0.3390000000003056</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>-0.03268858800778224</v>
       </c>
       <c r="G139" t="n">
-        <v>517.4999999999955</v>
+        <v>516.9999999999959</v>
       </c>
     </row>
     <row r="140">
@@ -4213,13 +4213,13 @@
         <v>44734</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>10.14400000000023</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>0.8003105590059073</v>
       </c>
       <c r="G140" t="n">
-        <v>643.4999999999945</v>
+        <v>643.9999999999827</v>
       </c>
     </row>
     <row r="141">
@@ -4240,13 +4240,13 @@
         <v>44717</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>-0.1320000000000164</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>-0.1033333333333528</v>
       </c>
       <c r="G141" t="n">
-        <v>60.90000000000018</v>
+        <v>60.00000000000014</v>
       </c>
     </row>
     <row r="142">
@@ -4267,13 +4267,13 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>-2.203000000000247</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>-0.3203488372093152</v>
       </c>
       <c r="G142" t="n">
-        <v>343.8000000000002</v>
+        <v>343.9999999999998</v>
       </c>
     </row>
     <row r="143">
@@ -4294,13 +4294,13 @@
         <v>44734</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>-4.108999999999651</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>-7.307407407405622</v>
       </c>
       <c r="G143" t="n">
-        <v>26.90000000000055</v>
+        <v>27.00000000000102</v>
       </c>
     </row>
     <row r="144">
@@ -4321,13 +4321,13 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3721000000019558</v>
+        <v>8.114000000001397</v>
       </c>
       <c r="F144" t="n">
-        <v>0.06497983131638749</v>
+        <v>1.57289377289411</v>
       </c>
       <c r="G144" t="n">
-        <v>272.6999999998952</v>
+        <v>272.9999999999563</v>
       </c>
     </row>
     <row r="145">
@@ -4348,13 +4348,13 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>2.641699999989942</v>
+        <v>8.240000000002329</v>
       </c>
       <c r="F145" t="n">
-        <v>0.1485684290887822</v>
+        <v>0.458969465648632</v>
       </c>
       <c r="G145" t="n">
-        <v>1047.800000000007</v>
+        <v>1048.000000000002</v>
       </c>
     </row>
     <row r="146">
@@ -4375,13 +4375,13 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>1.108999999999651</v>
+        <v>0.7229999999981374</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>0.3981366459611669</v>
       </c>
       <c r="G146" t="n">
-        <v>161.5999999999985</v>
+        <v>160.99999999999</v>
       </c>
     </row>
     <row r="147">
@@ -4402,13 +4402,13 @@
         <v>44724</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>-2.483000000000175</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>-0.6183168316830731</v>
       </c>
       <c r="G147" t="n">
-        <v>201.400000000001</v>
+        <v>201.9999999999982</v>
       </c>
     </row>
     <row r="148">
@@ -4429,13 +4429,13 @@
         <v>44667</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>-0.3460000000000036</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>-5.733333333334135</v>
       </c>
       <c r="G148" t="n">
-        <v>2.400000000000002</v>
+        <v>3.000000000000025</v>
       </c>
     </row>
     <row r="149">
@@ -4456,10 +4456,10 @@
         <v>44699</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>-0.05200000000000386</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>-0.6249999999999856</v>
       </c>
       <c r="G149" t="n">
         <v>4.000000000000092</v>
@@ -4483,13 +4483,13 @@
         <v>44734</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>-0.3460000000000036</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>-0.5766666666665267</v>
       </c>
       <c r="G150" t="n">
-        <v>30.59999999999974</v>
+        <v>29.99999999999972</v>
       </c>
     </row>
     <row r="151">
@@ -4510,13 +4510,13 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>7.870600000000559</v>
+        <v>3.491000000000349</v>
       </c>
       <c r="F151" t="n">
-        <v>3.686513761468199</v>
+        <v>1.365137614679358</v>
       </c>
       <c r="G151" t="n">
-        <v>109.0000000000032</v>
+        <v>108.9999999999975</v>
       </c>
     </row>
     <row r="152">
@@ -4537,13 +4537,13 @@
         <v>44614</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>-0.8139999999999418</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>-0.1301587301586837</v>
       </c>
       <c r="G152" t="n">
-        <v>314.7999999999996</v>
+        <v>315.0000000000006</v>
       </c>
     </row>
     <row r="153">
@@ -4564,13 +4564,13 @@
         <v>44734</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>-1.127000000000407</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>-0.1610619469028444</v>
       </c>
       <c r="G153" t="n">
-        <v>339.0000000000043</v>
+        <v>338.9999999999986</v>
       </c>
     </row>
     <row r="154">
@@ -4591,13 +4591,13 @@
         <v>44724</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>-2.108000000000175</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>-1.840350877193924</v>
       </c>
       <c r="G154" t="n">
-        <v>56.899999999996</v>
+        <v>56.99999999999932</v>
       </c>
     </row>
     <row r="155">
@@ -4618,13 +4618,13 @@
         <v>44712</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>-1.795999999999185</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>-0.08093525179856029</v>
       </c>
       <c r="G155" t="n">
-        <v>1111.399999999981</v>
+        <v>1112.000000000012</v>
       </c>
     </row>
     <row r="156">
@@ -4645,13 +4645,13 @@
         <v>44699</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>-0.3610000000000128</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>-0.5176470588234655</v>
       </c>
       <c r="G156" t="n">
-        <v>34.7999999999999</v>
+        <v>33.99999999999963</v>
       </c>
     </row>
     <row r="157">
@@ -4672,13 +4672,13 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.100700000001234</v>
+        <v>-15.3</v>
       </c>
       <c r="F157" t="n">
-        <v>0.00447231424545761</v>
+        <v>-0.9662721893490384</v>
       </c>
       <c r="G157" t="n">
-        <v>845.1999999999998</v>
+        <v>845.0000000000045</v>
       </c>
     </row>
     <row r="158">
@@ -4699,13 +4699,13 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2922000000020489</v>
+        <v>1.004000000003725</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>0.08663594470067552</v>
       </c>
       <c r="G158" t="n">
-        <v>651.50000000001</v>
+        <v>650.9999999999991</v>
       </c>
     </row>
     <row r="159">
@@ -4726,13 +4726,13 @@
         <v>44730</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>-6.172000000003027</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>-0.3108190090999967</v>
       </c>
       <c r="G159" t="n">
-        <v>989.1999999999825</v>
+        <v>989.0000000000327</v>
       </c>
     </row>
     <row r="160">
@@ -4753,13 +4753,13 @@
         <v>44733</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>2.551999999998952</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>0.3786350148366265</v>
       </c>
       <c r="G160" t="n">
-        <v>336.4000000000033</v>
+        <v>337.0000000000118</v>
       </c>
     </row>
     <row r="161">
@@ -4780,13 +4780,13 @@
         <v>44731</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>10.39000000000233</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>1.365263157894876</v>
       </c>
       <c r="G161" t="n">
-        <v>380.7000000000016</v>
+        <v>379.9999999999955</v>
       </c>
     </row>
     <row r="162">
@@ -4807,13 +4807,13 @@
         <v>44724</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>-2.676999999998952</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>-133.5000000000341</v>
       </c>
       <c r="G162" t="n">
-        <v>1.100000000008095</v>
+        <v>0.9999999999990905</v>
       </c>
     </row>
     <row r="163">
@@ -4834,13 +4834,13 @@
         <v>44619</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>-3.168000000000029</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>-0.948502994011766</v>
       </c>
       <c r="G163" t="n">
-        <v>166.7000000000002</v>
+        <v>167.0000000000002</v>
       </c>
     </row>
     <row r="164">
@@ -4861,13 +4861,13 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.01169999999983702</v>
+        <v>-2.823999999999796</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>-0.821893491124227</v>
       </c>
       <c r="G164" t="n">
-        <v>168.4999999999945</v>
+        <v>168.9999999999998</v>
       </c>
     </row>
     <row r="165">
@@ -4888,13 +4888,13 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.03989999999976135</v>
+        <v>-1.764999999999782</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>-0.9831168831168322</v>
       </c>
       <c r="G165" t="n">
-        <v>76.29999999999768</v>
+        <v>77.00000000000102</v>
       </c>
     </row>
     <row r="166">
@@ -4915,13 +4915,13 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>-1.155999999999949</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>-0.5029126213590744</v>
       </c>
       <c r="G166" t="n">
-        <v>102.4000000000001</v>
+        <v>103.0000000000001</v>
       </c>
     </row>
     <row r="167">

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3150000000000091</v>
+        <v>-0.3260000000000218</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2267605633802993</v>
+        <v>-0.2323943661971956</v>
       </c>
       <c r="G2" t="n">
         <v>71.00000000000009</v>
@@ -514,7 +514,7 @@
         <v>44734</v>
       </c>
       <c r="E3" t="n">
-        <v>3.335000000000582</v>
+        <v>3.339999999999418</v>
       </c>
       <c r="F3" t="n">
         <v>1.815217391303888</v>
@@ -541,10 +541,10 @@
         <v>44609</v>
       </c>
       <c r="E4" t="n">
-        <v>-26.73999999999069</v>
+        <v>-26.49000000000233</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.207839562443048</v>
+        <v>-1.206927985415002</v>
       </c>
       <c r="G4" t="n">
         <v>1096.99999999998</v>
@@ -568,10 +568,10 @@
         <v>44735</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.87900000000081</v>
+        <v>-10.70999999999913</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02283206204457414</v>
+        <v>-0.02280649422593</v>
       </c>
       <c r="G5" t="n">
         <v>23466.99999999983</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.332999999998719</v>
+        <v>-2.382000000000699</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2087033747779753</v>
+        <v>-0.2143872113677974</v>
       </c>
       <c r="G6" t="n">
         <v>562.9999999999995</v>
@@ -622,10 +622,10 @@
         <v>44711</v>
       </c>
       <c r="E7" t="n">
-        <v>3.487000000002445</v>
+        <v>4.212000000002445</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5722826086963699</v>
+        <v>0.572282608695579</v>
       </c>
       <c r="G7" t="n">
         <v>368.0000000000064</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.625</v>
+        <v>-16.61600000000326</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4586092715230531</v>
+        <v>-0.4583885209716136</v>
       </c>
       <c r="G8" t="n">
         <v>1811.999999999989</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4</v>
+        <v>2.294999999995343</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01700428803785277</v>
+        <v>0.01693035635066281</v>
       </c>
       <c r="G9" t="n">
         <v>6763.000000000102</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.480999999999767</v>
+        <v>-0.9240000000005238</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5840764331209316</v>
+        <v>-0.00445859872655973</v>
       </c>
       <c r="G10" t="n">
         <v>156.9999999999936</v>
@@ -730,7 +730,7 @@
         <v>44632</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3640000000000327</v>
+        <v>-0.3619999999999891</v>
       </c>
       <c r="F11" t="n">
         <v>-0.1381679389312933</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>19.75</v>
+        <v>24.9039999999979</v>
       </c>
       <c r="F12" t="n">
-        <v>1.718577648765988</v>
+        <v>1.895936139332468</v>
       </c>
       <c r="G12" t="n">
         <v>688.9999999999873</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0759999999999991</v>
+        <v>-0.04700000000000273</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.05000000000004959</v>
+        <v>-0.3416666666666424</v>
       </c>
       <c r="G13" t="n">
         <v>11.99999999999992</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4260000000000218</v>
+        <v>-0.4730000000001383</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.190000000000634</v>
+        <v>-2.540000000001017</v>
       </c>
       <c r="G14" t="n">
         <v>9.999999999999432</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>5.575</v>
+        <v>6.312999999997555</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9117088607593964</v>
+        <v>1.086075949366361</v>
       </c>
       <c r="G15" t="n">
         <v>316.0000000000082</v>
@@ -865,10 +865,10 @@
         <v>44735</v>
       </c>
       <c r="E16" t="n">
-        <v>-37.5820000000007</v>
+        <v>-37.47199999999721</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6300840336134844</v>
+        <v>-0.6294789915965056</v>
       </c>
       <c r="G16" t="n">
         <v>2975</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>51.1929999999993</v>
+        <v>42.96600000000035</v>
       </c>
       <c r="F17" t="n">
-        <v>4.999032882011589</v>
+        <v>3.311605415860885</v>
       </c>
       <c r="G17" t="n">
         <v>516.9999999999959</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>3.952000000000408</v>
+        <v>4.05399999999936</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2790387182909767</v>
+        <v>0.2622162883845046</v>
       </c>
       <c r="G18" t="n">
         <v>749.0000000000009</v>
@@ -946,10 +946,10 @@
         <v>44688</v>
       </c>
       <c r="E19" t="n">
-        <v>2.745999999999185</v>
+        <v>2.748999999999069</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2886554621846789</v>
+        <v>0.2888655462184879</v>
       </c>
       <c r="G19" t="n">
         <v>475.9999999999991</v>
@@ -973,10 +973,10 @@
         <v>44655</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.976999999998952</v>
+        <v>-8.961999999999534</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4124763705102568</v>
+        <v>-0.43459357277893</v>
       </c>
       <c r="G20" t="n">
         <v>1057.999999999993</v>
@@ -1000,10 +1000,10 @@
         <v>44720</v>
       </c>
       <c r="E21" t="n">
-        <v>1.426000000000931</v>
+        <v>1.454000000003725</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005063467708194528</v>
+        <v>0.005077416655062031</v>
       </c>
       <c r="G21" t="n">
         <v>14338</v>
@@ -1027,10 +1027,10 @@
         <v>44729</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.075</v>
+        <v>-5.072000000000116</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6958791208791605</v>
+        <v>-0.6975274725274483</v>
       </c>
       <c r="G22" t="n">
         <v>364.0000000000043</v>
@@ -1054,10 +1054,10 @@
         <v>44607</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.614000000001397</v>
+        <v>-2.604000000000815</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1431868131868</v>
+        <v>-0.1429670329671349</v>
       </c>
       <c r="G23" t="n">
         <v>910.0000000000023</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.771999999997206</v>
+        <v>-0.7809999999997672</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.03095803642101627</v>
+        <v>-0.03087885985766627</v>
       </c>
       <c r="G24" t="n">
         <v>1263.000000000011</v>
@@ -1108,10 +1108,10 @@
         <v>44619</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.977999999999884</v>
+        <v>-1.97899999999936</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.01309066843150151</v>
+        <v>-0.01310390469886718</v>
       </c>
       <c r="G25" t="n">
         <v>7555.000000000018</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.170000000001163</v>
+        <v>-6.344000000000233</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1163065843622175</v>
+        <v>-0.2100308641974644</v>
       </c>
       <c r="G26" t="n">
         <v>1944.000000000005</v>
@@ -1162,10 +1162,10 @@
         <v>44696</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3609999999999672</v>
+        <v>-0.3600000000000364</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.275000000000182</v>
+        <v>-4.725000000000919</v>
       </c>
       <c r="G27" t="n">
         <v>3.999999999999915</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.4</v>
+        <v>-2.013999999999942</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4500000000001581</v>
+        <v>-0.2163306451615099</v>
       </c>
       <c r="G28" t="n">
         <v>495.9999999999809</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1540000000037253</v>
+        <v>2.011999999999534</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08840381991868548</v>
+        <v>0.1754433833558821</v>
       </c>
       <c r="G29" t="n">
         <v>732.9999999999927</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.503999999997904</v>
+        <v>-4.363000000000466</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0888613861385274</v>
+        <v>-0.09113036303640926</v>
       </c>
       <c r="G30" t="n">
         <v>2424.000000000001</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2579999999999927</v>
+        <v>-0.2489999999999782</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4846153846152841</v>
+        <v>-0.4961538461538224</v>
       </c>
       <c r="G31" t="n">
         <v>26.00000000000051</v>
@@ -1297,10 +1297,10 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.09500000000000455</v>
+        <v>0.1720000000000027</v>
       </c>
       <c r="F32" t="n">
-        <v>3.149999999999951</v>
+        <v>-0.9500000000000755</v>
       </c>
       <c r="G32" t="n">
         <v>6.00000000000005</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.941999999999825</v>
+        <v>-1.409999999999127</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3455999999999767</v>
+        <v>-0.2183999999996741</v>
       </c>
       <c r="G33" t="n">
         <v>250</v>
@@ -1351,10 +1351,10 @@
         <v>44175</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.208000000000175</v>
+        <v>-2.202999999999883</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2859740259738899</v>
+        <v>-0.2862337662338721</v>
       </c>
       <c r="G34" t="n">
         <v>385</v>
@@ -1378,7 +1378,7 @@
         <v>44710</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.148000000001048</v>
+        <v>-4.132000000000699</v>
       </c>
       <c r="F35" t="n">
         <v>-0.1287227414330439</v>
@@ -1405,10 +1405,10 @@
         <v>44381</v>
       </c>
       <c r="E36" t="n">
-        <v>1.502000000000407</v>
+        <v>1.509000000001106</v>
       </c>
       <c r="F36" t="n">
-        <v>0.03405600722677576</v>
+        <v>0.03410117434508995</v>
       </c>
       <c r="G36" t="n">
         <v>2213.999999999999</v>
@@ -1432,10 +1432,10 @@
         <v>44701</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.07799999999988358</v>
+        <v>-0.06699999999837018</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.002892561983278653</v>
+        <v>-0.002644628099231281</v>
       </c>
       <c r="G37" t="n">
         <v>1210</v>
@@ -1459,10 +1459,10 @@
         <v>44707</v>
       </c>
       <c r="E38" t="n">
-        <v>-30.19199999999837</v>
+        <v>-30.12200000000303</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3814636616865382</v>
+        <v>-0.3813117244872531</v>
       </c>
       <c r="G38" t="n">
         <v>3949.000000000001</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>57.16599999999744</v>
+        <v>138.9049999999988</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05969600579036079</v>
+        <v>0.2048799070493914</v>
       </c>
       <c r="G39" t="n">
         <v>52501.0000000002</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>23.49400000000023</v>
+        <v>25.60999999999767</v>
       </c>
       <c r="F40" t="n">
-        <v>5.134412955467231</v>
+        <v>5.234008097166154</v>
       </c>
       <c r="G40" t="n">
         <v>246.9999999999345</v>
@@ -1540,10 +1540,10 @@
         <v>44724</v>
       </c>
       <c r="E41" t="n">
-        <v>9.134000000002562</v>
+        <v>9.844000000000232</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6633423180589162</v>
+        <v>0.6633423180597006</v>
       </c>
       <c r="G41" t="n">
         <v>742.0000000000073</v>
@@ -1567,7 +1567,7 @@
         <v>44682</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.6780000000000654</v>
+        <v>-0.67599999999984</v>
       </c>
       <c r="F42" t="n">
         <v>-0.1857142857142424</v>
@@ -1594,10 +1594,10 @@
         <v>44712</v>
       </c>
       <c r="E43" t="n">
-        <v>4.660999999998603</v>
+        <v>4.689000000001397</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06527429685325098</v>
+        <v>0.06530214424954535</v>
       </c>
       <c r="G43" t="n">
         <v>3590.999999999985</v>
@@ -1621,10 +1621,10 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>-9.368999999994411</v>
+        <v>-9.259999999997671</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.5400932400928649</v>
+        <v>-0.5391608391609523</v>
       </c>
       <c r="G44" t="n">
         <v>857.9999999999927</v>
@@ -1648,10 +1648,10 @@
         <v>44725</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.808000000000175</v>
+        <v>-1.803000000000611</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.2708708708709899</v>
+        <v>-0.2705705705706284</v>
       </c>
       <c r="G45" t="n">
         <v>333.0000000000041</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.930000000000291</v>
+        <v>-0.6209999999999127</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3272151898733105</v>
+        <v>-0.0658227848101825</v>
       </c>
       <c r="G46" t="n">
         <v>157.9999999999984</v>
@@ -1702,10 +1702,10 @@
         <v>44729</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4470000000030268</v>
+        <v>0.4809999999997672</v>
       </c>
       <c r="F47" t="n">
-        <v>0.03742236024805052</v>
+        <v>0.03726708074570415</v>
       </c>
       <c r="G47" t="n">
         <v>643.9999999999827</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>19.77200000000303</v>
+        <v>20.65599999999977</v>
       </c>
       <c r="F48" t="n">
-        <v>1.970229007634432</v>
+        <v>1.971755725189773</v>
       </c>
       <c r="G48" t="n">
         <v>524.0000000000236</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.3730000000000018</v>
+        <v>-0.3679999999999836</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.4918918918918166</v>
+        <v>-0.5081081081081411</v>
       </c>
       <c r="G49" t="n">
         <v>36.99999999999974</v>
@@ -1783,10 +1783,10 @@
         <v>44732</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.228000000002794</v>
+        <v>-1.096000000002096</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1086956521739142</v>
+        <v>-0.1079051383403362</v>
       </c>
       <c r="G50" t="n">
         <v>505.9999999999945</v>
@@ -1810,10 +1810,10 @@
         <v>44731</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.344000000000233</v>
+        <v>-1.336999999999534</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1457516339869778</v>
+        <v>-0.1455337690630276</v>
       </c>
       <c r="G51" t="n">
         <v>459.0000000000032</v>
@@ -1837,10 +1837,10 @@
         <v>44730</v>
       </c>
       <c r="E52" t="n">
-        <v>-3.687999999988824</v>
+        <v>-3.673999999999069</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.08777459407778697</v>
+        <v>-0.08767908309504678</v>
       </c>
       <c r="G52" t="n">
         <v>2093.99999999996</v>
@@ -1864,10 +1864,10 @@
         <v>44616</v>
       </c>
       <c r="E53" t="n">
-        <v>-26.40399999999208</v>
+        <v>-26.16899999999441</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1707110241356521</v>
+        <v>-0.1706979778212238</v>
       </c>
       <c r="G53" t="n">
         <v>7664.999999999964</v>
@@ -1891,10 +1891,10 @@
         <v>44682</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.579999999999927</v>
+        <v>-1.578999999999724</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.645833333332816</v>
+        <v>-1.643749999999816</v>
       </c>
       <c r="G54" t="n">
         <v>48.00000000000182</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>3.168000000005122</v>
+        <v>3.359999999997672</v>
       </c>
       <c r="F55" t="n">
-        <v>0.03358042994810163</v>
+        <v>0.06371386211988288</v>
       </c>
       <c r="G55" t="n">
         <v>2697.999999999956</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>0.45</v>
+        <v>6.243000000005122</v>
       </c>
       <c r="F56" t="n">
-        <v>0.03262032085564602</v>
+        <v>0.4402406417119137</v>
       </c>
       <c r="G56" t="n">
         <v>748.0000000000018</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3489999999999782</v>
+        <v>-0.3400000000000546</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.630000000000202</v>
+        <v>-1.770000000000537</v>
       </c>
       <c r="G57" t="n">
         <v>9.999999999999432</v>
@@ -1999,10 +1999,10 @@
         <v>44638</v>
       </c>
       <c r="E58" t="n">
-        <v>-40.98699999999953</v>
+        <v>-40.77199999999721</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1660613956517751</v>
+        <v>-0.1659311131015624</v>
       </c>
       <c r="G58" t="n">
         <v>12280.99999999995</v>
@@ -2029,7 +2029,7 @@
         <v>-0.2339999999999691</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.462499999999554</v>
+        <v>-1.462500000000122</v>
       </c>
       <c r="G59" t="n">
         <v>7.999999999999829</v>
@@ -2053,7 +2053,7 @@
         <v>44600</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.39399999999996</v>
+        <v>-0.3940000000000509</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5051282051282697</v>
@@ -2080,7 +2080,7 @@
         <v>44724</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3660000000000764</v>
+        <v>-0.3659999999999854</v>
       </c>
       <c r="F61" t="n">
         <v>-0.4255813953488276</v>
@@ -2107,10 +2107,10 @@
         <v>44620</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8399999999999637</v>
+        <v>-0.8409999999999854</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.003885914712939936</v>
+        <v>-0.003876684511723027</v>
       </c>
       <c r="G62" t="n">
         <v>10834</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>110.9260000000009</v>
+        <v>122.45</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8897837668444141</v>
+        <v>1.028611720463933</v>
       </c>
       <c r="G63" t="n">
         <v>6381.999999999971</v>
@@ -2161,7 +2161,7 @@
         <v>44720</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5589999999996508</v>
+        <v>-0.55</v>
       </c>
       <c r="F64" t="n">
         <v>-0.01948972360028331</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>-3.966999999999826</v>
+        <v>-3.952999999999883</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4962311557788958</v>
+        <v>-0.4969849246230876</v>
       </c>
       <c r="G65" t="n">
         <v>397.999999999999</v>
@@ -2215,10 +2215,10 @@
         <v>44730</v>
       </c>
       <c r="E66" t="n">
-        <v>-8.75</v>
+        <v>-8.726999999996043</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2187875751502185</v>
+        <v>-0.2184368737473779</v>
       </c>
       <c r="G66" t="n">
         <v>1996.000000000004</v>
@@ -2242,7 +2242,7 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>8.984000000002561</v>
+        <v>9.143999999994412</v>
       </c>
       <c r="F67" t="n">
         <v>1.745038167937786</v>
@@ -2269,7 +2269,7 @@
         <v>44707</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.1269999999999982</v>
+        <v>-0.1260000000000218</v>
       </c>
       <c r="F68" t="n">
         <v>-0.4500000000000761</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>4.004000000000815</v>
+        <v>4.90799999999872</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4826506024096264</v>
+        <v>0.5898795180725609</v>
       </c>
       <c r="G69" t="n">
         <v>414.9999999999864</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.69900000000016</v>
+        <v>-0.694999999999709</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.1191780821917652</v>
+        <v>-0.1188356164382708</v>
       </c>
       <c r="G70" t="n">
         <v>292.0000000000016</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.05099999999984</v>
+        <v>-1.029999999999927</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.2413636363635256</v>
+        <v>-0.2268181818182499</v>
       </c>
       <c r="G71" t="n">
         <v>220.0000000000045</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>21.79400000000023</v>
+        <v>21.96899999999441</v>
       </c>
       <c r="F72" t="n">
-        <v>1.334662998624872</v>
+        <v>1.687345254470207</v>
       </c>
       <c r="G72" t="n">
         <v>726.9999999999982</v>
@@ -2404,10 +2404,10 @@
         <v>44713</v>
       </c>
       <c r="E73" t="n">
-        <v>-2.991999999999825</v>
+        <v>-2.963000000000465</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7300492610840977</v>
+        <v>-0.7295566502462005</v>
       </c>
       <c r="G73" t="n">
         <v>202.9999999999973</v>
@@ -2431,10 +2431,10 @@
         <v>44614</v>
       </c>
       <c r="E74" t="n">
-        <v>-4.359000000000378</v>
+        <v>-4.360000000000582</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.787364620938812</v>
+        <v>-0.7866425992780151</v>
       </c>
       <c r="G74" t="n">
         <v>276.9999999999982</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>5.05</v>
+        <v>7.190000000002328</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5885057471272211</v>
+        <v>0.2379310344822159</v>
       </c>
       <c r="G75" t="n">
         <v>870.0000000000273</v>
@@ -2485,10 +2485,10 @@
         <v>44734</v>
       </c>
       <c r="E76" t="n">
-        <v>-27.4219999999972</v>
+        <v>-27.40499999999884</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.6935728744938605</v>
+        <v>-0.6933198380566725</v>
       </c>
       <c r="G76" t="n">
         <v>1976.000000000022</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>5.637999999994645</v>
+        <v>5.723999999999068</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1253286590708874</v>
+        <v>0.1255039439089122</v>
       </c>
       <c r="G77" t="n">
         <v>2282.000000000016</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>3.354000000000087</v>
+        <v>2.798999999999796</v>
       </c>
       <c r="F78" t="n">
-        <v>0.25064432989687</v>
+        <v>0.110051546391764</v>
       </c>
       <c r="G78" t="n">
         <v>775.9999999999991</v>
@@ -2566,10 +2566,10 @@
         <v>44701</v>
       </c>
       <c r="E79" t="n">
-        <v>1.095000000001164</v>
+        <v>1.616000000000349</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5050000000010474</v>
+        <v>0.5049999999992284</v>
       </c>
       <c r="G79" t="n">
         <v>159.9999999999909</v>
@@ -2593,10 +2593,10 @@
         <v>44734</v>
       </c>
       <c r="E80" t="n">
-        <v>5.478000000002794</v>
+        <v>5.502999999996973</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5159474671669809</v>
+        <v>0.516510318948777</v>
       </c>
       <c r="G80" t="n">
         <v>532.9999999999984</v>
@@ -2620,7 +2620,7 @@
         <v>44355</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.427000000000407</v>
+        <v>-3.416000000000349</v>
       </c>
       <c r="F81" t="n">
         <v>-0.1173076923077047</v>
@@ -2647,10 +2647,10 @@
         <v>44699</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.4550000000000182</v>
+        <v>-0.4529999999999745</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.7062500000000833</v>
+        <v>-0.7093749999998673</v>
       </c>
       <c r="G82" t="n">
         <v>31.99999999999932</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.275</v>
+        <v>-0.2960000000000036</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.6041666666665679</v>
+        <v>-0.6291666666667338</v>
       </c>
       <c r="G83" t="n">
         <v>24.00000000000091</v>
@@ -2701,10 +2701,10 @@
         <v>44735</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8939999999973225</v>
+        <v>-0.8879999999975553</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.004955910257811395</v>
+        <v>-0.00495591025784388</v>
       </c>
       <c r="G84" t="n">
         <v>8958.999999999993</v>
@@ -2728,10 +2728,10 @@
         <v>44727</v>
       </c>
       <c r="E85" t="n">
-        <v>2.440000000002328</v>
+        <v>2.506000000005588</v>
       </c>
       <c r="F85" t="n">
-        <v>0.07974603174638653</v>
+        <v>0.07936507936507936</v>
       </c>
       <c r="G85" t="n">
         <v>1575</v>
@@ -2755,10 +2755,10 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>-9.648000000001048</v>
+        <v>-9.612999999997555</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.4109401709400679</v>
+        <v>-0.4106837606836676</v>
       </c>
       <c r="G86" t="n">
         <v>1169.999999999982</v>
@@ -2782,7 +2782,7 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.386000000000058</v>
+        <v>-1.436000000000058</v>
       </c>
       <c r="F87" t="n">
         <v>-2.39333333333334</v>
@@ -2809,10 +2809,10 @@
         <v>44361</v>
       </c>
       <c r="E88" t="n">
-        <v>-6.01700000000128</v>
+        <v>-6.127999999999884</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.2000000000000905</v>
+        <v>-0.1999999999999006</v>
       </c>
       <c r="G88" t="n">
         <v>1532.000000000005</v>
@@ -2836,10 +2836,10 @@
         <v>44147</v>
       </c>
       <c r="E89" t="n">
-        <v>-2.761000000000058</v>
+        <v>-2.766999999999825</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.3629921259842978</v>
+        <v>-0.3632545931757614</v>
       </c>
       <c r="G89" t="n">
         <v>381</v>
@@ -2863,10 +2863,10 @@
         <v>44731</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.3549999999988359</v>
+        <v>5.777000000001863</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.02861952861923438</v>
+        <v>1.001178451178462</v>
       </c>
       <c r="G90" t="n">
         <v>594.0000000000055</v>
@@ -2890,10 +2890,10 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.9800000000046566</v>
+        <v>-3.443999999994412</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.1069367088607359</v>
+        <v>0.01974683544315586</v>
       </c>
       <c r="G91" t="n">
         <v>3950</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.6110000000000582</v>
+        <v>-0.5830000000001746</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.7820512820519416</v>
+        <v>-0.7128205128201353</v>
       </c>
       <c r="G92" t="n">
         <v>39.00000000000432</v>
@@ -2944,7 +2944,7 @@
         <v>44717</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6569999999999709</v>
+        <v>-0.6560000000001309</v>
       </c>
       <c r="F93" t="n">
         <v>-0.6560000000001309</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>31.93499999999767</v>
+        <v>40.07999999999883</v>
       </c>
       <c r="F94" t="n">
-        <v>9.913829787233716</v>
+        <v>11.40531914893464</v>
       </c>
       <c r="G94" t="n">
         <v>188.0000000000109</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>68.40000000000001</v>
+        <v>73.83799999998882</v>
       </c>
       <c r="F95" t="n">
-        <v>2.240414798206061</v>
+        <v>1.89848654708497</v>
       </c>
       <c r="G95" t="n">
         <v>1783.999999999924</v>
@@ -3025,10 +3025,10 @@
         <v>44734</v>
       </c>
       <c r="E96" t="n">
-        <v>19.01199999999954</v>
+        <v>19.61599999999744</v>
       </c>
       <c r="F96" t="n">
-        <v>1.388951841359751</v>
+        <v>1.389518413597415</v>
       </c>
       <c r="G96" t="n">
         <v>705.9999999999945</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.186999999999534</v>
+        <v>-1.181999999999971</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.5230088495571893</v>
+        <v>-0.5230088495578333</v>
       </c>
       <c r="G97" t="n">
         <v>112.9999999999995</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>16.79100000000035</v>
+        <v>23.45599999999977</v>
       </c>
       <c r="F98" t="n">
-        <v>0.339451114922853</v>
+        <v>0.4652144082332282</v>
       </c>
       <c r="G98" t="n">
         <v>2915</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.1929999999999836</v>
+        <v>-0.1720000000000255</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.7800000000002029</v>
+        <v>-1.000000000000004</v>
       </c>
       <c r="G99" t="n">
         <v>9.999999999999964</v>
@@ -3133,10 +3133,10 @@
         <v>44634</v>
       </c>
       <c r="E100" t="n">
-        <v>-4.811999999999534</v>
+        <v>-4.830999999999767</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.09606205250605795</v>
+        <v>-0.09610182975327794</v>
       </c>
       <c r="G100" t="n">
         <v>2514.000000000033</v>
@@ -3160,10 +3160,10 @@
         <v>44730</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.151000000000204</v>
+        <v>-1.133000000000175</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.7710144927546381</v>
+        <v>-0.8710144927528669</v>
       </c>
       <c r="G101" t="n">
         <v>68.99999999999977</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>6.185000000000582</v>
+        <v>8.726000000000932</v>
       </c>
       <c r="F102" t="n">
-        <v>1.329924242424823</v>
+        <v>1.975378787878578</v>
       </c>
       <c r="G102" t="n">
         <v>263.9999999999986</v>
@@ -3214,10 +3214,10 @@
         <v>44724</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.1519999999999982</v>
+        <v>-0.1440000000000055</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.357894736842143</v>
+        <v>-0.4</v>
       </c>
       <c r="G103" t="n">
         <v>18.99999999999977</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>86.93699999999953</v>
+        <v>76.25199999999896</v>
       </c>
       <c r="F104" t="n">
-        <v>2.216204913747985</v>
+        <v>1.769785676947181</v>
       </c>
       <c r="G104" t="n">
         <v>1913.000000000011</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.1339999999998326</v>
+        <v>-0.1789999999999054</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.105970149253603</v>
+        <v>-0.1611940298507384</v>
       </c>
       <c r="G105" t="n">
         <v>66.99999999999875</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>-13.38799999999464</v>
+        <v>-13.3359999999986</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.9768667642747925</v>
+        <v>-0.9756954612007356</v>
       </c>
       <c r="G106" t="n">
         <v>683.0000000000382</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>125.3700000000012</v>
+        <v>217.8150000000023</v>
       </c>
       <c r="F107" t="n">
-        <v>22.99697885196448</v>
+        <v>42.80815709969895</v>
       </c>
       <c r="G107" t="n">
         <v>330.9999999999945</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.7469999999999345</v>
+        <v>-0.7260000000000219</v>
       </c>
       <c r="F108" t="n">
-        <v>-2.318749999999969</v>
+        <v>-2.331249999999673</v>
       </c>
       <c r="G108" t="n">
         <v>16.00000000000037</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>-1.315999999999985</v>
+        <v>-1.314000000000124</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.4500000000000967</v>
+        <v>-0.4624999999999906</v>
       </c>
       <c r="G109" t="n">
         <v>143.9999999999998</v>
@@ -3403,10 +3403,10 @@
         <v>44724</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.4079999999999927</v>
+        <v>-0.4089999999999236</v>
       </c>
       <c r="F110" t="n">
-        <v>-2.049999999999316</v>
+        <v>-2.040000000000007</v>
       </c>
       <c r="G110" t="n">
         <v>9.999999999999787</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>3.551999999998952</v>
+        <v>6.786999999999535</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.4398437499999812</v>
+        <v>0.286458333333331</v>
       </c>
       <c r="G111" t="n">
         <v>768.0000000000064</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>-4.108000000000175</v>
+        <v>-3.65399999999936</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.5237822349569853</v>
+        <v>-0.6461318051574664</v>
       </c>
       <c r="G112" t="n">
         <v>349.0000000000009</v>
@@ -3484,10 +3484,10 @@
         <v>44696</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.04399999999999978</v>
+        <v>-0.04500000000000455</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.3666666666667199</v>
+        <v>-0.3833333333333718</v>
       </c>
       <c r="G113" t="n">
         <v>5.999999999999872</v>
@@ -3511,7 +3511,7 @@
         <v>44622</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.09099999999998545</v>
+        <v>-0.09200000000000727</v>
       </c>
       <c r="F114" t="n">
         <v>-0.07796610169492144</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02600000000002183</v>
+        <v>-0.003000000000020009</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.009523809523800825</v>
+        <v>-0.004761904762008684</v>
       </c>
       <c r="G115" t="n">
         <v>21.00000000000009</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>-7.284999999997671</v>
+        <v>-6.203000000002794</v>
       </c>
       <c r="F116" t="n">
-        <v>-1.551776649743571</v>
+        <v>-1.665482233505352</v>
       </c>
       <c r="G116" t="n">
         <v>197.0000000000027</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>12.62199999999721</v>
+        <v>15.32600000000093</v>
       </c>
       <c r="F117" t="n">
-        <v>3.513452914797134</v>
+        <v>3.359192825113542</v>
       </c>
       <c r="G117" t="n">
         <v>223.0000000000018</v>
@@ -3619,10 +3619,10 @@
         <v>44732</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1470000000001164</v>
+        <v>0.1440000000002328</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1044117647068229</v>
+        <v>0.1073529411758703</v>
       </c>
       <c r="G118" t="n">
         <v>68.00000000000068</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>107.9030000000028</v>
+        <v>90.04699999999721</v>
       </c>
       <c r="F119" t="n">
-        <v>12.52843822843768</v>
+        <v>8.461538461538533</v>
       </c>
       <c r="G119" t="n">
         <v>428.9999999999964</v>
@@ -3673,10 +3673,10 @@
         <v>44733</v>
       </c>
       <c r="E120" t="n">
-        <v>4.075</v>
+        <v>3.955000000001746</v>
       </c>
       <c r="F120" t="n">
-        <v>2.355952380953581</v>
+        <v>2.352380952382291</v>
       </c>
       <c r="G120" t="n">
         <v>83.99999999999181</v>
@@ -3700,10 +3700,10 @@
         <v>44735</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.3780000000000655</v>
+        <v>-0.3789999999999963</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.5250000000000917</v>
+        <v>-0.5277777777776775</v>
       </c>
       <c r="G121" t="n">
         <v>35.99999999999994</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>-8.194000000000234</v>
+        <v>-8.287999999997556</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.2770891364901023</v>
+        <v>-0.3000696378829814</v>
       </c>
       <c r="G122" t="n">
         <v>1436.000000000013</v>
@@ -3754,10 +3754,10 @@
         <v>44656</v>
       </c>
       <c r="E123" t="n">
-        <v>-5.332000000000699</v>
+        <v>-5.317000000001281</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.2604309500492244</v>
+        <v>-0.2603330068559001</v>
       </c>
       <c r="G123" t="n">
         <v>1020.999999999992</v>
@@ -3781,10 +3781,10 @@
         <v>44680</v>
       </c>
       <c r="E124" t="n">
-        <v>-1.116000000000349</v>
+        <v>-1.114999999999418</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.4455999999999767</v>
+        <v>-0.4463999999995576</v>
       </c>
       <c r="G124" t="n">
         <v>125</v>
@@ -3808,10 +3808,10 @@
         <v>44733</v>
       </c>
       <c r="E125" t="n">
-        <v>2.484999999997672</v>
+        <v>2.485999999998603</v>
       </c>
       <c r="F125" t="n">
-        <v>0.02745792736927616</v>
+        <v>0.02759078830828387</v>
       </c>
       <c r="G125" t="n">
         <v>4515.999999999985</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>10.03400000000256</v>
+        <v>11.27999999999884</v>
       </c>
       <c r="F126" t="n">
-        <v>8.830645161290258</v>
+        <v>9.362903225804505</v>
       </c>
       <c r="G126" t="n">
         <v>62.00000000000045</v>
@@ -3862,10 +3862,10 @@
         <v>44730</v>
       </c>
       <c r="E127" t="n">
-        <v>2.930000000004656</v>
+        <v>3.165000000002328</v>
       </c>
       <c r="F127" t="n">
-        <v>0.2548387096781686</v>
+        <v>0.2556451612899452</v>
       </c>
       <c r="G127" t="n">
         <v>620.0000000000045</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>50.56000000000931</v>
+        <v>41.57399999999907</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7047303404640545</v>
+        <v>0.5486592347095219</v>
       </c>
       <c r="G129" t="n">
         <v>3319.000000000051</v>
@@ -3943,7 +3943,7 @@
         <v>44647</v>
       </c>
       <c r="E130" t="n">
-        <v>-4.933999999999651</v>
+        <v>-4.927999999999884</v>
       </c>
       <c r="F130" t="n">
         <v>-1.339130434782554</v>
@@ -3970,10 +3970,10 @@
         <v>44635</v>
       </c>
       <c r="E131" t="n">
-        <v>-8.355000000000292</v>
+        <v>-8.401000000000931</v>
       </c>
       <c r="F131" t="n">
-        <v>-2.387500000000231</v>
+        <v>-2.385795454545752</v>
       </c>
       <c r="G131" t="n">
         <v>176</v>
@@ -3997,10 +3997,10 @@
         <v>44734</v>
       </c>
       <c r="E132" t="n">
-        <v>-14.3429999999993</v>
+        <v>-14.30499999999884</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.1918744971842007</v>
+        <v>-0.1917404129793512</v>
       </c>
       <c r="G132" t="n">
         <v>3728.999999999996</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>13.12000000000116</v>
+        <v>19.54800000000105</v>
       </c>
       <c r="F133" t="n">
-        <v>0.2863967906637441</v>
+        <v>0.4265134938001872</v>
       </c>
       <c r="G133" t="n">
         <v>2742.000000000007</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>11.3179999999993</v>
+        <v>11.09599999999918</v>
       </c>
       <c r="F134" t="n">
-        <v>0.8117647058821016</v>
+        <v>0.8200000000001424</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.76299999999992</v>
+        <v>-0.7649999999999636</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.153086419753059</v>
+        <v>-0.1617283950617399</v>
       </c>
       <c r="G135" t="n">
         <v>243.0000000000007</v>
@@ -4105,10 +4105,10 @@
         <v>44734</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.705999999999767</v>
+        <v>-1.686999999999898</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.1478108581435838</v>
+        <v>-0.1476357267951005</v>
       </c>
       <c r="G136" t="n">
         <v>571.0000000000036</v>
@@ -4132,10 +4132,10 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.4139999999999418</v>
+        <v>-0.2899999999999636</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.3645161290319972</v>
+        <v>-0.6935483870966518</v>
       </c>
       <c r="G137" t="n">
         <v>31.00000000000023</v>
@@ -4159,10 +4159,10 @@
         <v>44732</v>
       </c>
       <c r="E138" t="n">
-        <v>-13.11900000000023</v>
+        <v>-12.99699999999721</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.2110389610389611</v>
+        <v>-0.2109415584414678</v>
       </c>
       <c r="G138" t="n">
         <v>3080</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.3390000000003056</v>
+        <v>-0.3690000000002328</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.03268858800778224</v>
+        <v>-0.03868471953578367</v>
       </c>
       <c r="G139" t="n">
         <v>516.9999999999959</v>
@@ -4213,10 +4213,10 @@
         <v>44734</v>
       </c>
       <c r="E140" t="n">
-        <v>10.14400000000023</v>
+        <v>10.30999999999767</v>
       </c>
       <c r="F140" t="n">
-        <v>0.8003105590059073</v>
+        <v>0.8006211180124077</v>
       </c>
       <c r="G140" t="n">
         <v>643.9999999999827</v>
@@ -4240,10 +4240,10 @@
         <v>44717</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.1320000000000164</v>
+        <v>-0.1240000000000009</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.1033333333333528</v>
+        <v>-0.1033333333333149</v>
       </c>
       <c r="G141" t="n">
         <v>60.00000000000014</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>-2.203000000000247</v>
+        <v>-2.202999999999883</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.3203488372093152</v>
+        <v>-0.3200581395348374</v>
       </c>
       <c r="G142" t="n">
         <v>343.9999999999998</v>
@@ -4294,10 +4294,10 @@
         <v>44734</v>
       </c>
       <c r="E143" t="n">
-        <v>-4.108999999999651</v>
+        <v>-4.101999999998952</v>
       </c>
       <c r="F143" t="n">
-        <v>-7.307407407405622</v>
+        <v>-7.885185185182515</v>
       </c>
       <c r="G143" t="n">
         <v>27.00000000000102</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>8.114000000001397</v>
+        <v>8.609999999997672</v>
       </c>
       <c r="F144" t="n">
-        <v>1.57289377289411</v>
+        <v>1.580952380951696</v>
       </c>
       <c r="G144" t="n">
         <v>272.9999999999563</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>8.240000000002329</v>
+        <v>10.46600000000326</v>
       </c>
       <c r="F145" t="n">
-        <v>0.458969465648632</v>
+        <v>0.5402671755735845</v>
       </c>
       <c r="G145" t="n">
         <v>1048.000000000002</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>0.7229999999981374</v>
+        <v>2.195999999999185</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3981366459611669</v>
+        <v>0.9658385093179148</v>
       </c>
       <c r="G146" t="n">
         <v>160.99999999999</v>
@@ -4402,10 +4402,10 @@
         <v>44724</v>
       </c>
       <c r="E147" t="n">
-        <v>-2.483000000000175</v>
+        <v>-2.495999999999913</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.6183168316830731</v>
+        <v>-0.6173267326733305</v>
       </c>
       <c r="G147" t="n">
         <v>201.9999999999982</v>
@@ -4429,10 +4429,10 @@
         <v>44667</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.3460000000000036</v>
+        <v>-0.3420000000000073</v>
       </c>
       <c r="F148" t="n">
-        <v>-5.733333333334135</v>
+        <v>-5.666666666666013</v>
       </c>
       <c r="G148" t="n">
         <v>3.000000000000025</v>
@@ -4456,10 +4456,10 @@
         <v>44699</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.05200000000000386</v>
+        <v>-0.05099999999999909</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.6249999999999856</v>
+        <v>-0.6499999999999623</v>
       </c>
       <c r="G149" t="n">
         <v>4.000000000000092</v>
@@ -4483,10 +4483,10 @@
         <v>44734</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.3460000000000036</v>
+        <v>-0.3449999999999818</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.5766666666665267</v>
+        <v>-0.5733333333334236</v>
       </c>
       <c r="G150" t="n">
         <v>29.99999999999972</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>3.491000000000349</v>
+        <v>3.063000000000466</v>
       </c>
       <c r="F151" t="n">
-        <v>1.365137614679358</v>
+        <v>1.4449541284404</v>
       </c>
       <c r="G151" t="n">
         <v>108.9999999999975</v>
@@ -4537,10 +4537,10 @@
         <v>44614</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.8139999999999418</v>
+        <v>-0.8200000000000728</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.1301587301586837</v>
+        <v>-0.1301587301587992</v>
       </c>
       <c r="G152" t="n">
         <v>315.0000000000006</v>
@@ -4564,10 +4564,10 @@
         <v>44734</v>
       </c>
       <c r="E153" t="n">
-        <v>-1.127000000000407</v>
+        <v>-1.093000000000757</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.1610619469028444</v>
+        <v>-0.1613569321534273</v>
       </c>
       <c r="G153" t="n">
         <v>338.9999999999986</v>
@@ -4591,10 +4591,10 @@
         <v>44724</v>
       </c>
       <c r="E154" t="n">
-        <v>-2.108000000000175</v>
+        <v>-2.097000000000116</v>
       </c>
       <c r="F154" t="n">
-        <v>-1.840350877193924</v>
+        <v>-1.838596491227377</v>
       </c>
       <c r="G154" t="n">
         <v>56.99999999999932</v>
@@ -4618,10 +4618,10 @@
         <v>44712</v>
       </c>
       <c r="E155" t="n">
-        <v>-1.795999999999185</v>
+        <v>-1.802000000001863</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.08093525179856029</v>
+        <v>-0.08111510791383571</v>
       </c>
       <c r="G155" t="n">
         <v>1112.000000000012</v>
@@ -4645,10 +4645,10 @@
         <v>44699</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.3610000000000128</v>
+        <v>-0.3569999999999709</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.5176470588234655</v>
+        <v>-0.5323529411764604</v>
       </c>
       <c r="G156" t="n">
         <v>33.99999999999963</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>-15.3</v>
+        <v>-16.24700000000012</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.9662721893490384</v>
+        <v>-0.9564497041420893</v>
       </c>
       <c r="G157" t="n">
         <v>845.0000000000045</v>
@@ -4699,10 +4699,10 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>1.004000000003725</v>
+        <v>1.19199999999837</v>
       </c>
       <c r="F158" t="n">
-        <v>0.08663594470067552</v>
+        <v>0.09646697388586391</v>
       </c>
       <c r="G158" t="n">
         <v>650.9999999999991</v>
@@ -4726,10 +4726,10 @@
         <v>44730</v>
       </c>
       <c r="E159" t="n">
-        <v>-6.172000000003027</v>
+        <v>-6.145999999996275</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.3108190090999967</v>
+        <v>-0.3106167846306476</v>
       </c>
       <c r="G159" t="n">
         <v>989.0000000000327</v>
@@ -4753,10 +4753,10 @@
         <v>44733</v>
       </c>
       <c r="E160" t="n">
-        <v>2.551999999998952</v>
+        <v>2.552000000000407</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3786350148366265</v>
+        <v>0.3786350148370583</v>
       </c>
       <c r="G160" t="n">
         <v>337.0000000000118</v>
@@ -4780,10 +4780,10 @@
         <v>44731</v>
       </c>
       <c r="E161" t="n">
-        <v>10.39000000000233</v>
+        <v>10.37999999999884</v>
       </c>
       <c r="F161" t="n">
-        <v>1.365263157894876</v>
+        <v>1.366315789473272</v>
       </c>
       <c r="G161" t="n">
         <v>379.9999999999955</v>
@@ -4807,10 +4807,10 @@
         <v>44724</v>
       </c>
       <c r="E162" t="n">
-        <v>-2.676999999998952</v>
+        <v>-2.669000000000233</v>
       </c>
       <c r="F162" t="n">
-        <v>-133.5000000000341</v>
+        <v>-133.4000000002319</v>
       </c>
       <c r="G162" t="n">
         <v>0.9999999999990905</v>
@@ -4834,10 +4834,10 @@
         <v>44619</v>
       </c>
       <c r="E163" t="n">
-        <v>-3.168000000000029</v>
+        <v>-3.166999999999825</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.948502994011766</v>
+        <v>-0.9479041916168701</v>
       </c>
       <c r="G163" t="n">
         <v>167.0000000000002</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>-2.823999999999796</v>
+        <v>-2.786000000000058</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.821893491124227</v>
+        <v>-0.833727810650682</v>
       </c>
       <c r="G164" t="n">
         <v>168.9999999999998</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>-1.764999999999782</v>
+        <v>-1.470000000000073</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.9831168831168322</v>
+        <v>-1.145454545454492</v>
       </c>
       <c r="G165" t="n">
         <v>77.00000000000102</v>
@@ -4915,10 +4915,10 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>-1.155999999999949</v>
+        <v>-1.101000000000022</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.5029126213590744</v>
+        <v>-0.566019417475897</v>
       </c>
       <c r="G166" t="n">
         <v>103.0000000000001</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3260000000000218</v>
+        <v>-0.3299999999999727</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2323943661971956</v>
+        <v>-0.2323943661971316</v>
       </c>
       <c r="G2" t="n">
         <v>71.00000000000009</v>
@@ -514,10 +514,10 @@
         <v>44734</v>
       </c>
       <c r="E3" t="n">
-        <v>3.339999999999418</v>
+        <v>3.341000000000349</v>
       </c>
       <c r="F3" t="n">
-        <v>1.815217391303888</v>
+        <v>1.816304347826639</v>
       </c>
       <c r="G3" t="n">
         <v>92.00000000000728</v>
@@ -541,7 +541,7 @@
         <v>44609</v>
       </c>
       <c r="E4" t="n">
-        <v>-26.49000000000233</v>
+        <v>-26.48000000000466</v>
       </c>
       <c r="F4" t="n">
         <v>-1.206927985415002</v>
@@ -568,10 +568,10 @@
         <v>44735</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.70999999999913</v>
+        <v>-10.69899999999907</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02280649422593</v>
+        <v>-0.02278518771040251</v>
       </c>
       <c r="G5" t="n">
         <v>23466.99999999983</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.382000000000699</v>
+        <v>-2.464999999999418</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2143872113677974</v>
+        <v>-0.2239786856125407</v>
       </c>
       <c r="G6" t="n">
         <v>562.9999999999995</v>
@@ -622,10 +622,10 @@
         <v>44711</v>
       </c>
       <c r="E7" t="n">
-        <v>4.212000000002445</v>
+        <v>4.215000000002329</v>
       </c>
       <c r="F7" t="n">
-        <v>0.572282608695579</v>
+        <v>0.5728260869569547</v>
       </c>
       <c r="G7" t="n">
         <v>368.0000000000064</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.61600000000326</v>
+        <v>-16.61200000000536</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4583885209716136</v>
+        <v>-0.4583885209712923</v>
       </c>
       <c r="G8" t="n">
         <v>1811.999999999989</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>2.294999999995343</v>
+        <v>2.325</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01693035635066281</v>
+        <v>0.01744787816064822</v>
       </c>
       <c r="G9" t="n">
         <v>6763.000000000102</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9240000000005238</v>
+        <v>-0.3620000000009895</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.00445859872655973</v>
+        <v>-0.2261146496817232</v>
       </c>
       <c r="G10" t="n">
         <v>156.9999999999936</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>24.9039999999979</v>
+        <v>23.59099999999744</v>
       </c>
       <c r="F12" t="n">
-        <v>1.895936139332468</v>
+        <v>1.52714078374418</v>
       </c>
       <c r="G12" t="n">
         <v>688.9999999999873</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.04700000000000273</v>
+        <v>-0.08099999999999455</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3416666666666424</v>
+        <v>-0.3333333333333166</v>
       </c>
       <c r="G13" t="n">
         <v>11.99999999999992</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4730000000001383</v>
+        <v>-0.5100000000000364</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.540000000001017</v>
+        <v>-2.559999999999636</v>
       </c>
       <c r="G14" t="n">
         <v>9.999999999999432</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>6.312999999997555</v>
+        <v>7.959999999997672</v>
       </c>
       <c r="F15" t="n">
-        <v>1.086075949366361</v>
+        <v>1.432911392404989</v>
       </c>
       <c r="G15" t="n">
         <v>316.0000000000082</v>
@@ -865,10 +865,10 @@
         <v>44735</v>
       </c>
       <c r="E16" t="n">
-        <v>-37.47199999999721</v>
+        <v>-37.4359999999986</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6294789915965056</v>
+        <v>-0.628873949579918</v>
       </c>
       <c r="G16" t="n">
         <v>2975</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>42.96600000000035</v>
+        <v>31.99799999999959</v>
       </c>
       <c r="F17" t="n">
-        <v>3.311605415860885</v>
+        <v>2.877562862669066</v>
       </c>
       <c r="G17" t="n">
         <v>516.9999999999959</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>4.05399999999936</v>
+        <v>3.960000000000582</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2622162883845046</v>
+        <v>0.2664886515354657</v>
       </c>
       <c r="G18" t="n">
         <v>749.0000000000009</v>
@@ -946,10 +946,10 @@
         <v>44688</v>
       </c>
       <c r="E19" t="n">
-        <v>2.748999999999069</v>
+        <v>2.749000000000524</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2888655462184879</v>
+        <v>0.2886554621849846</v>
       </c>
       <c r="G19" t="n">
         <v>475.9999999999991</v>
@@ -973,10 +973,10 @@
         <v>44655</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.961999999999534</v>
+        <v>-8.717000000001281</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.43459357277893</v>
+        <v>-0.4119092627598062</v>
       </c>
       <c r="G20" t="n">
         <v>1057.999999999993</v>
@@ -1000,10 +1000,10 @@
         <v>44720</v>
       </c>
       <c r="E21" t="n">
-        <v>1.454000000003725</v>
+        <v>1.455999999999767</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005077416655062031</v>
+        <v>0.005077416655021434</v>
       </c>
       <c r="G21" t="n">
         <v>14338</v>
@@ -1027,7 +1027,7 @@
         <v>44729</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.072000000000116</v>
+        <v>-5.077999999999884</v>
       </c>
       <c r="F22" t="n">
         <v>-0.6975274725274483</v>
@@ -1054,10 +1054,10 @@
         <v>44607</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.604000000000815</v>
+        <v>-2.604999999998836</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1429670329671349</v>
+        <v>-0.1432967032964727</v>
       </c>
       <c r="G23" t="n">
         <v>910.0000000000023</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7809999999997672</v>
+        <v>31.78099999999977</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.03087885985766627</v>
+        <v>1.426365795724638</v>
       </c>
       <c r="G24" t="n">
         <v>1263.000000000011</v>
@@ -1108,7 +1108,7 @@
         <v>44619</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.97899999999936</v>
+        <v>-1.979999999998836</v>
       </c>
       <c r="F25" t="n">
         <v>-0.01310390469886718</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.344000000000233</v>
+        <v>-8.163999999998486</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2100308641974644</v>
+        <v>-0.209927983539082</v>
       </c>
       <c r="G26" t="n">
         <v>1944.000000000005</v>
@@ -1162,10 +1162,10 @@
         <v>44696</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3600000000000364</v>
+        <v>-0.3789999999999963</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.725000000000919</v>
+        <v>-4.749999999999192</v>
       </c>
       <c r="G27" t="n">
         <v>3.999999999999915</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.013999999999942</v>
+        <v>-2.49600000000064</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2163306451615099</v>
+        <v>-0.2868951612902515</v>
       </c>
       <c r="G28" t="n">
         <v>495.9999999999809</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>2.011999999999534</v>
+        <v>2.439999999996508</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1754433833558821</v>
+        <v>0.1574351978169053</v>
       </c>
       <c r="G29" t="n">
         <v>732.9999999999927</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.363000000000466</v>
+        <v>-4.234000000002561</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.09113036303640926</v>
+        <v>-0.083539603960396</v>
       </c>
       <c r="G30" t="n">
         <v>2424.000000000001</v>
@@ -1270,7 +1270,7 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2489999999999782</v>
+        <v>-0.2539999999999963</v>
       </c>
       <c r="F31" t="n">
         <v>-0.4961538461538224</v>
@@ -1297,7 +1297,7 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1720000000000027</v>
+        <v>-0.07800000000000865</v>
       </c>
       <c r="F32" t="n">
         <v>-0.9500000000000755</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.409999999999127</v>
+        <v>-0.8990000000005238</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2183999999996741</v>
+        <v>-0.1412000000005355</v>
       </c>
       <c r="G33" t="n">
         <v>250</v>
@@ -1354,7 +1354,7 @@
         <v>-2.202999999999883</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2862337662338721</v>
+        <v>-0.2859740259738899</v>
       </c>
       <c r="G34" t="n">
         <v>385</v>
@@ -1378,10 +1378,10 @@
         <v>44710</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.132000000000699</v>
+        <v>0.7869999999995343</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1287227414330439</v>
+        <v>-0.1290965732087304</v>
       </c>
       <c r="G35" t="n">
         <v>1604.999999999995</v>
@@ -1405,10 +1405,10 @@
         <v>44381</v>
       </c>
       <c r="E36" t="n">
-        <v>1.509000000001106</v>
+        <v>1.509999999999127</v>
       </c>
       <c r="F36" t="n">
-        <v>0.03410117434508995</v>
+        <v>0.03410117434502422</v>
       </c>
       <c r="G36" t="n">
         <v>2213.999999999999</v>
@@ -1432,10 +1432,10 @@
         <v>44701</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.06699999999837018</v>
+        <v>-0.06500000000232831</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.002644628099231281</v>
+        <v>-0.002727272727407424</v>
       </c>
       <c r="G37" t="n">
         <v>1210</v>
@@ -1459,10 +1459,10 @@
         <v>44707</v>
       </c>
       <c r="E38" t="n">
-        <v>-30.12200000000303</v>
+        <v>-30.10400000000373</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3813117244872531</v>
+        <v>-0.381007850088683</v>
       </c>
       <c r="G38" t="n">
         <v>3949.000000000001</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>138.9049999999988</v>
+        <v>126.4370000000054</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2048799070493914</v>
+        <v>0.03594788670692727</v>
       </c>
       <c r="G39" t="n">
         <v>52501.0000000002</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>25.60999999999767</v>
+        <v>27.225</v>
       </c>
       <c r="F40" t="n">
-        <v>5.234008097166154</v>
+        <v>5.784615384617107</v>
       </c>
       <c r="G40" t="n">
         <v>246.9999999999345</v>
@@ -1540,10 +1540,10 @@
         <v>44724</v>
       </c>
       <c r="E41" t="n">
-        <v>9.844000000000232</v>
+        <v>9.847000000003026</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6633423180597006</v>
+        <v>0.6637466307277563</v>
       </c>
       <c r="G41" t="n">
         <v>742.0000000000073</v>
@@ -1567,10 +1567,10 @@
         <v>44682</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.67599999999984</v>
+        <v>-0.675</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1857142857142424</v>
+        <v>-0.1851648351648798</v>
       </c>
       <c r="G42" t="n">
         <v>181.9999999999993</v>
@@ -1594,10 +1594,10 @@
         <v>44712</v>
       </c>
       <c r="E43" t="n">
-        <v>4.689000000001397</v>
+        <v>4.689999999999418</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06530214424954535</v>
+        <v>0.0653021442494643</v>
       </c>
       <c r="G43" t="n">
         <v>3590.999999999985</v>
@@ -1621,10 +1621,10 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>-9.259999999997671</v>
+        <v>-9.25</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.5391608391609523</v>
+        <v>-0.5389277389276349</v>
       </c>
       <c r="G44" t="n">
         <v>857.9999999999927</v>
@@ -1648,10 +1648,10 @@
         <v>44725</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.803000000000611</v>
+        <v>-1.802999999999884</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.2705705705706284</v>
+        <v>-0.2708708708707714</v>
       </c>
       <c r="G45" t="n">
         <v>333.0000000000041</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.6209999999999127</v>
+        <v>-0.1580000000001746</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0658227848101825</v>
+        <v>-0.03417721518992902</v>
       </c>
       <c r="G46" t="n">
         <v>157.9999999999984</v>
@@ -1705,7 +1705,7 @@
         <v>0.4809999999997672</v>
       </c>
       <c r="F47" t="n">
-        <v>0.03726708074570415</v>
+        <v>0.03742236024805052</v>
       </c>
       <c r="G47" t="n">
         <v>643.9999999999827</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>20.65599999999977</v>
+        <v>20.66900000000023</v>
       </c>
       <c r="F48" t="n">
-        <v>1.971755725189773</v>
+        <v>1.972709923665055</v>
       </c>
       <c r="G48" t="n">
         <v>524.0000000000236</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.3679999999999836</v>
+        <v>-0.3690000000000054</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.5081081081081411</v>
+        <v>-0.5054054054053794</v>
       </c>
       <c r="G49" t="n">
         <v>36.99999999999974</v>
@@ -1786,7 +1786,7 @@
         <v>-1.096000000002096</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1079051383403362</v>
+        <v>-0.1086956521739142</v>
       </c>
       <c r="G50" t="n">
         <v>505.9999999999945</v>
@@ -1810,7 +1810,7 @@
         <v>44731</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.336999999999534</v>
+        <v>-1.335999999998603</v>
       </c>
       <c r="F51" t="n">
         <v>-0.1455337690630276</v>
@@ -1837,10 +1837,10 @@
         <v>44730</v>
       </c>
       <c r="E52" t="n">
-        <v>-3.673999999999069</v>
+        <v>-3.66600000000326</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.08767908309504678</v>
+        <v>-0.08739255014293458</v>
       </c>
       <c r="G52" t="n">
         <v>2093.99999999996</v>
@@ -1864,10 +1864,10 @@
         <v>44616</v>
       </c>
       <c r="E53" t="n">
-        <v>-26.16899999999441</v>
+        <v>-26.15999999999767</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1706979778212238</v>
+        <v>-0.170593607305949</v>
       </c>
       <c r="G53" t="n">
         <v>7664.999999999964</v>
@@ -1891,10 +1891,10 @@
         <v>44682</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.578999999999724</v>
+        <v>-1.577000000000044</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.643749999999816</v>
+        <v>-1.641666666666817</v>
       </c>
       <c r="G54" t="n">
         <v>48.00000000000182</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>3.359999999997672</v>
+        <v>4.975999999995111</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06371386211988288</v>
+        <v>0.0679021497403598</v>
       </c>
       <c r="G55" t="n">
         <v>2697.999999999956</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>6.243000000005122</v>
+        <v>3.54100000000326</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4402406417119137</v>
+        <v>0.03315508021365465</v>
       </c>
       <c r="G56" t="n">
         <v>748.0000000000018</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3400000000000546</v>
+        <v>-0.3420000000000073</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.770000000000537</v>
+        <v>-1.769999999999628</v>
       </c>
       <c r="G57" t="n">
         <v>9.999999999999432</v>
@@ -1999,10 +1999,10 @@
         <v>44638</v>
       </c>
       <c r="E58" t="n">
-        <v>-40.77199999999721</v>
+        <v>-40.73300000000163</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1659311131015624</v>
+        <v>-0.1657438319355014</v>
       </c>
       <c r="G58" t="n">
         <v>12280.99999999995</v>
@@ -2026,7 +2026,7 @@
         <v>44724</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2339999999999691</v>
+        <v>-0.2340000000000146</v>
       </c>
       <c r="F59" t="n">
         <v>-1.462500000000122</v>
@@ -2080,10 +2080,10 @@
         <v>44724</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3659999999999854</v>
+        <v>-0.3649999999999636</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.4255813953488276</v>
+        <v>-0.423255813953428</v>
       </c>
       <c r="G61" t="n">
         <v>42.99999999999926</v>
@@ -2107,10 +2107,10 @@
         <v>44620</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8409999999999854</v>
+        <v>-0.8399999999999637</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.003876684511723027</v>
+        <v>-0.003876684511721348</v>
       </c>
       <c r="G62" t="n">
         <v>10834</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>122.45</v>
+        <v>138.2539999999921</v>
       </c>
       <c r="F63" t="n">
-        <v>1.028611720463933</v>
+        <v>1.136258226261416</v>
       </c>
       <c r="G63" t="n">
         <v>6381.999999999971</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>-3.952999999999883</v>
+        <v>-3.961000000000058</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4969849246230876</v>
+        <v>-0.4982412060301959</v>
       </c>
       <c r="G65" t="n">
         <v>397.999999999999</v>
@@ -2218,7 +2218,7 @@
         <v>-8.726999999996043</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2184368737473779</v>
+        <v>-0.2187875751502185</v>
       </c>
       <c r="G66" t="n">
         <v>1996.000000000004</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>9.143999999994412</v>
+        <v>9.144000000000233</v>
       </c>
       <c r="F67" t="n">
-        <v>1.745038167937786</v>
+        <v>1.745038167940008</v>
       </c>
       <c r="G67" t="n">
         <v>262.0000000000118</v>
@@ -2269,10 +2269,10 @@
         <v>44707</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.1260000000000218</v>
+        <v>-0.1269999999999982</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.4500000000000761</v>
+        <v>-0.4571428571427643</v>
       </c>
       <c r="G68" t="n">
         <v>14.00000000000006</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>4.90799999999872</v>
+        <v>5.135000000000582</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5898795180725609</v>
+        <v>0.6474698795179814</v>
       </c>
       <c r="G69" t="n">
         <v>414.9999999999864</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.694999999999709</v>
+        <v>-0.7110000000000583</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.1188356164382708</v>
+        <v>-0.1246575342466793</v>
       </c>
       <c r="G70" t="n">
         <v>292.0000000000016</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.029999999999927</v>
+        <v>-1.013000000000102</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.2268181818182499</v>
+        <v>-0.2336363636363324</v>
       </c>
       <c r="G71" t="n">
         <v>220.0000000000045</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>21.96899999999441</v>
+        <v>23.04700000000303</v>
       </c>
       <c r="F72" t="n">
-        <v>1.687345254470207</v>
+        <v>1.485557083906469</v>
       </c>
       <c r="G72" t="n">
         <v>726.9999999999982</v>
@@ -2404,7 +2404,7 @@
         <v>44713</v>
       </c>
       <c r="E73" t="n">
-        <v>-2.963000000000465</v>
+        <v>-2.961999999999534</v>
       </c>
       <c r="F73" t="n">
         <v>-0.7295566502462005</v>
@@ -2431,10 +2431,10 @@
         <v>44614</v>
       </c>
       <c r="E74" t="n">
-        <v>-4.360000000000582</v>
+        <v>-4.355999999999767</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7866425992780151</v>
+        <v>-0.7859205776172181</v>
       </c>
       <c r="G74" t="n">
         <v>276.9999999999982</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>7.190000000002328</v>
+        <v>-2.460000000009313</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2379310344822159</v>
+        <v>-0.5206896551729328</v>
       </c>
       <c r="G75" t="n">
         <v>870.0000000000273</v>
@@ -2485,10 +2485,10 @@
         <v>44734</v>
       </c>
       <c r="E76" t="n">
-        <v>-27.40499999999884</v>
+        <v>-27.39500000000116</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.6933198380566725</v>
+        <v>-0.6930668016194844</v>
       </c>
       <c r="G76" t="n">
         <v>1976.000000000022</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>5.723999999999068</v>
+        <v>51.56300000000046</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1255039439089122</v>
+        <v>1.283216476774821</v>
       </c>
       <c r="G77" t="n">
         <v>2282.000000000016</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>2.798999999999796</v>
+        <v>1.84800000000032</v>
       </c>
       <c r="F78" t="n">
-        <v>0.110051546391764</v>
+        <v>0.08737113402060366</v>
       </c>
       <c r="G78" t="n">
         <v>775.9999999999991</v>
@@ -2566,7 +2566,7 @@
         <v>44701</v>
       </c>
       <c r="E79" t="n">
-        <v>1.616000000000349</v>
+        <v>1.615999999997439</v>
       </c>
       <c r="F79" t="n">
         <v>0.5049999999992284</v>
@@ -2596,7 +2596,7 @@
         <v>5.502999999996973</v>
       </c>
       <c r="F80" t="n">
-        <v>0.516510318948777</v>
+        <v>0.5159474671669809</v>
       </c>
       <c r="G80" t="n">
         <v>532.9999999999984</v>
@@ -2620,10 +2620,10 @@
         <v>44355</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.416000000000349</v>
+        <v>-3.413999999999942</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.1173076923077047</v>
+        <v>-0.1171703296703141</v>
       </c>
       <c r="G81" t="n">
         <v>1455.999999999995</v>
@@ -2647,10 +2647,10 @@
         <v>44699</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.4529999999999745</v>
+        <v>-0.4539999999999964</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.7093749999998673</v>
+        <v>-0.7093750000001515</v>
       </c>
       <c r="G82" t="n">
         <v>31.99999999999932</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.2960000000000036</v>
+        <v>-0.3130000000000109</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.6291666666667338</v>
+        <v>-0.674999999999929</v>
       </c>
       <c r="G83" t="n">
         <v>24.00000000000091</v>
@@ -2701,10 +2701,10 @@
         <v>44735</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8879999999975553</v>
+        <v>-0.8870000000024447</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.00495591025784388</v>
+        <v>-0.004944748297825787</v>
       </c>
       <c r="G84" t="n">
         <v>8958.999999999993</v>
@@ -2731,7 +2731,7 @@
         <v>2.506000000005588</v>
       </c>
       <c r="F85" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.07974603174638653</v>
       </c>
       <c r="G85" t="n">
         <v>1575</v>
@@ -2755,10 +2755,10 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>-9.612999999997555</v>
+        <v>-9.607000000000699</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.4106837606836676</v>
+        <v>-0.410427350427516</v>
       </c>
       <c r="G86" t="n">
         <v>1169.999999999982</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.436000000000058</v>
+        <v>-1.435000000000218</v>
       </c>
       <c r="F87" t="n">
-        <v>-2.39333333333334</v>
+        <v>-2.39000000000054</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2809,10 +2809,10 @@
         <v>44361</v>
       </c>
       <c r="E88" t="n">
-        <v>-6.127999999999884</v>
+        <v>-6.126999999998953</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.1999999999999006</v>
+        <v>-0.1999347258485937</v>
       </c>
       <c r="G88" t="n">
         <v>1532.000000000005</v>
@@ -2836,10 +2836,10 @@
         <v>44147</v>
       </c>
       <c r="E89" t="n">
-        <v>-2.766999999999825</v>
+        <v>-2.765999999998894</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.3632545931757614</v>
+        <v>-0.3627296587924523</v>
       </c>
       <c r="G89" t="n">
         <v>381</v>
@@ -2863,10 +2863,10 @@
         <v>44731</v>
       </c>
       <c r="E90" t="n">
-        <v>5.777000000001863</v>
+        <v>5.219999999998254</v>
       </c>
       <c r="F90" t="n">
-        <v>1.001178451178462</v>
+        <v>-0.1223905723908848</v>
       </c>
       <c r="G90" t="n">
         <v>594.0000000000055</v>
@@ -2890,10 +2890,10 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>-3.443999999994412</v>
+        <v>-5.95</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01974683544315586</v>
+        <v>-0.1703797468355609</v>
       </c>
       <c r="G91" t="n">
         <v>3950</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.5830000000001746</v>
+        <v>-0.5819999999999709</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.7128205128201353</v>
+        <v>-0.7794871794873171</v>
       </c>
       <c r="G92" t="n">
         <v>39.00000000000432</v>
@@ -2944,10 +2944,10 @@
         <v>44717</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6560000000001309</v>
+        <v>-0.6559999999999491</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.6560000000001309</v>
+        <v>-0.6559999999997672</v>
       </c>
       <c r="G93" t="n">
         <v>50</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>40.07999999999883</v>
+        <v>53.43399999999674</v>
       </c>
       <c r="F94" t="n">
-        <v>11.40531914893464</v>
+        <v>17.01702127659389</v>
       </c>
       <c r="G94" t="n">
         <v>188.0000000000109</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>73.83799999998882</v>
+        <v>53.025</v>
       </c>
       <c r="F95" t="n">
-        <v>1.89848654708497</v>
+        <v>1.073766816143857</v>
       </c>
       <c r="G95" t="n">
         <v>1783.999999999924</v>
@@ -3025,10 +3025,10 @@
         <v>44734</v>
       </c>
       <c r="E96" t="n">
-        <v>19.61599999999744</v>
+        <v>19.62600000000093</v>
       </c>
       <c r="F96" t="n">
-        <v>1.389518413597415</v>
+        <v>1.390368271955147</v>
       </c>
       <c r="G96" t="n">
         <v>705.9999999999945</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.181999999999971</v>
+        <v>-1.181000000000495</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.5230088495578333</v>
+        <v>-0.5221238938054407</v>
       </c>
       <c r="G97" t="n">
         <v>112.9999999999995</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>23.45599999999977</v>
+        <v>35.56999999999825</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4652144082332282</v>
+        <v>0.7550257289879811</v>
       </c>
       <c r="G98" t="n">
         <v>2915</v>
@@ -3106,7 +3106,7 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.1720000000000255</v>
+        <v>-0.1929999999999836</v>
       </c>
       <c r="F99" t="n">
         <v>-1.000000000000004</v>
@@ -3133,10 +3133,10 @@
         <v>44634</v>
       </c>
       <c r="E100" t="n">
-        <v>-4.830999999999767</v>
+        <v>-4.829999999998836</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.09610182975327794</v>
+        <v>-0.09602227525860642</v>
       </c>
       <c r="G100" t="n">
         <v>2514.000000000033</v>
@@ -3160,10 +3160,10 @@
         <v>44730</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.133000000000175</v>
+        <v>-0.825</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.8710144927528669</v>
+        <v>-0.8927536231889149</v>
       </c>
       <c r="G101" t="n">
         <v>68.99999999999977</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>8.726000000000932</v>
+        <v>11.3609999999986</v>
       </c>
       <c r="F102" t="n">
-        <v>1.975378787878578</v>
+        <v>2.328409090909147</v>
       </c>
       <c r="G102" t="n">
         <v>263.9999999999986</v>
@@ -3214,7 +3214,7 @@
         <v>44724</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.1440000000000055</v>
+        <v>-0.1519999999999982</v>
       </c>
       <c r="F103" t="n">
         <v>-0.4</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>76.25199999999896</v>
+        <v>54.92399999999907</v>
       </c>
       <c r="F104" t="n">
-        <v>1.769785676947181</v>
+        <v>1.101306847882864</v>
       </c>
       <c r="G104" t="n">
         <v>1913.000000000011</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.1789999999999054</v>
+        <v>-0.2170000000000073</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.1611940298507384</v>
+        <v>-0.1626865671642038</v>
       </c>
       <c r="G105" t="n">
         <v>66.99999999999875</v>
@@ -3295,7 +3295,7 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>-13.3359999999986</v>
+        <v>-13.32800000000279</v>
       </c>
       <c r="F106" t="n">
         <v>-0.9756954612007356</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>217.8150000000023</v>
+        <v>251.8359999999986</v>
       </c>
       <c r="F107" t="n">
-        <v>42.80815709969895</v>
+        <v>33.27522658610249</v>
       </c>
       <c r="G107" t="n">
         <v>330.9999999999945</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.7260000000000219</v>
+        <v>-0.7429999999999382</v>
       </c>
       <c r="F108" t="n">
-        <v>-2.331249999999673</v>
+        <v>-2.324999999999537</v>
       </c>
       <c r="G108" t="n">
         <v>16.00000000000037</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>-1.314000000000124</v>
+        <v>-1.272999999999956</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.4624999999999906</v>
+        <v>-0.461805555555531</v>
       </c>
       <c r="G109" t="n">
         <v>143.9999999999998</v>
@@ -3403,10 +3403,10 @@
         <v>44724</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.4089999999999236</v>
+        <v>-0.4080000000000837</v>
       </c>
       <c r="F110" t="n">
-        <v>-2.040000000000007</v>
+        <v>-2.040000000000917</v>
       </c>
       <c r="G110" t="n">
         <v>9.999999999999787</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>6.786999999999535</v>
+        <v>-1.178999999997905</v>
       </c>
       <c r="F111" t="n">
-        <v>0.286458333333331</v>
+        <v>-0.4399739583330569</v>
       </c>
       <c r="G111" t="n">
         <v>768.0000000000064</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>-3.65399999999936</v>
+        <v>-4.309999999999855</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.6461318051574664</v>
+        <v>-0.6455587392549794</v>
       </c>
       <c r="G112" t="n">
         <v>349.0000000000009</v>
@@ -3484,10 +3484,10 @@
         <v>44696</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.04500000000000455</v>
+        <v>-0.04499999999999886</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.3833333333333718</v>
+        <v>-0.3666666666666252</v>
       </c>
       <c r="G113" t="n">
         <v>5.999999999999872</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.003000000000020009</v>
+        <v>-0.001999999999998181</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.004761904762008684</v>
+        <v>-0.004761904761792139</v>
       </c>
       <c r="G115" t="n">
         <v>21.00000000000009</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>-6.203000000002794</v>
+        <v>-6.625</v>
       </c>
       <c r="F116" t="n">
-        <v>-1.665482233505352</v>
+        <v>-1.73401015228294</v>
       </c>
       <c r="G116" t="n">
         <v>197.0000000000027</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>15.32600000000093</v>
+        <v>15.39100000000326</v>
       </c>
       <c r="F117" t="n">
-        <v>3.359192825113542</v>
+        <v>3.542600896860958</v>
       </c>
       <c r="G117" t="n">
         <v>223.0000000000018</v>
@@ -3619,10 +3619,10 @@
         <v>44732</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1440000000002328</v>
+        <v>0.144999999999709</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1073529411758703</v>
+        <v>0.1058823529413466</v>
       </c>
       <c r="G118" t="n">
         <v>68.00000000000068</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>90.04699999999721</v>
+        <v>68.95300000000279</v>
       </c>
       <c r="F119" t="n">
-        <v>8.461538461538533</v>
+        <v>7.611421911422626</v>
       </c>
       <c r="G119" t="n">
         <v>428.9999999999964</v>
@@ -3673,10 +3673,10 @@
         <v>44733</v>
       </c>
       <c r="E120" t="n">
-        <v>3.955000000001746</v>
+        <v>3.954000000000815</v>
       </c>
       <c r="F120" t="n">
-        <v>2.352380952382291</v>
+        <v>2.354761904761995</v>
       </c>
       <c r="G120" t="n">
         <v>83.99999999999181</v>
@@ -3703,7 +3703,7 @@
         <v>-0.3789999999999963</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.5277777777776775</v>
+        <v>-0.5250000000000917</v>
       </c>
       <c r="G121" t="n">
         <v>35.99999999999994</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>-8.287999999997556</v>
+        <v>-8.925000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.3000696378829814</v>
+        <v>-0.3246518105849229</v>
       </c>
       <c r="G122" t="n">
         <v>1436.000000000013</v>
@@ -3754,10 +3754,10 @@
         <v>44656</v>
       </c>
       <c r="E123" t="n">
-        <v>-5.317000000001281</v>
+        <v>-5.313999999998487</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.2603330068559001</v>
+        <v>-0.2601371204701065</v>
       </c>
       <c r="G123" t="n">
         <v>1020.999999999992</v>
@@ -3781,10 +3781,10 @@
         <v>44680</v>
       </c>
       <c r="E124" t="n">
-        <v>-1.114999999999418</v>
+        <v>-1.115999999999622</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.4463999999995576</v>
+        <v>-0.4464000000001396</v>
       </c>
       <c r="G124" t="n">
         <v>125</v>
@@ -3808,10 +3808,10 @@
         <v>44733</v>
       </c>
       <c r="E125" t="n">
-        <v>2.485999999998603</v>
+        <v>2.493000000005122</v>
       </c>
       <c r="F125" t="n">
-        <v>0.02759078830828387</v>
+        <v>0.02761293179811848</v>
       </c>
       <c r="G125" t="n">
         <v>4515.999999999985</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>11.27999999999884</v>
+        <v>13.65</v>
       </c>
       <c r="F126" t="n">
-        <v>9.362903225804505</v>
+        <v>12.6532258064534</v>
       </c>
       <c r="G126" t="n">
         <v>62.00000000000045</v>
@@ -3862,10 +3862,10 @@
         <v>44730</v>
       </c>
       <c r="E127" t="n">
-        <v>3.165000000002328</v>
+        <v>3.165999999997439</v>
       </c>
       <c r="F127" t="n">
-        <v>0.2556451612899452</v>
+        <v>0.2549999999999606</v>
       </c>
       <c r="G127" t="n">
         <v>620.0000000000045</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>41.57399999999907</v>
+        <v>33.42399999999907</v>
       </c>
       <c r="F129" t="n">
-        <v>0.5486592347095219</v>
+        <v>0.458391081650784</v>
       </c>
       <c r="G129" t="n">
         <v>3319.000000000051</v>
@@ -3943,10 +3943,10 @@
         <v>44647</v>
       </c>
       <c r="E130" t="n">
-        <v>-4.927999999999884</v>
+        <v>-4.926999999998952</v>
       </c>
       <c r="F130" t="n">
-        <v>-1.339130434782554</v>
+        <v>-1.338586956521178</v>
       </c>
       <c r="G130" t="n">
         <v>184.0000000000032</v>
@@ -3970,10 +3970,10 @@
         <v>44635</v>
       </c>
       <c r="E131" t="n">
-        <v>-8.401000000000931</v>
+        <v>-8.39600000000064</v>
       </c>
       <c r="F131" t="n">
-        <v>-2.385795454545752</v>
+        <v>-2.384659090909157</v>
       </c>
       <c r="G131" t="n">
         <v>176</v>
@@ -3997,10 +3997,10 @@
         <v>44734</v>
       </c>
       <c r="E132" t="n">
-        <v>-14.30499999999884</v>
+        <v>-14.29200000000128</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.1917404129793512</v>
+        <v>-0.1915258782515765</v>
       </c>
       <c r="G132" t="n">
         <v>3728.999999999996</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>19.54800000000105</v>
+        <v>29.47000000000116</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4265134938001872</v>
+        <v>0.6482494529540463</v>
       </c>
       <c r="G133" t="n">
         <v>2742.000000000007</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>11.09599999999918</v>
+        <v>11.64899999999907</v>
       </c>
       <c r="F134" t="n">
-        <v>0.8200000000001424</v>
+        <v>0.8930882352938497</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.7649999999999636</v>
+        <v>-0.7850000000000363</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.1617283950617399</v>
+        <v>-0.1613168724279861</v>
       </c>
       <c r="G135" t="n">
         <v>243.0000000000007</v>
@@ -4105,7 +4105,7 @@
         <v>44734</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.686999999999898</v>
+        <v>-1.686000000000058</v>
       </c>
       <c r="F136" t="n">
         <v>-0.1476357267951005</v>
@@ -4132,10 +4132,10 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.2899999999999636</v>
+        <v>-0.3380000000000109</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.6935483870966518</v>
+        <v>-0.6903225806452619</v>
       </c>
       <c r="G137" t="n">
         <v>31.00000000000023</v>
@@ -4159,10 +4159,10 @@
         <v>44732</v>
       </c>
       <c r="E138" t="n">
-        <v>-12.99699999999721</v>
+        <v>-12.99500000000116</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.2109415584414678</v>
+        <v>-0.2109740259741545</v>
       </c>
       <c r="G138" t="n">
         <v>3080</v>
@@ -4186,7 +4186,7 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.3690000000002328</v>
+        <v>-0.4</v>
       </c>
       <c r="F139" t="n">
         <v>-0.03868471953578367</v>
@@ -4213,7 +4213,7 @@
         <v>44734</v>
       </c>
       <c r="E140" t="n">
-        <v>10.30999999999767</v>
+        <v>10.31199999999953</v>
       </c>
       <c r="F140" t="n">
         <v>0.8006211180124077</v>
@@ -4243,7 +4243,7 @@
         <v>-0.1240000000000009</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.1033333333333149</v>
+        <v>-0.1033333333333528</v>
       </c>
       <c r="G141" t="n">
         <v>60.00000000000014</v>
@@ -4267,7 +4267,7 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>-2.202999999999883</v>
+        <v>-2.20199999999968</v>
       </c>
       <c r="F142" t="n">
         <v>-0.3200581395348374</v>
@@ -4294,10 +4294,10 @@
         <v>44734</v>
       </c>
       <c r="E143" t="n">
-        <v>-4.101999999998952</v>
+        <v>-4.258000000000175</v>
       </c>
       <c r="F143" t="n">
-        <v>-7.885185185182515</v>
+        <v>-7.885185185187905</v>
       </c>
       <c r="G143" t="n">
         <v>27.00000000000102</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>8.609999999997672</v>
+        <v>8.921999999997206</v>
       </c>
       <c r="F144" t="n">
-        <v>1.580952380951696</v>
+        <v>1.687179487179672</v>
       </c>
       <c r="G144" t="n">
         <v>272.9999999999563</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>10.46600000000326</v>
+        <v>11.97600000000093</v>
       </c>
       <c r="F145" t="n">
-        <v>0.5402671755735845</v>
+        <v>0.6030534351140584</v>
       </c>
       <c r="G145" t="n">
         <v>1048.000000000002</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>2.195999999999185</v>
+        <v>4.597000000000117</v>
       </c>
       <c r="F146" t="n">
-        <v>0.9658385093179148</v>
+        <v>1.889440993787925</v>
       </c>
       <c r="G146" t="n">
         <v>160.99999999999</v>
@@ -4402,7 +4402,7 @@
         <v>44724</v>
       </c>
       <c r="E147" t="n">
-        <v>-2.495999999999913</v>
+        <v>-2.494000000000233</v>
       </c>
       <c r="F147" t="n">
         <v>-0.6173267326733305</v>
@@ -4429,10 +4429,10 @@
         <v>44667</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.3420000000000073</v>
+        <v>-0.3409999999999854</v>
       </c>
       <c r="F148" t="n">
-        <v>-5.666666666666013</v>
+        <v>-5.700000000000074</v>
       </c>
       <c r="G148" t="n">
         <v>3.000000000000025</v>
@@ -4459,7 +4459,7 @@
         <v>-0.05099999999999909</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.6499999999999623</v>
+        <v>-0.6249999999999856</v>
       </c>
       <c r="G149" t="n">
         <v>4.000000000000092</v>
@@ -4483,10 +4483,10 @@
         <v>44734</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.3449999999999818</v>
+        <v>-0.3450000000000727</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.5733333333334236</v>
+        <v>-0.5766666666668298</v>
       </c>
       <c r="G150" t="n">
         <v>29.99999999999972</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>3.063000000000466</v>
+        <v>2.955999999999767</v>
       </c>
       <c r="F151" t="n">
-        <v>1.4449541284404</v>
+        <v>1.266972477064036</v>
       </c>
       <c r="G151" t="n">
         <v>108.9999999999975</v>
@@ -4537,10 +4537,10 @@
         <v>44614</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.8200000000000728</v>
+        <v>-0.8190000000002329</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.1301587301587992</v>
+        <v>-0.1298412698412742</v>
       </c>
       <c r="G152" t="n">
         <v>315.0000000000006</v>
@@ -4564,10 +4564,10 @@
         <v>44734</v>
       </c>
       <c r="E153" t="n">
-        <v>-1.093000000000757</v>
+        <v>-1.092999999999301</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.1613569321534273</v>
+        <v>-0.1610619469024152</v>
       </c>
       <c r="G153" t="n">
         <v>338.9999999999986</v>
@@ -4591,7 +4591,7 @@
         <v>44724</v>
       </c>
       <c r="E154" t="n">
-        <v>-2.097000000000116</v>
+        <v>-2.095999999999185</v>
       </c>
       <c r="F154" t="n">
         <v>-1.838596491227377</v>
@@ -4618,10 +4618,10 @@
         <v>44712</v>
       </c>
       <c r="E155" t="n">
-        <v>-1.802000000001863</v>
+        <v>-1.804000000000815</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.08111510791383571</v>
+        <v>-0.08111510791357399</v>
       </c>
       <c r="G155" t="n">
         <v>1112.000000000012</v>
@@ -4645,10 +4645,10 @@
         <v>44699</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.3569999999999709</v>
+        <v>-0.3610000000000128</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.5323529411764604</v>
+        <v>-0.5294117647059416</v>
       </c>
       <c r="G156" t="n">
         <v>33.99999999999963</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>-16.24700000000012</v>
+        <v>-16.11000000000058</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.9564497041420893</v>
+        <v>-0.9500591715976142</v>
       </c>
       <c r="G157" t="n">
         <v>845.0000000000045</v>
@@ -4699,10 +4699,10 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>1.19199999999837</v>
+        <v>1.312999999994645</v>
       </c>
       <c r="F158" t="n">
-        <v>0.09646697388586391</v>
+        <v>0.09631336405469165</v>
       </c>
       <c r="G158" t="n">
         <v>650.9999999999991</v>
@@ -4726,10 +4726,10 @@
         <v>44730</v>
       </c>
       <c r="E159" t="n">
-        <v>-6.145999999996275</v>
+        <v>-6.144000000000233</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.3106167846306476</v>
+        <v>-0.3106167846312361</v>
       </c>
       <c r="G159" t="n">
         <v>989.0000000000327</v>
@@ -4756,7 +4756,7 @@
         <v>2.552000000000407</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3786350148370583</v>
+        <v>0.3786350148366265</v>
       </c>
       <c r="G160" t="n">
         <v>337.0000000000118</v>
@@ -4780,10 +4780,10 @@
         <v>44731</v>
       </c>
       <c r="E161" t="n">
-        <v>10.37999999999884</v>
+        <v>10.38199999999488</v>
       </c>
       <c r="F161" t="n">
-        <v>1.366315789473272</v>
+        <v>1.365789473683308</v>
       </c>
       <c r="G161" t="n">
         <v>379.9999999999955</v>
@@ -4810,7 +4810,7 @@
         <v>-2.669000000000233</v>
       </c>
       <c r="F162" t="n">
-        <v>-133.4000000002319</v>
+        <v>-133.5000000000341</v>
       </c>
       <c r="G162" t="n">
         <v>0.9999999999990905</v>
@@ -4834,10 +4834,10 @@
         <v>44619</v>
       </c>
       <c r="E163" t="n">
-        <v>-3.166999999999825</v>
+        <v>-3.163999999999942</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.9479041916168701</v>
+        <v>-0.9467065868262069</v>
       </c>
       <c r="G163" t="n">
         <v>167.0000000000002</v>
@@ -4861,7 +4861,7 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>-2.786000000000058</v>
+        <v>-2.811999999999534</v>
       </c>
       <c r="F164" t="n">
         <v>-0.833727810650682</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>-1.470000000000073</v>
+        <v>-1.668999999999869</v>
       </c>
       <c r="F165" t="n">
-        <v>-1.145454545454492</v>
+        <v>-1.144155844155999</v>
       </c>
       <c r="G165" t="n">
         <v>77.00000000000102</v>
@@ -4915,10 +4915,10 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>-1.101000000000022</v>
+        <v>-1.160000000000036</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.566019417475897</v>
+        <v>-0.5660194174757205</v>
       </c>
       <c r="G166" t="n">
         <v>103.0000000000001</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -487,10 +487,10 @@
         <v>44632</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3299999999999727</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2323943661971316</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>71.00000000000009</v>
@@ -514,10 +514,10 @@
         <v>44734</v>
       </c>
       <c r="E3" t="n">
-        <v>3.341000000000349</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.816304347826639</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>92.00000000000728</v>
@@ -541,10 +541,10 @@
         <v>44609</v>
       </c>
       <c r="E4" t="n">
-        <v>-26.48000000000466</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.206927985415002</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>1096.99999999998</v>
@@ -568,10 +568,10 @@
         <v>44735</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.69899999999907</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02278518771040251</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>23466.99999999983</v>
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.464999999999418</v>
+        <v>0.4169999999983702</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2239786856125407</v>
+        <v>0.03179396092376822</v>
       </c>
       <c r="G6" t="n">
         <v>562.9999999999995</v>
@@ -622,10 +622,10 @@
         <v>44711</v>
       </c>
       <c r="E7" t="n">
-        <v>4.215000000002329</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5728260869569547</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>368.0000000000064</v>
@@ -649,10 +649,10 @@
         <v>44734</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.61200000000536</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4583885209712923</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>1811.999999999989</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>2.325</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01744787816064822</v>
+        <v>0.002498891024610521</v>
       </c>
       <c r="G9" t="n">
         <v>6763.000000000102</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3620000000009895</v>
+        <v>1.477000000000408</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2261146496817232</v>
+        <v>0.3592356687897864</v>
       </c>
       <c r="G10" t="n">
         <v>156.9999999999936</v>
@@ -730,10 +730,10 @@
         <v>44632</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3619999999999891</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1381679389312933</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>131.0000000000002</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>23.59099999999744</v>
+        <v>26.49700000000303</v>
       </c>
       <c r="F12" t="n">
-        <v>1.52714078374418</v>
+        <v>1.736719883889356</v>
       </c>
       <c r="G12" t="n">
         <v>688.9999999999873</v>
@@ -784,10 +784,10 @@
         <v>44607</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.08099999999999455</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3333333333333166</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>11.99999999999992</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5100000000000364</v>
+        <v>0.04500000000007276</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.559999999999636</v>
+        <v>0.2199999999993577</v>
       </c>
       <c r="G14" t="n">
         <v>9.999999999999432</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>7.959999999997672</v>
+        <v>3.105999999999767</v>
       </c>
       <c r="F15" t="n">
-        <v>1.432911392404989</v>
+        <v>0.6629746835446551</v>
       </c>
       <c r="G15" t="n">
         <v>316.0000000000082</v>
@@ -865,10 +865,10 @@
         <v>44735</v>
       </c>
       <c r="E16" t="n">
-        <v>-37.4359999999986</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.628873949579918</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>2975</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>31.99799999999959</v>
+        <v>33.95800000000018</v>
       </c>
       <c r="F17" t="n">
-        <v>2.877562862669066</v>
+        <v>3.065183752417842</v>
       </c>
       <c r="G17" t="n">
         <v>516.9999999999959</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>3.960000000000582</v>
+        <v>0.2180000000007567</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2664886515354657</v>
+        <v>0.01668891855807741</v>
       </c>
       <c r="G18" t="n">
         <v>749.0000000000009</v>
@@ -946,10 +946,10 @@
         <v>44688</v>
       </c>
       <c r="E19" t="n">
-        <v>2.749000000000524</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2886554621849846</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>475.9999999999991</v>
@@ -973,10 +973,10 @@
         <v>44655</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.717000000001281</v>
+        <v>0.4970000000001164</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4119092627598062</v>
+        <v>0.02344045368629957</v>
       </c>
       <c r="G20" t="n">
         <v>1057.999999999993</v>
@@ -1000,10 +1000,10 @@
         <v>44720</v>
       </c>
       <c r="E21" t="n">
-        <v>1.455999999999767</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005077416655021434</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>14338</v>
@@ -1027,10 +1027,10 @@
         <v>44729</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.077999999999884</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6975274725274483</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>364.0000000000043</v>
@@ -1054,10 +1054,10 @@
         <v>44607</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.604999999998836</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1432967032964727</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>910.0000000000023</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>31.78099999999977</v>
+        <v>32.58800000000046</v>
       </c>
       <c r="F24" t="n">
-        <v>1.426365795724638</v>
+        <v>1.458273950910923</v>
       </c>
       <c r="G24" t="n">
         <v>1263.000000000011</v>
@@ -1108,10 +1108,10 @@
         <v>44619</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.979999999998836</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.01310390469886718</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>7555.000000000018</v>
@@ -1135,10 +1135,10 @@
         <v>44582</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.163999999998486</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.209927983539082</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>1944.000000000005</v>
@@ -1162,10 +1162,10 @@
         <v>44696</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3789999999999963</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.749999999999192</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>3.999999999999915</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.49600000000064</v>
+        <v>2.044999999999709</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2868951612902515</v>
+        <v>0.1697580645161004</v>
       </c>
       <c r="G28" t="n">
         <v>495.9999999999809</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>2.439999999996508</v>
+        <v>12.37400000000489</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1574351978169053</v>
+        <v>0.8346521145982514</v>
       </c>
       <c r="G29" t="n">
         <v>732.9999999999927</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.234000000002561</v>
+        <v>0.8189999999944121</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.083539603960396</v>
+        <v>0.02062706270627062</v>
       </c>
       <c r="G30" t="n">
         <v>2424.000000000001</v>
@@ -1270,10 +1270,10 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2539999999999963</v>
+        <v>0.002999999999974534</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4961538461538224</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>26.00000000000051</v>
@@ -1297,10 +1297,10 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.07800000000000865</v>
+        <v>0.03899999999999863</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9500000000000755</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>6.00000000000005</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8990000000005238</v>
+        <v>3.908999999999651</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1412000000005355</v>
+        <v>0.820799999999581</v>
       </c>
       <c r="G33" t="n">
         <v>250</v>
@@ -1351,10 +1351,10 @@
         <v>44175</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.202999999999883</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2859740259738899</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>385</v>
@@ -1378,10 +1378,10 @@
         <v>44710</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7869999999995343</v>
+        <v>4.979999999998836</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1290965732087304</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>1604.999999999995</v>
@@ -1405,10 +1405,10 @@
         <v>44381</v>
       </c>
       <c r="E36" t="n">
-        <v>1.509999999999127</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.03410117434502422</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>2213.999999999999</v>
@@ -1432,10 +1432,10 @@
         <v>44701</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.06500000000232831</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.002727272727407424</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>1210</v>
@@ -1459,10 +1459,10 @@
         <v>44707</v>
       </c>
       <c r="E38" t="n">
-        <v>-30.10400000000373</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.381007850088683</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>3949.000000000001</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>126.4370000000054</v>
+        <v>147.4410000000033</v>
       </c>
       <c r="F39" t="n">
-        <v>0.03594788670692727</v>
+        <v>0.05421991962058465</v>
       </c>
       <c r="G39" t="n">
         <v>52501.0000000002</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>27.225</v>
+        <v>7.176999999996042</v>
       </c>
       <c r="F40" t="n">
-        <v>5.784615384617107</v>
+        <v>1.725910931172379</v>
       </c>
       <c r="G40" t="n">
         <v>246.9999999999345</v>
@@ -1540,10 +1540,10 @@
         <v>44724</v>
       </c>
       <c r="E41" t="n">
-        <v>9.847000000003026</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6637466307277563</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>742.0000000000073</v>
@@ -1567,10 +1567,10 @@
         <v>44682</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.675</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1851648351648798</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>181.9999999999993</v>
@@ -1594,10 +1594,10 @@
         <v>44712</v>
       </c>
       <c r="E43" t="n">
-        <v>4.689999999999418</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0653021442494643</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>3590.999999999985</v>
@@ -1621,10 +1621,10 @@
         <v>44734</v>
       </c>
       <c r="E44" t="n">
-        <v>-9.25</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.5389277389276349</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>857.9999999999927</v>
@@ -1648,10 +1648,10 @@
         <v>44725</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.802999999999884</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.2708708708707714</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>333.0000000000041</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1580000000001746</v>
+        <v>1.812000000000262</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.03417721518992902</v>
+        <v>0.5892405063289725</v>
       </c>
       <c r="G46" t="n">
         <v>157.9999999999984</v>
@@ -1702,10 +1702,10 @@
         <v>44729</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4809999999997672</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.03742236024805052</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>643.9999999999827</v>
@@ -1729,10 +1729,10 @@
         <v>44733</v>
       </c>
       <c r="E48" t="n">
-        <v>20.66900000000023</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1.972709923665055</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>524.0000000000236</v>
@@ -1756,10 +1756,10 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.3690000000000054</v>
+        <v>0.007000000000016371</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.5054054054053794</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>36.99999999999974</v>
@@ -1783,10 +1783,10 @@
         <v>44732</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.096000000002096</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1086956521739142</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>505.9999999999945</v>
@@ -1810,10 +1810,10 @@
         <v>44731</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.335999999998603</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1455337690630276</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>459.0000000000032</v>
@@ -1837,10 +1837,10 @@
         <v>44730</v>
       </c>
       <c r="E52" t="n">
-        <v>-3.66600000000326</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.08739255014293458</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>2093.99999999996</v>
@@ -1864,10 +1864,10 @@
         <v>44616</v>
       </c>
       <c r="E53" t="n">
-        <v>-26.15999999999767</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.170593607305949</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>7664.999999999964</v>
@@ -1891,10 +1891,10 @@
         <v>44682</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.577000000000044</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.641666666666817</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>48.00000000000182</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>4.975999999995111</v>
+        <v>13.4359999999986</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0679021497403598</v>
+        <v>0.2242401779095663</v>
       </c>
       <c r="G55" t="n">
         <v>2697.999999999956</v>
@@ -1945,10 +1945,10 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>3.54100000000326</v>
+        <v>3.051999999996042</v>
       </c>
       <c r="F56" t="n">
-        <v>0.03315508021365465</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>748.0000000000018</v>
@@ -1972,10 +1972,10 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3420000000000073</v>
+        <v>0.01199999999998909</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.769999999999628</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>9.999999999999432</v>
@@ -1999,10 +1999,10 @@
         <v>44638</v>
       </c>
       <c r="E58" t="n">
-        <v>-40.73300000000163</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1657438319355014</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>12280.99999999995</v>
@@ -2026,10 +2026,10 @@
         <v>44724</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.2340000000000146</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.462500000000122</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>7.999999999999829</v>
@@ -2053,10 +2053,10 @@
         <v>44600</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3940000000000509</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5051282051282697</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>39.00000000000006</v>
@@ -2080,10 +2080,10 @@
         <v>44724</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3649999999999636</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.423255813953428</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
         <v>42.99999999999926</v>
@@ -2107,10 +2107,10 @@
         <v>44620</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8399999999999637</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.003876684511721348</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>10834</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>138.2539999999921</v>
+        <v>110.7</v>
       </c>
       <c r="F63" t="n">
-        <v>1.136258226261416</v>
+        <v>0.9182074584769706</v>
       </c>
       <c r="G63" t="n">
         <v>6381.999999999971</v>
@@ -2161,10 +2161,10 @@
         <v>44720</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.01948972360028331</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>1411.000000000013</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>-3.961000000000058</v>
+        <v>0.01600000000034925</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4982412060301959</v>
+        <v>0.001256281407108304</v>
       </c>
       <c r="G65" t="n">
         <v>397.999999999999</v>
@@ -2215,10 +2215,10 @@
         <v>44730</v>
       </c>
       <c r="E66" t="n">
-        <v>-8.726999999996043</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2187875751502185</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>1996.000000000004</v>
@@ -2242,10 +2242,10 @@
         <v>44735</v>
       </c>
       <c r="E67" t="n">
-        <v>9.144000000000233</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1.745038167940008</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>262.0000000000118</v>
@@ -2269,10 +2269,10 @@
         <v>44707</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.1269999999999982</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.4571428571427643</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>14.00000000000006</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>5.135000000000582</v>
+        <v>1.125</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6474698795179814</v>
+        <v>0.164096385542118</v>
       </c>
       <c r="G69" t="n">
         <v>414.9999999999864</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.7110000000000583</v>
+        <v>0.0180000000000291</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.1246575342466793</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>292.0000000000016</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.013000000000102</v>
+        <v>0.04799999999995634</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.2336363636363324</v>
+        <v>0.007727272727193193</v>
       </c>
       <c r="G71" t="n">
         <v>220.0000000000045</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>23.04700000000303</v>
+        <v>36.94600000000209</v>
       </c>
       <c r="F72" t="n">
-        <v>1.485557083906469</v>
+        <v>2.438927097661597</v>
       </c>
       <c r="G72" t="n">
         <v>726.9999999999982</v>
@@ -2404,10 +2404,10 @@
         <v>44713</v>
       </c>
       <c r="E73" t="n">
-        <v>-2.961999999999534</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.7295566502462005</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>202.9999999999973</v>
@@ -2431,10 +2431,10 @@
         <v>44614</v>
       </c>
       <c r="E74" t="n">
-        <v>-4.355999999999767</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.7859205776172181</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>276.9999999999982</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.460000000009313</v>
+        <v>23.66399999998976</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.5206896551729328</v>
+        <v>0.9671264367804013</v>
       </c>
       <c r="G75" t="n">
         <v>870.0000000000273</v>
@@ -2485,10 +2485,10 @@
         <v>44734</v>
       </c>
       <c r="E76" t="n">
-        <v>-27.39500000000116</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.6930668016194844</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>1976.000000000022</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>51.56300000000046</v>
+        <v>45.60999999999767</v>
       </c>
       <c r="F77" t="n">
-        <v>1.283216476774821</v>
+        <v>1.152103418054218</v>
       </c>
       <c r="G77" t="n">
         <v>2282.000000000016</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>1.84800000000032</v>
+        <v>1.690999999999622</v>
       </c>
       <c r="F78" t="n">
-        <v>0.08737113402060366</v>
+        <v>0.07719072164945838</v>
       </c>
       <c r="G78" t="n">
         <v>775.9999999999991</v>
@@ -2566,10 +2566,10 @@
         <v>44701</v>
       </c>
       <c r="E79" t="n">
-        <v>1.615999999997439</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5049999999992284</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>159.9999999999909</v>
@@ -2593,10 +2593,10 @@
         <v>44734</v>
       </c>
       <c r="E80" t="n">
-        <v>5.502999999996973</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.5159474671669809</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>532.9999999999984</v>
@@ -2620,10 +2620,10 @@
         <v>44355</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.413999999999942</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.1171703296703141</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>1455.999999999995</v>
@@ -2647,10 +2647,10 @@
         <v>44699</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.4539999999999964</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.7093750000001515</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>31.99999999999932</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.3130000000000109</v>
+        <v>0.04600000000000364</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.674999999999929</v>
+        <v>0.07083333333336096</v>
       </c>
       <c r="G83" t="n">
         <v>24.00000000000091</v>
@@ -2701,10 +2701,10 @@
         <v>44735</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8870000000024447</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.004944748297825787</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
         <v>8958.999999999993</v>
@@ -2728,10 +2728,10 @@
         <v>44727</v>
       </c>
       <c r="E85" t="n">
-        <v>2.506000000005588</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.07974603174638653</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>1575</v>
@@ -2755,10 +2755,10 @@
         <v>44632</v>
       </c>
       <c r="E86" t="n">
-        <v>-9.607000000000699</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.410427350427516</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>1169.999999999982</v>
@@ -2782,10 +2782,10 @@
         <v>44693</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.435000000000218</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>-2.39000000000054</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>30.00000000000114</v>
@@ -2809,10 +2809,10 @@
         <v>44361</v>
       </c>
       <c r="E88" t="n">
-        <v>-6.126999999998953</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.1999347258485937</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>1532.000000000005</v>
@@ -2836,10 +2836,10 @@
         <v>44147</v>
       </c>
       <c r="E89" t="n">
-        <v>-2.765999999998894</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.3627296587924523</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>381</v>
@@ -2863,10 +2863,10 @@
         <v>44731</v>
       </c>
       <c r="E90" t="n">
-        <v>5.219999999998254</v>
+        <v>6.712999999997555</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.1223905723908848</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
         <v>594.0000000000055</v>
@@ -2890,10 +2890,10 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>-5.95</v>
+        <v>7.623999999999069</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.1703797468355609</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>3950</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.5819999999999709</v>
+        <v>0.02599999999983993</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.7794871794873171</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>39.00000000000432</v>
@@ -2944,10 +2944,10 @@
         <v>44717</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6559999999999491</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.6559999999997672</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>50</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>53.43399999999674</v>
+        <v>35.3219999999972</v>
       </c>
       <c r="F94" t="n">
-        <v>17.01702127659389</v>
+        <v>12.23723404255236</v>
       </c>
       <c r="G94" t="n">
         <v>188.0000000000109</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>53.025</v>
+        <v>80.05999999999767</v>
       </c>
       <c r="F95" t="n">
-        <v>1.073766816143857</v>
+        <v>1.818946188340885</v>
       </c>
       <c r="G95" t="n">
         <v>1783.999999999924</v>
@@ -3025,10 +3025,10 @@
         <v>44734</v>
       </c>
       <c r="E96" t="n">
-        <v>19.62600000000093</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>1.390368271955147</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>705.9999999999945</v>
@@ -3052,10 +3052,10 @@
         <v>44704</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.181000000000495</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.5221238938054407</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>112.9999999999995</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>35.56999999999825</v>
+        <v>25.19700000000012</v>
       </c>
       <c r="F98" t="n">
-        <v>0.7550257289879811</v>
+        <v>0.5766723842194742</v>
       </c>
       <c r="G98" t="n">
         <v>2915</v>
@@ -3106,10 +3106,10 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.1929999999999836</v>
+        <v>0.006999999999970896</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>9.999999999999964</v>
@@ -3133,10 +3133,10 @@
         <v>44634</v>
       </c>
       <c r="E100" t="n">
-        <v>-4.829999999998836</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.09602227525860642</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
         <v>2514.000000000033</v>
@@ -3160,10 +3160,10 @@
         <v>44730</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.825</v>
+        <v>1.045000000000436</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.8927536231889149</v>
+        <v>0.4579710144932612</v>
       </c>
       <c r="G101" t="n">
         <v>68.99999999999977</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>11.3609999999986</v>
+        <v>7.554999999998836</v>
       </c>
       <c r="F102" t="n">
-        <v>2.328409090909147</v>
+        <v>1.605681818181253</v>
       </c>
       <c r="G102" t="n">
         <v>263.9999999999986</v>
@@ -3214,10 +3214,10 @@
         <v>44724</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.1519999999999982</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
         <v>18.99999999999977</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>54.92399999999907</v>
+        <v>65.69599999999919</v>
       </c>
       <c r="F104" t="n">
-        <v>1.101306847882864</v>
+        <v>1.375640355462482</v>
       </c>
       <c r="G104" t="n">
         <v>1913.000000000011</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.2170000000000073</v>
+        <v>0.075</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.1626865671642038</v>
+        <v>0.05671641791032937</v>
       </c>
       <c r="G105" t="n">
         <v>66.99999999999875</v>
@@ -3295,10 +3295,10 @@
         <v>44666</v>
       </c>
       <c r="E106" t="n">
-        <v>-13.32800000000279</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.9756954612007356</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>683.0000000000382</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>251.8359999999986</v>
+        <v>221.2530000000028</v>
       </c>
       <c r="F107" t="n">
-        <v>33.27522658610249</v>
+        <v>28.83413897280937</v>
       </c>
       <c r="G107" t="n">
         <v>330.9999999999945</v>
@@ -3349,10 +3349,10 @@
         <v>44724</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.7429999999999382</v>
+        <v>0.002999999999974534</v>
       </c>
       <c r="F108" t="n">
-        <v>-2.324999999999537</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
         <v>16.00000000000037</v>
@@ -3376,10 +3376,10 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>-1.272999999999956</v>
+        <v>0.06199999999989814</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.461805555555531</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
         <v>143.9999999999998</v>
@@ -3403,10 +3403,10 @@
         <v>44724</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.4080000000000837</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>-2.040000000000917</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
         <v>9.999999999999787</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>-1.178999999997905</v>
+        <v>5.717999999999302</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.4399739583330569</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>768.0000000000064</v>
@@ -3457,10 +3457,10 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>-4.309999999999855</v>
+        <v>0.2069999999999709</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.6455587392549794</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>349.0000000000009</v>
@@ -3484,10 +3484,10 @@
         <v>44696</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.04499999999999886</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.3666666666666252</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>5.999999999999872</v>
@@ -3511,10 +3511,10 @@
         <v>44622</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.09200000000000727</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.07796610169492144</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
         <v>58.99999999999999</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.001999999999998181</v>
+        <v>0.1190000000000055</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.004761904761792139</v>
+        <v>0.2809523809522326</v>
       </c>
       <c r="G115" t="n">
         <v>21.00000000000009</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>-6.625</v>
+        <v>5.236999999999535</v>
       </c>
       <c r="F116" t="n">
-        <v>-1.73401015228294</v>
+        <v>1.275126903553045</v>
       </c>
       <c r="G116" t="n">
         <v>197.0000000000027</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>15.39100000000326</v>
+        <v>24.575</v>
       </c>
       <c r="F117" t="n">
-        <v>3.542600896860958</v>
+        <v>5.605381165919237</v>
       </c>
       <c r="G117" t="n">
         <v>223.0000000000018</v>
@@ -3619,10 +3619,10 @@
         <v>44732</v>
       </c>
       <c r="E118" t="n">
-        <v>0.144999999999709</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1058823529413466</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
         <v>68.00000000000068</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>68.95300000000279</v>
+        <v>84.41699999999837</v>
       </c>
       <c r="F119" t="n">
-        <v>7.611421911422626</v>
+        <v>9.407226107224993</v>
       </c>
       <c r="G119" t="n">
         <v>428.9999999999964</v>
@@ -3673,10 +3673,10 @@
         <v>44733</v>
       </c>
       <c r="E120" t="n">
-        <v>3.954000000000815</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>2.354761904761995</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>83.99999999999181</v>
@@ -3700,10 +3700,10 @@
         <v>44735</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.3789999999999963</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.5250000000000917</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>35.99999999999994</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>-8.925000000000001</v>
+        <v>2.044000000000233</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.3246518105849229</v>
+        <v>0.05696378830078651</v>
       </c>
       <c r="G122" t="n">
         <v>1436.000000000013</v>
@@ -3754,10 +3754,10 @@
         <v>44656</v>
       </c>
       <c r="E123" t="n">
-        <v>-5.313999999998487</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.2601371204701065</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
         <v>1020.999999999992</v>
@@ -3781,10 +3781,10 @@
         <v>44680</v>
       </c>
       <c r="E124" t="n">
-        <v>-1.115999999999622</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.4464000000001396</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
         <v>125</v>
@@ -3808,10 +3808,10 @@
         <v>44733</v>
       </c>
       <c r="E125" t="n">
-        <v>2.493000000005122</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.02761293179811848</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
         <v>4515.999999999985</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>13.65</v>
+        <v>6.807000000000698</v>
       </c>
       <c r="F126" t="n">
-        <v>12.6532258064534</v>
+        <v>7.138709677420803</v>
       </c>
       <c r="G126" t="n">
         <v>62.00000000000045</v>
@@ -3862,10 +3862,10 @@
         <v>44730</v>
       </c>
       <c r="E127" t="n">
-        <v>3.165999999997439</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.2549999999999606</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
         <v>620.0000000000045</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>33.42399999999907</v>
+        <v>30.75600000000559</v>
       </c>
       <c r="F129" t="n">
-        <v>0.458391081650784</v>
+        <v>0.4184995480567073</v>
       </c>
       <c r="G129" t="n">
         <v>3319.000000000051</v>
@@ -3943,10 +3943,10 @@
         <v>44647</v>
       </c>
       <c r="E130" t="n">
-        <v>-4.926999999998952</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>-1.338586956521178</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
         <v>184.0000000000032</v>
@@ -3970,10 +3970,10 @@
         <v>44635</v>
       </c>
       <c r="E131" t="n">
-        <v>-8.39600000000064</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>-2.384659090909157</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>176</v>
@@ -3997,10 +3997,10 @@
         <v>44734</v>
       </c>
       <c r="E132" t="n">
-        <v>-14.29200000000128</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.1915258782515765</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
         <v>3728.999999999996</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>29.47000000000116</v>
+        <v>25.26699999999837</v>
       </c>
       <c r="F133" t="n">
-        <v>0.6482494529540463</v>
+        <v>0.5706053975200271</v>
       </c>
       <c r="G133" t="n">
         <v>2742.000000000007</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>11.64899999999907</v>
+        <v>7.952999999999884</v>
       </c>
       <c r="F134" t="n">
-        <v>0.8930882352938497</v>
+        <v>0.6208823529411979</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4078,10 +4078,10 @@
         <v>44735</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.7850000000000363</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.1613168724279861</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
         <v>243.0000000000007</v>
@@ -4105,10 +4105,10 @@
         <v>44734</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.686000000000058</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.1476357267951005</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
         <v>571.0000000000036</v>
@@ -4132,10 +4132,10 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.3380000000000109</v>
+        <v>0.09600000000000364</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.6903225806452619</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>31.00000000000023</v>
@@ -4159,10 +4159,10 @@
         <v>44732</v>
       </c>
       <c r="E138" t="n">
-        <v>-12.99500000000116</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.2109740259741545</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
         <v>3080</v>
@@ -4186,10 +4186,10 @@
         <v>44732</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.4</v>
+        <v>0.1270000000000437</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.03868471953578367</v>
+        <v>0.01218568665379156</v>
       </c>
       <c r="G139" t="n">
         <v>516.9999999999959</v>
@@ -4213,10 +4213,10 @@
         <v>44734</v>
       </c>
       <c r="E140" t="n">
-        <v>10.31199999999953</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0.8006211180124077</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
         <v>643.9999999999827</v>
@@ -4240,10 +4240,10 @@
         <v>44717</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.1240000000000009</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.1033333333333528</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>60.00000000000014</v>
@@ -4267,10 +4267,10 @@
         <v>44731</v>
       </c>
       <c r="E142" t="n">
-        <v>-2.20199999999968</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.3200581395348374</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
         <v>343.9999999999998</v>
@@ -4294,10 +4294,10 @@
         <v>44734</v>
       </c>
       <c r="E143" t="n">
-        <v>-4.258000000000175</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>-7.885185185187905</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>27.00000000000102</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>8.921999999997206</v>
+        <v>1.35</v>
       </c>
       <c r="F144" t="n">
-        <v>1.687179487179672</v>
+        <v>0.3003663003667748</v>
       </c>
       <c r="G144" t="n">
         <v>272.9999999999563</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>11.97600000000093</v>
+        <v>10.11899999999441</v>
       </c>
       <c r="F145" t="n">
-        <v>0.6030534351140584</v>
+        <v>0.5138358778623724</v>
       </c>
       <c r="G145" t="n">
         <v>1048.000000000002</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>4.597000000000117</v>
+        <v>9.365999999997438</v>
       </c>
       <c r="F146" t="n">
-        <v>1.889440993787925</v>
+        <v>3.376397515527292</v>
       </c>
       <c r="G146" t="n">
         <v>160.99999999999</v>
@@ -4402,10 +4402,10 @@
         <v>44724</v>
       </c>
       <c r="E147" t="n">
-        <v>-2.494000000000233</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.6173267326733305</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
         <v>201.9999999999982</v>
@@ -4429,10 +4429,10 @@
         <v>44667</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.3409999999999854</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>-5.700000000000074</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>3.000000000000025</v>
@@ -4456,10 +4456,10 @@
         <v>44699</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.05099999999999909</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.6249999999999856</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
         <v>4.000000000000092</v>
@@ -4483,10 +4483,10 @@
         <v>44734</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.3450000000000727</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.5766666666668298</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
         <v>29.99999999999972</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>2.955999999999767</v>
+        <v>2.782000000000699</v>
       </c>
       <c r="F151" t="n">
-        <v>1.266972477064036</v>
+        <v>1.187155963302993</v>
       </c>
       <c r="G151" t="n">
         <v>108.9999999999975</v>
@@ -4537,10 +4537,10 @@
         <v>44614</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.8190000000002329</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.1298412698412742</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
         <v>315.0000000000006</v>
@@ -4564,10 +4564,10 @@
         <v>44734</v>
       </c>
       <c r="E153" t="n">
-        <v>-1.092999999999301</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.1610619469024152</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
         <v>338.9999999999986</v>
@@ -4591,10 +4591,10 @@
         <v>44724</v>
       </c>
       <c r="E154" t="n">
-        <v>-2.095999999999185</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>-1.838596491227377</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
         <v>56.99999999999932</v>
@@ -4618,10 +4618,10 @@
         <v>44712</v>
       </c>
       <c r="E155" t="n">
-        <v>-1.804000000000815</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.08111510791357399</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
         <v>1112.000000000012</v>
@@ -4645,10 +4645,10 @@
         <v>44699</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.3610000000000128</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.5294117647059416</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>33.99999999999963</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>-16.11000000000058</v>
+        <v>0.3879999999975553</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.9500591715976142</v>
+        <v>0.02532544378680301</v>
       </c>
       <c r="G157" t="n">
         <v>845.0000000000045</v>
@@ -4699,10 +4699,10 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>1.312999999994645</v>
+        <v>0.653000000002794</v>
       </c>
       <c r="F158" t="n">
-        <v>0.09631336405469165</v>
+        <v>0.04608294930875582</v>
       </c>
       <c r="G158" t="n">
         <v>650.9999999999991</v>
@@ -4726,10 +4726,10 @@
         <v>44730</v>
       </c>
       <c r="E159" t="n">
-        <v>-6.144000000000233</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.3106167846312361</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
         <v>989.0000000000327</v>
@@ -4753,10 +4753,10 @@
         <v>44733</v>
       </c>
       <c r="E160" t="n">
-        <v>2.552000000000407</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3786350148366265</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
         <v>337.0000000000118</v>
@@ -4780,10 +4780,10 @@
         <v>44731</v>
       </c>
       <c r="E161" t="n">
-        <v>10.38199999999488</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>1.365789473683308</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
         <v>379.9999999999955</v>
@@ -4807,10 +4807,10 @@
         <v>44724</v>
       </c>
       <c r="E162" t="n">
-        <v>-2.669000000000233</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>-133.5000000000341</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
         <v>0.9999999999990905</v>
@@ -4834,10 +4834,10 @@
         <v>44619</v>
       </c>
       <c r="E163" t="n">
-        <v>-3.163999999999942</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.9467065868262069</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
         <v>167.0000000000002</v>
@@ -4861,10 +4861,10 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>-2.811999999999534</v>
+        <v>0.005999999999767169</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.833727810650682</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
         <v>168.9999999999998</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>-1.668999999999869</v>
+        <v>0.1</v>
       </c>
       <c r="F165" t="n">
-        <v>-1.144155844155999</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>77.00000000000102</v>
@@ -4915,10 +4915,10 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>-1.160000000000036</v>
+        <v>0.006000000000130967</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.5660194174757205</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>103.0000000000001</v>

--- a/covid.xlsx
+++ b/covid.xlsx
@@ -595,10 +595,10 @@
         <v>44716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4169999999983702</v>
+        <v>0.3059999999997672</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03179396092376822</v>
+        <v>0.02095914742438749</v>
       </c>
       <c r="G6" t="n">
         <v>562.9999999999995</v>
@@ -676,10 +676,10 @@
         <v>44735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.3339999999967403</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002498891024610521</v>
+        <v>0.002439745675030694</v>
       </c>
       <c r="G9" t="n">
         <v>6763.000000000102</v>
@@ -703,10 +703,10 @@
         <v>44710</v>
       </c>
       <c r="E10" t="n">
-        <v>1.477000000000408</v>
+        <v>1.175999999999476</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3592356687897864</v>
+        <v>0.3898089171971714</v>
       </c>
       <c r="G10" t="n">
         <v>156.9999999999936</v>
@@ -757,10 +757,10 @@
         <v>44731</v>
       </c>
       <c r="E12" t="n">
-        <v>26.49700000000303</v>
+        <v>22.93399999999674</v>
       </c>
       <c r="F12" t="n">
-        <v>1.736719883889356</v>
+        <v>1.592017416544937</v>
       </c>
       <c r="G12" t="n">
         <v>688.9999999999873</v>
@@ -811,10 +811,10 @@
         <v>44734</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04500000000007276</v>
+        <v>0.04499999999989086</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2199999999993577</v>
+        <v>0.2299999999995765</v>
       </c>
       <c r="G14" t="n">
         <v>9.999999999999432</v>
@@ -838,10 +838,10 @@
         <v>44734</v>
       </c>
       <c r="E15" t="n">
-        <v>3.105999999999767</v>
+        <v>5.860000000000582</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6629746835446551</v>
+        <v>1.191455696202317</v>
       </c>
       <c r="G15" t="n">
         <v>316.0000000000082</v>
@@ -892,10 +892,10 @@
         <v>44706</v>
       </c>
       <c r="E17" t="n">
-        <v>33.95800000000018</v>
+        <v>15.84700000000012</v>
       </c>
       <c r="F17" t="n">
-        <v>3.065183752417842</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>516.9999999999959</v>
@@ -919,10 +919,10 @@
         <v>44566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2180000000007567</v>
+        <v>0.125</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01668891855807741</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>749.0000000000009</v>
@@ -973,10 +973,10 @@
         <v>44655</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4970000000001164</v>
+        <v>0.2480000000010477</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02344045368629957</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>1057.999999999993</v>
@@ -1027,10 +1027,10 @@
         <v>44729</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.01599999999889406</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.004395604395300512</v>
       </c>
       <c r="G22" t="n">
         <v>364.0000000000043</v>
@@ -1081,10 +1081,10 @@
         <v>44730</v>
       </c>
       <c r="E24" t="n">
-        <v>32.58800000000046</v>
+        <v>38.6100000000035</v>
       </c>
       <c r="F24" t="n">
-        <v>1.458273950910923</v>
+        <v>1.598733174980063</v>
       </c>
       <c r="G24" t="n">
         <v>1263.000000000011</v>
@@ -1189,10 +1189,10 @@
         <v>44718</v>
       </c>
       <c r="E28" t="n">
-        <v>2.044999999999709</v>
+        <v>0.939999999999418</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1697580645161004</v>
+        <v>0.01975806451604764</v>
       </c>
       <c r="G28" t="n">
         <v>495.9999999999809</v>
@@ -1216,10 +1216,10 @@
         <v>44732</v>
       </c>
       <c r="E29" t="n">
-        <v>12.37400000000489</v>
+        <v>10.96299999999465</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8346521145982514</v>
+        <v>0.6608458390169796</v>
       </c>
       <c r="G29" t="n">
         <v>732.9999999999927</v>
@@ -1243,10 +1243,10 @@
         <v>44734</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8189999999944121</v>
+        <v>1.013000000000466</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02062706270627062</v>
+        <v>0.02116336633665286</v>
       </c>
       <c r="G30" t="n">
         <v>2424.000000000001</v>
@@ -1270,7 +1270,7 @@
         <v>44724</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002999999999974534</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>44724</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03899999999999863</v>
+        <v>0.03500000000000227</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1324,10 +1324,10 @@
         <v>44728</v>
       </c>
       <c r="E33" t="n">
-        <v>3.908999999999651</v>
+        <v>3.938999999999942</v>
       </c>
       <c r="F33" t="n">
-        <v>0.820799999999581</v>
+        <v>0.7548000000003958</v>
       </c>
       <c r="G33" t="n">
         <v>250</v>
@@ -1378,7 +1378,7 @@
         <v>44710</v>
       </c>
       <c r="E35" t="n">
-        <v>4.979999999998836</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1486,10 +1486,10 @@
         <v>44665</v>
       </c>
       <c r="E39" t="n">
-        <v>147.4410000000033</v>
+        <v>28.46600000000326</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05421991962058465</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>52501.0000000002</v>
@@ -1513,10 +1513,10 @@
         <v>44734</v>
       </c>
       <c r="E40" t="n">
-        <v>7.176999999996042</v>
+        <v>9.612999999994646</v>
       </c>
       <c r="F40" t="n">
-        <v>1.725910931172379</v>
+        <v>2.165991902834582</v>
       </c>
       <c r="G40" t="n">
         <v>246.9999999999345</v>
@@ -1675,10 +1675,10 @@
         <v>44730</v>
       </c>
       <c r="E46" t="n">
-        <v>1.812000000000262</v>
+        <v>1.811999999999534</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5892405063289725</v>
+        <v>0.5575949367087191</v>
       </c>
       <c r="G46" t="n">
         <v>157.9999999999984</v>
@@ -1756,7 +1756,7 @@
         <v>44724</v>
       </c>
       <c r="E49" t="n">
-        <v>0.007000000000016371</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         <v>44700</v>
       </c>
       <c r="E55" t="n">
-        <v>13.4359999999986</v>
+        <v>11.04400000000023</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2242401779095663</v>
+        <v>0.1848776871757059</v>
       </c>
       <c r="G55" t="n">
         <v>2697.999999999956</v>
@@ -1945,7 +1945,7 @@
         <v>44662</v>
       </c>
       <c r="E56" t="n">
-        <v>3.051999999996042</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         <v>44699</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01199999999998909</v>
+        <v>0.002999999999974534</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>44734</v>
       </c>
       <c r="E63" t="n">
-        <v>110.7</v>
+        <v>114.5550000000047</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9182074584769706</v>
+        <v>0.8754935756815939</v>
       </c>
       <c r="G63" t="n">
         <v>6381.999999999971</v>
@@ -2188,10 +2188,10 @@
         <v>44631</v>
       </c>
       <c r="E65" t="n">
-        <v>0.01600000000034925</v>
+        <v>0.009999999999126884</v>
       </c>
       <c r="F65" t="n">
-        <v>0.001256281407108304</v>
+        <v>0.001256281406742679</v>
       </c>
       <c r="G65" t="n">
         <v>397.999999999999</v>
@@ -2296,10 +2296,10 @@
         <v>44683</v>
       </c>
       <c r="E69" t="n">
-        <v>1.125</v>
+        <v>2.15799999999872</v>
       </c>
       <c r="F69" t="n">
-        <v>0.164096385542118</v>
+        <v>0.3559036144575906</v>
       </c>
       <c r="G69" t="n">
         <v>414.9999999999864</v>
@@ -2323,10 +2323,10 @@
         <v>44641</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0180000000000291</v>
+        <v>0.01599999999998545</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>0.005479452054789508</v>
       </c>
       <c r="G70" t="n">
         <v>292.0000000000016</v>
@@ -2350,10 +2350,10 @@
         <v>44733</v>
       </c>
       <c r="E71" t="n">
-        <v>0.04799999999995634</v>
+        <v>0.03899999999994179</v>
       </c>
       <c r="F71" t="n">
-        <v>0.007727272727193193</v>
+        <v>0.01000000000005271</v>
       </c>
       <c r="G71" t="n">
         <v>220.0000000000045</v>
@@ -2377,10 +2377,10 @@
         <v>44735</v>
       </c>
       <c r="E72" t="n">
-        <v>36.94600000000209</v>
+        <v>32.62199999999721</v>
       </c>
       <c r="F72" t="n">
-        <v>2.438927097661597</v>
+        <v>2.048143053645442</v>
       </c>
       <c r="G72" t="n">
         <v>726.9999999999982</v>
@@ -2458,10 +2458,10 @@
         <v>44732</v>
       </c>
       <c r="E75" t="n">
-        <v>23.66399999998976</v>
+        <v>15.51399999998976</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9671264367804013</v>
+        <v>0.8160919540229629</v>
       </c>
       <c r="G75" t="n">
         <v>870.0000000000273</v>
@@ -2512,10 +2512,10 @@
         <v>44734</v>
       </c>
       <c r="E77" t="n">
-        <v>45.60999999999767</v>
+        <v>36.94099999999744</v>
       </c>
       <c r="F77" t="n">
-        <v>1.152103418054218</v>
+        <v>0.4666958808063069</v>
       </c>
       <c r="G77" t="n">
         <v>2282.000000000016</v>
@@ -2539,10 +2539,10 @@
         <v>44721</v>
       </c>
       <c r="E78" t="n">
-        <v>1.690999999999622</v>
+        <v>1.162000000000262</v>
       </c>
       <c r="F78" t="n">
-        <v>0.07719072164945838</v>
+        <v>0.05438144329898414</v>
       </c>
       <c r="G78" t="n">
         <v>775.9999999999991</v>
@@ -2674,10 +2674,10 @@
         <v>44725</v>
       </c>
       <c r="E83" t="n">
-        <v>0.04600000000000364</v>
+        <v>0.05200000000004366</v>
       </c>
       <c r="F83" t="n">
-        <v>0.07083333333336096</v>
+        <v>0.1458333333334794</v>
       </c>
       <c r="G83" t="n">
         <v>24.00000000000091</v>
@@ -2863,7 +2863,7 @@
         <v>44731</v>
       </c>
       <c r="E90" t="n">
-        <v>6.712999999997555</v>
+        <v>2.795999999999185</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>44571</v>
       </c>
       <c r="E91" t="n">
-        <v>7.623999999999069</v>
+        <v>2.544999999995343</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         <v>44726</v>
       </c>
       <c r="E92" t="n">
-        <v>0.02599999999983993</v>
+        <v>0.004000000000087311</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>0.010256410256633</v>
       </c>
       <c r="G92" t="n">
         <v>39.00000000000432</v>
@@ -2971,10 +2971,10 @@
         <v>44731</v>
       </c>
       <c r="E94" t="n">
-        <v>35.3219999999972</v>
+        <v>51.65299999999697</v>
       </c>
       <c r="F94" t="n">
-        <v>12.23723404255236</v>
+        <v>15.23776595744444</v>
       </c>
       <c r="G94" t="n">
         <v>188.0000000000109</v>
@@ -2998,10 +2998,10 @@
         <v>44733</v>
       </c>
       <c r="E95" t="n">
-        <v>80.05999999999767</v>
+        <v>61.52999999999302</v>
       </c>
       <c r="F95" t="n">
-        <v>1.818946188340885</v>
+        <v>1.630044843049006</v>
       </c>
       <c r="G95" t="n">
         <v>1783.999999999924</v>
@@ -3079,10 +3079,10 @@
         <v>44585</v>
       </c>
       <c r="E98" t="n">
-        <v>25.19700000000012</v>
+        <v>41.25</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5766723842194742</v>
+        <v>0.8384219554031673</v>
       </c>
       <c r="G98" t="n">
         <v>2915</v>
@@ -3106,7 +3106,7 @@
         <v>44632</v>
       </c>
       <c r="E99" t="n">
-        <v>0.006999999999970896</v>
+        <v>0.003000000000020009</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3160,10 +3160,10 @@
         <v>44730</v>
       </c>
       <c r="E101" t="n">
-        <v>1.045000000000436</v>
+        <v>0.932999999999447</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4579710144932612</v>
+        <v>0.3826086956520908</v>
       </c>
       <c r="G101" t="n">
         <v>68.99999999999977</v>
@@ -3187,10 +3187,10 @@
         <v>44734</v>
       </c>
       <c r="E102" t="n">
-        <v>7.554999999998836</v>
+        <v>10.54199999999837</v>
       </c>
       <c r="F102" t="n">
-        <v>1.605681818181253</v>
+        <v>2.387499999999968</v>
       </c>
       <c r="G102" t="n">
         <v>263.9999999999986</v>
@@ -3241,10 +3241,10 @@
         <v>44734</v>
       </c>
       <c r="E104" t="n">
-        <v>65.69599999999919</v>
+        <v>41.46299999999756</v>
       </c>
       <c r="F104" t="n">
-        <v>1.375640355462482</v>
+        <v>0.7917929952953492</v>
       </c>
       <c r="G104" t="n">
         <v>1913.000000000011</v>
@@ -3268,10 +3268,10 @@
         <v>44734</v>
       </c>
       <c r="E105" t="n">
-        <v>0.075</v>
+        <v>0.08599999999987631</v>
       </c>
       <c r="F105" t="n">
-        <v>0.05671641791032937</v>
+        <v>0.0716417910447123</v>
       </c>
       <c r="G105" t="n">
         <v>66.99999999999875</v>
@@ -3322,10 +3322,10 @@
         <v>44534</v>
       </c>
       <c r="E107" t="n">
-        <v>221.2530000000028</v>
+        <v>162.6859999999986</v>
       </c>
       <c r="F107" t="n">
-        <v>28.83413897280937</v>
+        <v>20.31570996978921</v>
       </c>
       <c r="G107" t="n">
         <v>330.9999999999945</v>
@@ -3376,7 +3376,7 @@
         <v>44724</v>
       </c>
       <c r="E109" t="n">
-        <v>0.06199999999989814</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -3430,10 +3430,10 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>5.717999999999302</v>
+        <v>7.425</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>0.4072916666666481</v>
       </c>
       <c r="G111" t="n">
         <v>768.0000000000064</v>
@@ -3457,7 +3457,7 @@
         <v>44724</v>
       </c>
       <c r="E112" t="n">
-        <v>0.2069999999999709</v>
+        <v>0.03499999999985448</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -3538,10 +3538,10 @@
         <v>44682</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1190000000000055</v>
+        <v>0.08899999999998727</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2809523809522326</v>
+        <v>0.1428571428572289</v>
       </c>
       <c r="G115" t="n">
         <v>21.00000000000009</v>
@@ -3565,10 +3565,10 @@
         <v>44732</v>
       </c>
       <c r="E116" t="n">
-        <v>5.236999999999535</v>
+        <v>4.651999999996042</v>
       </c>
       <c r="F116" t="n">
-        <v>1.275126903553045</v>
+        <v>1.086294416241867</v>
       </c>
       <c r="G116" t="n">
         <v>197.0000000000027</v>
@@ -3592,10 +3592,10 @@
         <v>44733</v>
       </c>
       <c r="E117" t="n">
-        <v>24.575</v>
+        <v>26.15</v>
       </c>
       <c r="F117" t="n">
-        <v>5.605381165919237</v>
+        <v>6.121076233183807</v>
       </c>
       <c r="G117" t="n">
         <v>223.0000000000018</v>
@@ -3646,10 +3646,10 @@
         <v>44735</v>
       </c>
       <c r="E119" t="n">
-        <v>84.41699999999837</v>
+        <v>74.06999999999535</v>
       </c>
       <c r="F119" t="n">
-        <v>9.407226107224993</v>
+        <v>7.858508158508332</v>
       </c>
       <c r="G119" t="n">
         <v>428.9999999999964</v>
@@ -3727,10 +3727,10 @@
         <v>44734</v>
       </c>
       <c r="E122" t="n">
-        <v>2.044000000000233</v>
+        <v>0.8179999999993015</v>
       </c>
       <c r="F122" t="n">
-        <v>0.05696378830078651</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
         <v>1436.000000000013</v>
@@ -3835,10 +3835,10 @@
         <v>44728</v>
       </c>
       <c r="E126" t="n">
-        <v>6.807000000000698</v>
+        <v>10.84200000000128</v>
       </c>
       <c r="F126" t="n">
-        <v>7.138709677420803</v>
+        <v>10.34838709677468</v>
       </c>
       <c r="G126" t="n">
         <v>62.00000000000045</v>
@@ -3916,10 +3916,10 @@
         <v>44713</v>
       </c>
       <c r="E129" t="n">
-        <v>30.75600000000559</v>
+        <v>23.78499999999767</v>
       </c>
       <c r="F129" t="n">
-        <v>0.4184995480567073</v>
+        <v>0.3049111178064233</v>
       </c>
       <c r="G129" t="n">
         <v>3319.000000000051</v>
@@ -4024,10 +4024,10 @@
         <v>44630</v>
       </c>
       <c r="E133" t="n">
-        <v>25.26699999999837</v>
+        <v>39.8179999999993</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5706053975200271</v>
+        <v>0.8815463165572593</v>
       </c>
       <c r="G133" t="n">
         <v>2742.000000000007</v>
@@ -4051,10 +4051,10 @@
         <v>44710</v>
       </c>
       <c r="E134" t="n">
-        <v>7.952999999999884</v>
+        <v>9.563999999998487</v>
       </c>
       <c r="F134" t="n">
-        <v>0.6208823529411979</v>
+        <v>0.7855882352938832</v>
       </c>
       <c r="G134" t="n">
         <v>679.9999999999955</v>
@@ -4132,7 +4132,7 @@
         <v>44686</v>
       </c>
       <c r="E137" t="n">
-        <v>0.09600000000000364</v>
+        <v>0.1529999999999745</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>0.1270000000000437</v>
       </c>
       <c r="F139" t="n">
-        <v>0.01218568665379156</v>
+        <v>0.009284332688579637</v>
       </c>
       <c r="G139" t="n">
         <v>516.9999999999959</v>
@@ -4321,10 +4321,10 @@
         <v>44734</v>
       </c>
       <c r="E144" t="n">
-        <v>1.35</v>
+        <v>1.954999999998836</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3003663003667748</v>
+        <v>0.4084249084258266</v>
       </c>
       <c r="G144" t="n">
         <v>272.9999999999563</v>
@@ -4348,10 +4348,10 @@
         <v>44734</v>
       </c>
       <c r="E145" t="n">
-        <v>10.11899999999441</v>
+        <v>12.38999999999069</v>
       </c>
       <c r="F145" t="n">
-        <v>0.5138358778623724</v>
+        <v>0.6679389312977088</v>
       </c>
       <c r="G145" t="n">
         <v>1048.000000000002</v>
@@ -4375,10 +4375,10 @@
         <v>44731</v>
       </c>
       <c r="E146" t="n">
-        <v>9.365999999997438</v>
+        <v>11.44199999999837</v>
       </c>
       <c r="F146" t="n">
-        <v>3.376397515527292</v>
+        <v>3.730434782608783</v>
       </c>
       <c r="G146" t="n">
         <v>160.99999999999</v>
@@ -4510,10 +4510,10 @@
         <v>44716</v>
       </c>
       <c r="E151" t="n">
-        <v>2.782000000000699</v>
+        <v>2.074000000000524</v>
       </c>
       <c r="F151" t="n">
-        <v>1.187155963302993</v>
+        <v>0.7155963302755128</v>
       </c>
       <c r="G151" t="n">
         <v>108.9999999999975</v>
@@ -4672,10 +4672,10 @@
         <v>44610</v>
       </c>
       <c r="E157" t="n">
-        <v>0.3879999999975553</v>
+        <v>0.6309999999997672</v>
       </c>
       <c r="F157" t="n">
-        <v>0.02532544378680301</v>
+        <v>0.04934911242618678</v>
       </c>
       <c r="G157" t="n">
         <v>845.0000000000045</v>
@@ -4699,10 +4699,10 @@
         <v>44668</v>
       </c>
       <c r="E158" t="n">
-        <v>0.653000000002794</v>
+        <v>0.7969999999972061</v>
       </c>
       <c r="F158" t="n">
-        <v>0.04608294930875582</v>
+        <v>0.06758832565319953</v>
       </c>
       <c r="G158" t="n">
         <v>650.9999999999991</v>
@@ -4861,7 +4861,7 @@
         <v>44734</v>
       </c>
       <c r="E164" t="n">
-        <v>0.005999999999767169</v>
+        <v>0.002999999999883585</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -4888,10 +4888,10 @@
         <v>44727</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1</v>
+        <v>0.3619999999998981</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>0.1168831168833043</v>
       </c>
       <c r="G165" t="n">
         <v>77.00000000000102</v>
@@ -4915,7 +4915,7 @@
         <v>44724</v>
       </c>
       <c r="E166" t="n">
-        <v>0.006000000000130967</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
